--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 04-Sep-2026  14:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-Sep-2026  16:26</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.467</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.9329999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.711</v>
+        <v>0.6223</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,56 +703,56 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>6</v>
-      </c>
       <c r="E5" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <v>0.6</v>
-      </c>
       <c r="H5" s="10" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.583</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,31 +765,31 @@
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -802,7 +802,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.4</v>
@@ -811,16 +811,16 @@
         <v>0.467</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4447</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -830,112 +830,112 @@
         <v>6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.4167</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.45</v>
+        <v>0.417</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.4</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F11" s="10" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>0.333</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>0.5329999999999999</v>
-      </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3997</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.067</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.667</v>
+        <v>0.467</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.3557</v>
@@ -951,7 +951,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.3</v>
@@ -969,7 +969,7 @@
         <v>0.4</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,87 +982,87 @@
         <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>0.167</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0.25</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.25</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>13</v>
-      </c>
       <c r="F15" s="10" t="n">
-        <v>0.175</v>
+        <v>0.067</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.325</v>
+        <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2083</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.125</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.275</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2250</v>
+        <v>2215</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2133.35</v>
+        <v>2141.13</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2021.73</v>
+        <v>2029.31</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1921.26</v>
+        <v>1925.69</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>601</v>
+        <v>589.15</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>588.39</v>
+        <v>588.46</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>575.14</v>
+        <v>575.6900000000001</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>556.72</v>
+        <v>556.88</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1165</v>
+        <v>1147.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1140.45</v>
+        <v>1141.16</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1121.35</v>
+        <v>1122.39</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1117.8</v>
+        <v>1118.89</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>737.85</v>
+        <v>736.8</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>722.48</v>
+        <v>723.84</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>720.61</v>
+        <v>721.24</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>734.5599999999999</v>
+        <v>734.72</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1325</v>
+        <v>2658.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1305.31</v>
+        <v>2557.47</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1285.09</v>
+        <v>2510.69</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1227.5</v>
+        <v>2453.38</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2727</v>
+        <v>187.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>2546.84</v>
+        <v>186</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2504.65</v>
+        <v>179.57</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2454.47</v>
+        <v>166.9</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,387 +1397,387 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>196.8</v>
+        <v>2597.9</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>185.8</v>
+        <v>2286.68</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>179.23</v>
+        <v>1963.73</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>166.24</v>
+        <v>1385.85</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>188.79</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>186.02</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>188.28</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>188.28</v>
-      </c>
-      <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>679.05</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>640.99</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>599.87</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>584.98</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>2590.6</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>2253.92</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>1937.84</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>1372.7</v>
-      </c>
-      <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>772.4</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>663.0599999999999</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>624.91</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>546.85</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>BRIGADE</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>696.1</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>636.99</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>596.64</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>585.22</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1660</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>1638.75</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>1596.62</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1414.19</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>681.9</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>673.13</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>655.96</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>643.87</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>9315</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>8848.42</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>8183.83</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>7038.87</v>
+      </c>
+      <c r="G13" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>1875.6</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>1865.83</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>1831.22</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>1716.62</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>2974.3</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>2839.21</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>2657.8</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>2207.02</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>1942</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>1928.86</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1928.77</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1811.7</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>2451.9</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2394.47</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2323.24</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2197.41</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>740.85</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>651.55</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>618.89</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>544.83</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>867.3</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>846.27</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>834.28</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>723.2</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>145</v>
+        <v>1959.1</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>143.33</v>
+        <v>1908.47</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>142.8</v>
+        <v>1821.59</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>139.9</v>
+        <v>1617.58</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BANKINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>879.7</v>
+        <v>1876.7</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>877.65</v>
+        <v>1844.15</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>862.79</v>
+        <v>1729.97</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>832.28</v>
+        <v>1366.31</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>85.95</v>
+        <v>1156.9</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>82.58</v>
+        <v>1143.93</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>81.78</v>
+        <v>1125.49</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>73.69</v>
+        <v>1039.34</v>
       </c>
       <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>117</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>115.56</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>112.93</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>110.42</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>AFFLE</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>1623.2</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1622.66</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1593.43</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1593.91</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AFFLE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>187.22</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>184.59</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>178.73</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>165.97</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>1935</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1887.95</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1742.69</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1566.12</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1972.8</v>
+        <v>1105.4</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1883</v>
+        <v>1018.94</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1734.84</v>
+        <v>945.49</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>1564.83</v>
+        <v>962.85</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,23 +1789,23 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1101.8</v>
+        <v>243.01</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1009.83</v>
+        <v>230.11</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>938.97</v>
+        <v>215.35</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>962.65</v>
+        <v>151.86</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>231.44</v>
+        <v>15.6</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>228.75</v>
+        <v>14.37</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>214.22</v>
+        <v>13.91</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>150.86</v>
+        <v>12.09</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,835 +1845,527 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>15.02</v>
+        <v>593.6</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>14.24</v>
+        <v>545.26</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>13.84</v>
+        <v>536.38</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>12</v>
+        <v>509.81</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>12058</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>11893.75</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>11394.88</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>9583.92</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>189.01</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>186.36</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>183.73</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>180.43</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>5643</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>5604.57</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>5406.93</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>5307.65</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>176</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>173.71</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>167.58</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>1756.1</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>1718.55</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>1753.97</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>1718.15</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>487</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>476.55</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>464.02</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>448.73</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>TEJASNET</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>614.15</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>540.17</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>534.05</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>509.53</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>288.64</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>283.95</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>277.34</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>1427.5</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1426.67</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1407.2</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1362.32</v>
+      </c>
+      <c r="G30" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>422.1</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>410.9</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>400.52</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>396.56</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>552</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>527.23</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>523.63</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>528.42</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>3330.2</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>3159.18</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>3004.28</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>2642.93</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>85</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>82.81</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>81.91</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>115.56</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>113.03</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>110.53</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>186.04</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>179.01</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>166.27</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>48025</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>47124.16</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>44502.64</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>39897.92</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>AMBER</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>7474</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>7438.7</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>7465.1</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>7452.62</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AMBER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>1239.6</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>1227.35</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>1206.74</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>1141.8</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>598.8</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>595.58</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>553.9400000000001</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>477.51</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>VGUARD</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
-        <v>335.4</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>332.08</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>322.18</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>324.09</v>
-      </c>
-      <c r="G33" s="15">
+      <c r="C38" s="14" t="n">
+        <v>332.55</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>332.13</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>322.59</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>324.67</v>
+      </c>
+      <c r="G38" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VGUARD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>1636.52</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>1594.03</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>1411.37</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>9100</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>8799.309999999999</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>8137.67</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>7024.64</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>2932.4</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>2824.99</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>2644.88</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>2199.96</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>2437.2</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>2388.42</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>2317.99</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>2189.92</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>848.3</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>844.0599999999999</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>832.9299999999999</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>721.22</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C39" s="18" t="n">
-        <v>1965.3</v>
+        <v>370.3</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>1903.14</v>
+        <v>358.17</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>1815.97</v>
+        <v>337.5</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>1615.7</v>
+        <v>296.31</v>
       </c>
       <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>1273</v>
+        <v>86.44</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>1256.46</v>
+        <v>85.27</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>1266.06</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>1259.95</v>
+        <v>77.39</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>424.5</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>409.72</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>399.63</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>396.3</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>711.55</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>671.62</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>634.1</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>552.63</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>562.05</v>
+        <v>895</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>524.62</v>
+        <v>886.6799999999999</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>522.47</v>
+        <v>885.86</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>527.75</v>
+        <v>820.54</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>3275.4</v>
+        <v>418.85</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>3141.18</v>
+        <v>406.23</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>2990.97</v>
+        <v>412.01</v>
       </c>
       <c r="F43" s="14" t="n">
-        <v>2636.21</v>
+        <v>413.36</v>
       </c>
       <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>190.27</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>186.09</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>183.51</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>180.49</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>488.3</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>475.45</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>463.08</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>448.48</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>11919</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>11800.05</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>11311.29</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>10193.31</v>
-      </c>
-      <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="n">
-        <v>368.65</v>
-      </c>
-      <c r="D47" s="18" t="n">
-        <v>356.89</v>
-      </c>
-      <c r="E47" s="18" t="n">
-        <v>336.16</v>
-      </c>
-      <c r="F47" s="18" t="n">
-        <v>295.55</v>
-      </c>
-      <c r="G47" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n">
-        <v>1227.2</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>1202.38</v>
-      </c>
-      <c r="E48" s="18" t="n">
-        <v>1137.29</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <v>1066.59</v>
-      </c>
-      <c r="G48" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>86.70999999999999</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>85.15000000000001</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>82.76000000000001</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>77.3</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B50" s="13" t="inlineStr">
-        <is>
-          <t>INDUSINDBK</t>
-        </is>
-      </c>
-      <c r="C50" s="14" t="n">
-        <v>1008.5</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>1006.15</v>
-      </c>
-      <c r="E50" s="14" t="n">
-        <v>994.58</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>918.29</v>
-      </c>
-      <c r="G50" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSINDBK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B51" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="n">
-        <v>431.1</v>
-      </c>
-      <c r="D51" s="18" t="n">
-        <v>423.3</v>
-      </c>
-      <c r="E51" s="18" t="n">
-        <v>412.23</v>
-      </c>
-      <c r="F51" s="18" t="n">
-        <v>348.36</v>
-      </c>
-      <c r="G51" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B52" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n">
-        <v>891</v>
-      </c>
-      <c r="D52" s="18" t="n">
-        <v>885.8099999999999</v>
-      </c>
-      <c r="E52" s="18" t="n">
-        <v>885.49</v>
-      </c>
-      <c r="F52" s="18" t="n">
-        <v>819.29</v>
-      </c>
-      <c r="G52" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="D53" s="18" t="n">
-        <v>404.9</v>
-      </c>
-      <c r="E53" s="18" t="n">
-        <v>411.73</v>
-      </c>
-      <c r="F53" s="18" t="n">
-        <v>413.64</v>
-      </c>
-      <c r="G53" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B54" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n">
-        <v>690.6</v>
-      </c>
-      <c r="D54" s="14" t="n">
-        <v>667.41</v>
-      </c>
-      <c r="E54" s="14" t="n">
-        <v>630.9400000000001</v>
-      </c>
-      <c r="F54" s="14" t="n">
-        <v>552.49</v>
-      </c>
-      <c r="G54" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-Sep-2026  16:26</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 08-Sep-2026  15:03</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
         <v>7</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>13</v>
@@ -684,13 +684,13 @@
         <v>0.467</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.867</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6223</v>
+        <v>0.6446999999999999</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>5</v>
@@ -712,7 +712,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.5</v>
@@ -721,7 +721,7 @@
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,7 +734,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>10</v>
@@ -743,7 +743,7 @@
         <v>11</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0.5</v>
@@ -752,7 +752,7 @@
         <v>0.55</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4833</v>
+        <v>0.5167</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,7 +765,7 @@
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9</v>
@@ -774,7 +774,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.45</v>
@@ -783,7 +783,7 @@
         <v>0.5</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -820,32 +820,32 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>9</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.35</v>
+        <v>0.333</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3667</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -861,19 +861,19 @@
         <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.361</v>
@@ -882,63 +882,63 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.067</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3557</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>0.467</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>0.3557</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>4</v>
@@ -994,75 +994,75 @@
         <v>0.083</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1943</v>
+        <v>0.2497</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.067</v>
+        <v>0.15</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="F16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.067</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.275</v>
+        <v>0.333</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2215</v>
+        <v>2185</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2141.13</v>
+        <v>2137.87</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2029.31</v>
+        <v>2027.93</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1925.69</v>
+        <v>1920.95</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>589.15</v>
+        <v>532.85</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>588.46</v>
+        <v>530.54</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>575.6900000000001</v>
+        <v>525</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>556.88</v>
+        <v>489.11</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1147.9</v>
+        <v>595.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1141.16</v>
+        <v>589.13</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1122.39</v>
+        <v>576.47</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1118.89</v>
+        <v>557.27</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>736.8</v>
+        <v>738.75</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>723.84</v>
+        <v>724.03</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>721.24</v>
+        <v>721.3200000000001</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>734.72</v>
+        <v>734.74</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2658.5</v>
+        <v>2803.8</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2557.47</v>
+        <v>2571.31</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2510.69</v>
+        <v>2516.38</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2453.38</v>
+        <v>2454.83</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>187.9</v>
+        <v>186.1</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>186</v>
+        <v>186.01</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>179.57</v>
+        <v>179.83</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>166.9</v>
+        <v>167.09</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2597.9</v>
+        <v>2599.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2286.68</v>
+        <v>2316.47</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1963.73</v>
+        <v>1988.66</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1385.85</v>
+        <v>1397.93</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>679.05</v>
+        <v>687</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>640.99</v>
+        <v>641.75</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>599.87</v>
+        <v>600.1900000000001</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>584.98</v>
+        <v>585.0599999999999</v>
       </c>
       <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
@@ -1453,79 +1453,79 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>675.1</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>673.3200000000001</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>656.71</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>644.13</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>772.4</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>663.0599999999999</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>624.91</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>546.85</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="C12" s="18" t="n">
+        <v>857.8</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>671.2</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>628.26</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>547.6900000000001</v>
+      </c>
+      <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>1660</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>1638.75</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>1596.62</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>1414.19</v>
-      </c>
-      <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>9315</v>
+        <v>3579.3</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>8848.42</v>
+        <v>3541.23</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>8183.83</v>
+        <v>3447.94</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>7038.87</v>
+        <v>3078.23</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>2974.3</v>
+        <v>1692</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>2839.21</v>
+        <v>1641.8</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2657.8</v>
+        <v>1597.87</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>2207.02</v>
+        <v>1414.5</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2451.9</v>
+        <v>9575</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2394.47</v>
+        <v>8917.620000000001</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2323.24</v>
+        <v>8238.389999999999</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2197.41</v>
+        <v>7064.1</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>867.3</v>
+        <v>2959.3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>846.27</v>
+        <v>2850.65</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>834.28</v>
+        <v>2669.62</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>723.2</v>
+        <v>2214.51</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1959.1</v>
+        <v>2474.5</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1908.47</v>
+        <v>2402.09</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1821.59</v>
+        <v>2329.17</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1617.58</v>
+        <v>2200.17</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1876.7</v>
+        <v>895.35</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1844.15</v>
+        <v>850.95</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1729.97</v>
+        <v>836.6799999999999</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1366.31</v>
+        <v>724.91</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,135 +1677,135 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1967.2</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1914.07</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1827.3</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>1621.06</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1946.9</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1850.83</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1732.73</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1367.01</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>4960</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>4945.28</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>4872.49</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>4426.84</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>1156.9</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>1143.93</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>1125.49</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>1039.34</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C22" s="14" t="n">
+        <v>1145.5</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1144.08</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1126.27</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1040.39</v>
+      </c>
+      <c r="G22" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>AFFLE</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>1623.2</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1622.66</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1593.43</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1593.91</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AFFLE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
-        <v>1935</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1887.95</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1742.69</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1566.12</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="C23" s="18" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1893.86</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1750.82</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1569.94</v>
+      </c>
+      <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>1105.4</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>1018.94</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>945.49</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>962.85</v>
-      </c>
-      <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>243.01</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>230.11</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>215.35</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>151.86</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>15.6</v>
+        <v>1086.3</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>14.37</v>
+        <v>1025.35</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>13.91</v>
+        <v>951.01</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>12.09</v>
+        <v>964.08</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1845,107 +1845,107 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>250.76</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>232.08</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>216.74</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>152.84</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>15.42</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
           <t>TEJASNET</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>593.6</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>545.26</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>536.38</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>509.81</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C27" s="18" t="n">
+        <v>590.05</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>549.52</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>538.49</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>510.61</v>
+      </c>
+      <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>189.01</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>186.36</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>183.73</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>180.43</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C28" s="14" t="n">
+        <v>189.46</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>186.66</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>183.95</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>180.52</v>
+      </c>
+      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>176</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>173.71</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>172.6</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>167.58</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>487</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>476.55</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>464.02</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>448.73</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1957,135 +1957,135 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>290.95</v>
+        <v>175.09</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>288.64</v>
+        <v>173.84</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>283.95</v>
+        <v>172.69</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>277.34</v>
+        <v>167.65</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>1427.5</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>1426.67</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>1407.2</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>1362.32</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>495.4</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>478.34</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>465.25</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>449.19</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>422.1</v>
+        <v>11880</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>410.9</v>
+        <v>11807.66</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>400.52</v>
+        <v>11352.02</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>396.56</v>
+        <v>10254.67</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>552</v>
+        <v>48785</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>527.23</v>
+        <v>47282.33</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>523.63</v>
+        <v>44670.57</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>528.42</v>
+        <v>39986.35</v>
       </c>
       <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C33" s="18" t="n">
-        <v>3330.2</v>
+        <v>163.85</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>3159.18</v>
+        <v>163.73</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>3004.28</v>
+        <v>157.44</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>2642.93</v>
+        <v>135.94</v>
       </c>
       <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2101,16 +2101,16 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>85</v>
+        <v>84.79000000000001</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>82.81</v>
+        <v>83</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>81.91</v>
+        <v>82.02</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>73.88</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>115.6</v>
+        <v>116</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>115.56</v>
+        <v>115.61</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>113.03</v>
+        <v>113.15</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>110.53</v>
+        <v>110.59</v>
       </c>
       <c r="G35" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
@@ -2146,226 +2146,338 @@
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>186.04</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>184.73</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>179.01</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>166.27</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>1250.2</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>1228.94</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>1208.96</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>1142.97</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>48025</v>
+        <v>612.6</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>47124.16</v>
+        <v>597.2</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>44502.64</v>
+        <v>556.24</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>39897.92</v>
+        <v>479.19</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>332.55</v>
+        <v>419.25</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>332.13</v>
+        <v>411.7</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>322.59</v>
+        <v>401.25</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>324.67</v>
+        <v>396.79</v>
       </c>
       <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VGUARD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>358.17</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>337.5</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>296.31</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>563</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>528.28</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>524.0599999999999</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>528.53</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>86.44</v>
+        <v>3342</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>85.27</v>
+        <v>3176.59</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>82.90000000000001</v>
+        <v>3017.52</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>77.39</v>
+        <v>2649.89</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>357.99</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>337.43</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>296.29</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>1231.3</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>1201.18</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>1141.7</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>1067.58</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n">
+        <v>910.7</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>888.97</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>886.84</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>821.4400000000001</v>
+      </c>
+      <c r="G44" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>420.25</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>407.56</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>412.33</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>413.43</v>
+      </c>
+      <c r="G45" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>4750</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>4351.96</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>4395.33</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>4051.07</v>
+      </c>
+      <c r="G46" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n">
-        <v>711.55</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>671.62</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>634.1</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>552.63</v>
-      </c>
-      <c r="G41" s="19">
+      <c r="C47" s="14" t="n">
+        <v>711.45</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>675.41</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>637.14</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>554.22</v>
+      </c>
+      <c r="G47" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>895</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>886.6799999999999</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>885.86</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>820.54</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>418.85</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>406.23</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>412.01</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>413.36</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 08-Sep-2026  15:03</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 09-Sep-2026  15:13</t>
         </is>
       </c>
     </row>
@@ -672,87 +672,87 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.467</v>
+        <v>0.867</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6446999999999999</v>
+        <v>0.9109999999999999</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="E5" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.55</v>
+        <v>0.8</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5167</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,25 +765,25 @@
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4167</v>
+        <v>0.3833</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,242 +796,242 @@
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="E9" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3777</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.067</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.361</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.417</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.3</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.3</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.3</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.175</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2497</v>
+        <v>0.2583</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.15</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2185</v>
+        <v>3104.7</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2137.87</v>
+        <v>2997.99</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2027.93</v>
+        <v>2990.98</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1920.95</v>
+        <v>2681</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>532.85</v>
+        <v>2168</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>530.54</v>
+        <v>2140.74</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>525</v>
+        <v>2033.42</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>489.11</v>
+        <v>1923.7</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>595.5</v>
+        <v>1026.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>589.13</v>
+        <v>1022.53</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>576.47</v>
+        <v>1014.39</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>557.27</v>
+        <v>959.55</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>738.75</v>
+        <v>532.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>724.03</v>
+        <v>530.7</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>721.3200000000001</v>
+        <v>525.29</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>734.74</v>
+        <v>489.44</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2803.8</v>
+        <v>605.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2571.31</v>
+        <v>590.6799999999999</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2516.38</v>
+        <v>577.61</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2454.83</v>
+        <v>557.58</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>186.1</v>
+        <v>1146.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>186.01</v>
+        <v>1140.67</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>179.83</v>
+        <v>1122.9</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>167.09</v>
+        <v>1118.44</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,499 +1397,499 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2599.5</v>
+        <v>783.3</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2316.47</v>
+        <v>729.67</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1988.66</v>
+        <v>723.75</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1397.93</v>
+        <v>736.86</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>BRIGADE</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>687</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>641.75</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>600.1900000000001</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>585.0599999999999</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1304.81</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1287.14</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1232.28</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>675.1</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>673.3200000000001</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>656.71</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>644.13</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>85.31</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="G11" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>857.8</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>671.2</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>628.26</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>547.6900000000001</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>2859.2</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>2598.73</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>2529.83</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>2457.59</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>3579.3</v>
+        <v>186.4</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>3541.23</v>
+        <v>186.05</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>3447.94</v>
+        <v>180.09</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>3078.23</v>
+        <v>167.12</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1692</v>
+        <v>188.75</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1641.8</v>
+        <v>186.09</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1597.87</v>
+        <v>188.05</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1414.5</v>
+        <v>188.4</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>2608.5</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2344.29</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2012.97</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1412.08</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1698.9</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1647.24</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1601.83</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1417.64</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
       </c>
-      <c r="C15" s="14" t="n">
-        <v>9575</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>8917.620000000001</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>8238.389999999999</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>7064.1</v>
-      </c>
-      <c r="G15" s="15">
+      <c r="C17" s="18" t="n">
+        <v>9488</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>8971.940000000001</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>8287.389999999999</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>7086.2</v>
+      </c>
+      <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>GLAND</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
-        <v>2959.3</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>2850.65</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>2669.62</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>2214.51</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C18" s="18" t="n">
+        <v>3026.2</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>2867.37</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>2683.6</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>2226.04</v>
+      </c>
+      <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>GLENMARK</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
-        <v>2474.5</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>2402.09</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>2329.17</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>2200.17</v>
-      </c>
-      <c r="G17" s="15">
+      <c r="C19" s="18" t="n">
+        <v>2435</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>2405.23</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>2333.33</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>2207.67</v>
+      </c>
+      <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>GRANULES</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
-        <v>895.35</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>850.95</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>836.6799999999999</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>724.91</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="C20" s="18" t="n">
+        <v>884.8</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>854.17</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>838.5599999999999</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>726.98</v>
+      </c>
+      <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>IPCALAB</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>1967.2</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>1914.07</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>1827.3</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>1621.06</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C21" s="18" t="n">
+        <v>1963.6</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1918.78</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1832.64</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1624.44</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
-        <v>1946.9</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>1850.83</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>1732.73</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>1367.01</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C22" s="18" t="n">
+        <v>1937</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>1859.04</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>1740.74</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>1373.26</v>
+      </c>
+      <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>4960</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>4945.28</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>4872.49</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>4426.84</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1145.5</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1144.08</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1126.27</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1040.39</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>643.76</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>602.64</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>585.55</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>MAHLIFE</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>370.1</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>369.64</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>361.64</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>808.45</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>684.27</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>635.3200000000001</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>550.63</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1950</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1893.86</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1750.82</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1569.94</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>CYIENT</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>1086.3</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1025.35</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>951.01</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>964.08</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C26" s="18" t="n">
+        <v>1075.1</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1030.09</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>955.88</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>966.29</v>
+      </c>
+      <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>250.76</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>232.08</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>216.74</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>152.84</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>14.47</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>13.97</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1901,582 +1901,694 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>245.43</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>233.35</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>217.86</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>153.69</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>14.03</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>1772.8</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>1726.66</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>1754.66</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>1723</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
           <t>TEJASNET</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
-        <v>590.05</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>549.52</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>538.49</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>510.61</v>
-      </c>
-      <c r="G27" s="19">
+      <c r="C30" s="18" t="n">
+        <v>575.9</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>552.04</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>539.95</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>510.94</v>
+      </c>
+      <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>1343.4</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>1294.48</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>1247.76</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>972.6900000000001</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C28" s="14" t="n">
-        <v>189.46</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>186.66</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>183.95</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>180.52</v>
-      </c>
-      <c r="G28" s="15">
+      <c r="C32" s="14" t="n">
+        <v>189.16</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>184.16</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>180.6</v>
+      </c>
+      <c r="G32" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>GAIL</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>175.09</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>173.84</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>172.69</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>167.65</v>
-      </c>
-      <c r="G29" s="15">
+      <c r="C33" s="14" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>173.94</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>172.78</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>167.77</v>
+      </c>
+      <c r="G33" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>OIL</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
-        <v>495.4</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>478.34</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>465.25</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>449.19</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="C34" s="14" t="n">
+        <v>498.95</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>480.31</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>466.57</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>449.73</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>296.88</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>500.55</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>500.49</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>493.96</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>442.83</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>BAJAJ-AUTO</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>11880</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>11807.66</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>11352.02</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>10254.67</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BAJAJ-AUTO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>BOSCHLTD</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>48785</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>47282.33</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>44670.57</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>39986.35</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="C37" s="14" t="n">
+        <v>49100</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>47455.44</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>44844.28</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>40088.34</v>
+      </c>
+      <c r="G37" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>163.85</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>163.73</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>157.44</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>414</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>411.92</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>397.13</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>555</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>530.8200000000001</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>525.28</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>528.62</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>3193.11</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>3030.56</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>2656.53</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n">
-        <v>84.79000000000001</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>83</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>82.02</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="G34" s="15">
+      <c r="C41" s="14" t="n">
+        <v>84.56</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>83.15000000000001</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>82.12</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>74.04000000000001</v>
+      </c>
+      <c r="G41" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
-        <v>116</v>
-      </c>
-      <c r="D35" s="14" t="n">
+      <c r="C42" s="14" t="n">
         <v>115.61</v>
       </c>
-      <c r="E35" s="14" t="n">
-        <v>113.15</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>110.59</v>
-      </c>
-      <c r="G35" s="15">
+      <c r="D42" s="14" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>113.24</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>110.64</v>
+      </c>
+      <c r="G42" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>KAJARIACER</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
-        <v>1250.2</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>1228.94</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>1208.96</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>1142.97</v>
-      </c>
-      <c r="G36" s="19">
+      <c r="C43" s="18" t="n">
+        <v>1239.2</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>1229.91</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>1210.15</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>1144.44</v>
+      </c>
+      <c r="G43" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n">
-        <v>612.6</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>597.2</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>556.24</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>479.19</v>
-      </c>
-      <c r="G37" s="19">
+      <c r="C44" s="18" t="n">
+        <v>607.6</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>598.1900000000001</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>558.25</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>480</v>
+      </c>
+      <c r="G44" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>411.7</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>401.25</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>396.79</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>563</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>528.28</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>524.0599999999999</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>528.53</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>3342</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>3176.59</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>3017.52</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>2649.89</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>368.4</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>357.99</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>337.43</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>296.29</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>1231.3</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>1201.18</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>1141.7</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>1067.58</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="n">
+        <v>214.9</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>208.09</v>
+      </c>
+      <c r="E45" s="14" t="n">
+        <v>210.46</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>191.07</v>
+      </c>
+      <c r="G45" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>424.04</v>
+      </c>
+      <c r="E46" s="14" t="n">
+        <v>413.78</v>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="G46" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>926.95</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>892.59</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>888.41</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>821.99</v>
+      </c>
+      <c r="G47" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="n">
+        <v>431</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>409.79</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>413.07</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>413.67</v>
+      </c>
+      <c r="G48" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>4673</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>4382.54</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>4406.22</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>4057.26</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B50" s="17" t="inlineStr">
         <is>
           <t>IDFCFIRSTB</t>
         </is>
       </c>
-      <c r="C43" s="14" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>85.39</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>83.04000000000001</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>77.48</v>
-      </c>
-      <c r="G43" s="15">
+      <c r="C50" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>77.67</v>
+      </c>
+      <c r="G50" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>910.7</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>888.97</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>886.84</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>821.4400000000001</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>420.25</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>407.56</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>412.33</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>413.43</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>4750</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>4351.96</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>4395.33</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>4051.07</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="C47" s="14" t="n">
-        <v>711.45</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>675.41</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>637.14</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>554.22</v>
-      </c>
-      <c r="G47" s="15">
+      <c r="C51" s="14" t="n">
+        <v>700.05</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>677.76</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>639.6</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>554.34</v>
+      </c>
+      <c r="G51" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 09-Sep-2026  15:13</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 10-Sep-2026  14:57</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="F4" s="6" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>0.867</v>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>0.9329999999999999</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.9329999999999999</v>
-      </c>
       <c r="I4" s="7" t="n">
-        <v>0.9109999999999999</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -706,7 +706,7 @@
         <v>7</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>11</v>
@@ -715,137 +715,137 @@
         <v>0.35</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.55</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.4443</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3833</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.7</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.333</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -864,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.067</v>
@@ -873,20 +873,20 @@
         <v>0.267</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.289</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>4</v>
@@ -895,81 +895,81 @@
         <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2833</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.417</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.278</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.167</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,25 +982,25 @@
         <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.175</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.275</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2583</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>4</v>
@@ -1025,13 +1025,13 @@
         <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.222</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3104.7</v>
+        <v>3077.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2997.99</v>
+        <v>3005.54</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2990.98</v>
+        <v>2994.36</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2681</v>
+        <v>2687.24</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2168</v>
+        <v>2194.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2140.74</v>
+        <v>2145.89</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2033.42</v>
+        <v>2039.75</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1923.7</v>
+        <v>1926.46</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1026.9</v>
+        <v>593.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1022.53</v>
+        <v>590.96</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1014.39</v>
+        <v>578.23</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>959.55</v>
+        <v>557.89</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDALCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>532.3</v>
+        <v>762.15</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>530.7</v>
+        <v>732.77</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>525.29</v>
+        <v>725.26</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>489.44</v>
+        <v>737.86</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDCOPPER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>605.4</v>
+        <v>2823</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>590.6799999999999</v>
+        <v>2620.09</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>577.61</v>
+        <v>2541.32</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>557.58</v>
+        <v>2461.41</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,555 +1369,555 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1146.5</v>
+        <v>2776.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1140.67</v>
+        <v>2385.49</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1122.9</v>
+        <v>2042.93</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1118.44</v>
+        <v>1425.51</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>JSL</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>783.3</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>729.67</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>723.75</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>736.86</v>
-      </c>
-      <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1668.4</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1649.25</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1604.44</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1420.66</v>
+      </c>
+      <c r="G9" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>1310</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1304.81</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1287.14</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>1232.28</v>
-      </c>
-      <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>9438.5</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>9016.379999999999</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>8332.530000000001</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>7111.95</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>85.31</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>85.45</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>83.15000000000001</v>
-      </c>
-      <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NMDC","Chart 📈")</f>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>2946.9</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>2874.94</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>2693.93</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>2231.72</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>2859.2</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>2598.73</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>2529.83</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>2457.59</v>
-      </c>
-      <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2415</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2406.16</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2336.53</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>2210.9</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>186.05</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>180.09</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>167.12</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>899.25</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>858.47</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>840.9400000000001</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>728.66</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>188.75</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>186.09</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>188.05</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>188.4</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>1970.9</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>1923.75</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>1838.06</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>1627.31</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>2608.5</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>2344.29</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>2012.97</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>1412.08</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>1945</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1867.22</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1748.75</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1378.47</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>1698.9</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>1647.24</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1601.83</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>1417.64</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>1307.6</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1295.73</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>1250.11</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>976.01</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>9488</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>8971.940000000001</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>8287.389999999999</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>7086.2</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>188.06</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>187.01</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>184.31</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>180.79</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>3026.2</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>2867.37</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>2683.6</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>2226.04</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>174.49</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>173.99</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>172.85</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>167.91</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>2435</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>2405.23</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>2333.33</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>2207.67</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>500.3</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>482.21</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>467.89</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>450.09</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>884.8</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>854.17</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>838.5599999999999</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>726.98</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>288.7</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>288.01</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>284.03</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>277.61</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>1963.6</v>
+        <v>374.65</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1918.78</v>
+        <v>360.99</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>1832.64</v>
+        <v>340.28</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1624.44</v>
+        <v>297.24</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1937</v>
+        <v>1221.3</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1859.04</v>
+        <v>1200.34</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1740.74</v>
+        <v>1145.86</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>1373.26</v>
+        <v>1070.85</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>505.15</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>500.94</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>443.43</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>658.4</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>652.87</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>657.0700000000001</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>619.28</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>BRIGADE</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
-        <v>662.9</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>643.76</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>602.64</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>585.55</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="C25" s="14" t="n">
+        <v>651.15</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>644.47</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>604.55</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>588.12</v>
+      </c>
+      <c r="G25" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>MAHLIFE</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>370.1</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>369.86</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>369.64</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>361.64</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
-        <v>808.45</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>684.27</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>635.3200000000001</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>550.63</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="C26" s="14" t="n">
+        <v>853.85</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>700.42</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>643.89</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>554.55</v>
+      </c>
+      <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>CYIENT</t>
         </is>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>1075.1</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1030.09</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>955.88</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>966.29</v>
-      </c>
-      <c r="G26" s="19">
+      <c r="C27" s="18" t="n">
+        <v>1076.4</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1034.5</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>960.61</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>971.14</v>
+      </c>
+      <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>245.43</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>233.35</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>217.86</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>153.69</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>15.52</v>
+        <v>14.9</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>14.57</v>
+        <v>14.6</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>14.03</v>
+        <v>14.07</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>12.15</v>
+        <v>12.18</v>
       </c>
       <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
@@ -1961,16 +1961,16 @@
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1772.8</v>
+        <v>1764.4</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1726.66</v>
+        <v>1730.26</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1754.66</v>
+        <v>1755.05</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1723</v>
+        <v>1721.74</v>
       </c>
       <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
@@ -1978,617 +1978,449 @@
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>TEJASNET</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>575.9</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>552.04</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>539.95</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>510.94</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>48775</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>47581.12</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>44998.41</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>40135.21</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>1343.4</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>1294.48</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>1247.76</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>972.6900000000001</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>1243.9</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>1231.24</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>1211.47</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>1145.72</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>189.16</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>186.9</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>184.16</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>180.6</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>599.8099999999999</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>560.49</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>481.9</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>174.9</v>
+        <v>1859</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>173.94</v>
+        <v>1849.77</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>172.78</v>
+        <v>1816.8</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>167.77</v>
+        <v>1696.85</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>498.95</v>
+        <v>416.55</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>480.31</v>
+        <v>412.36</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>466.57</v>
+        <v>402.33</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>449.73</v>
+        <v>397.53</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>374.4</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>359.55</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>338.88</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>296.88</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>552.3</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>532.87</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>526.34</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>529.12</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>500.55</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>500.49</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>493.96</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>442.83</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>3203.29</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>3041.12</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>2663.05</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>49100</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>47455.44</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>44844.28</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>40088.34</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>84.34999999999999</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>83.26000000000001</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>82.20999999999999</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A38" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C38" s="18" t="n">
-        <v>414</v>
+        <v>116.85</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>411.92</v>
+        <v>115.72</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>401.75</v>
+        <v>113.38</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>397.13</v>
+        <v>110.86</v>
       </c>
       <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>555</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>530.8200000000001</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>525.28</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>528.62</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>213.5</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>208.6</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>210.58</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>191.15</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>3350</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>3193.11</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>3030.56</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>2656.53</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>424.56</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>414.4</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>352.14</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>MAHABANK</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>84.56</v>
+        <v>914.55</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>83.15000000000001</v>
+        <v>894.6799999999999</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>82.12</v>
+        <v>889.4400000000001</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>74.04000000000001</v>
+        <v>825.22</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>115.61</v>
+        <v>432</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>115.61</v>
+        <v>411.91</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>113.24</v>
+        <v>413.81</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>110.64</v>
+        <v>414.15</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>1239.2</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>1229.91</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>1210.15</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>1144.44</v>
-      </c>
-      <c r="G43" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>4545</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>4398.01</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>4411.67</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>4063.46</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="C44" s="18" t="n">
-        <v>607.6</v>
+        <v>86.84</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>598.1900000000001</v>
+        <v>85.58</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>558.25</v>
+        <v>83.3</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>480</v>
+        <v>77.69</v>
       </c>
       <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>214.9</v>
+        <v>705.15</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>208.09</v>
+        <v>680.37</v>
       </c>
       <c r="E45" s="14" t="n">
-        <v>210.46</v>
+        <v>642.17</v>
       </c>
       <c r="F45" s="14" t="n">
-        <v>191.07</v>
+        <v>556.3099999999999</v>
       </c>
       <c r="G45" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="n">
-        <v>433.7</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <v>424.04</v>
-      </c>
-      <c r="E46" s="14" t="n">
-        <v>413.78</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>350.92</v>
-      </c>
-      <c r="G46" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>926.95</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>892.59</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>888.41</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>821.99</v>
-      </c>
-      <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
-        <v>431</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>409.79</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>413.07</v>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>413.67</v>
-      </c>
-      <c r="G48" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>4673</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>4382.54</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>4406.22</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>4057.26</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>86</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>85.45</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>83.16</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>77.67</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>700.05</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>677.76</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>639.6</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>554.34</v>
-      </c>
-      <c r="G51" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 10-Sep-2026  14:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 11-Sep-2026  15:02</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.8</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.667</v>
+        <v>0.4887</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,7 +703,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>9</v>
@@ -712,7 +712,7 @@
         <v>11</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.45</v>
@@ -721,66 +721,66 @@
         <v>0.55</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.45</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4443</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.4</v>
@@ -789,104 +789,104 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.7</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.15</v>
+        <v>0.267</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.35</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3113</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>4</v>
@@ -895,50 +895,50 @@
         <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.311</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -957,7 +957,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.167</v>
@@ -966,10 +966,10 @@
         <v>0.167</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.278</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -985,7 +985,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>11</v>
@@ -994,13 +994,13 @@
         <v>0.25</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.15</v>
+        <v>0.125</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.275</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.225</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3077.2</v>
+        <v>3060</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3005.54</v>
+        <v>3010.72</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2994.36</v>
+        <v>2996.94</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2687.24</v>
+        <v>2695.66</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2194.8</v>
+        <v>2153.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2145.89</v>
+        <v>2146.61</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2039.75</v>
+        <v>2044.21</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1926.46</v>
+        <v>1927.6</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>593.6</v>
+        <v>756.1</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>590.96</v>
+        <v>734.99</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>578.23</v>
+        <v>726.46</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>557.89</v>
+        <v>736.66</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>762.15</v>
+        <v>2811.4</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>732.77</v>
+        <v>2638.31</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>725.26</v>
+        <v>2551.92</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>737.86</v>
+        <v>2466.09</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,79 +1341,79 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2823</v>
+        <v>2676.6</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2620.09</v>
+        <v>2413.21</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2541.32</v>
+        <v>2067.78</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2461.41</v>
+        <v>1436.89</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>2776.9</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>2385.49</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>2042.93</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>1425.51</v>
-      </c>
-      <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1679.8</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>1652.16</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1607.4</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1428.07</v>
+      </c>
+      <c r="G8" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C9" s="18" t="n">
-        <v>1668.4</v>
+        <v>9322</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1649.25</v>
+        <v>9045.48</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>1604.44</v>
+        <v>8371.34</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1420.66</v>
+        <v>7132.65</v>
       </c>
       <c r="G9" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>9438.5</v>
+        <v>2922.3</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>9016.379999999999</v>
+        <v>2879.45</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>8332.530000000001</v>
+        <v>2702.89</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>7111.95</v>
+        <v>2243.7</v>
       </c>
       <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>2946.9</v>
+        <v>2419.2</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>2874.94</v>
+        <v>2407.4</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>2693.93</v>
+        <v>2339.77</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>2231.72</v>
+        <v>2212.72</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>2415</v>
+        <v>909.3</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>2406.16</v>
+        <v>863.3099999999999</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2336.53</v>
+        <v>843.62</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>2210.9</v>
+        <v>730.5700000000001</v>
       </c>
       <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,23 +1509,23 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>899.25</v>
+        <v>1968.5</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>858.47</v>
+        <v>1928.01</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>840.9400000000001</v>
+        <v>1843.18</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>728.66</v>
+        <v>1630.64</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,23 +1537,23 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>1970.9</v>
+        <v>1969</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1923.75</v>
+        <v>1876.92</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1838.06</v>
+        <v>1757.39</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1627.31</v>
+        <v>1384.28</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,695 +1565,695 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1945</v>
+        <v>4965.5</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1867.22</v>
+        <v>4944.7</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1748.75</v>
+        <v>4880.39</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1378.47</v>
+        <v>4439.72</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1307.6</v>
+        <v>370.3</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1295.73</v>
+        <v>361.88</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1250.11</v>
+        <v>341.46</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>976.01</v>
+        <v>298.17</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>188.06</v>
+        <v>1237.1</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>187.01</v>
+        <v>1203.84</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>184.31</v>
+        <v>1149.44</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>180.79</v>
+        <v>1073.67</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>174.49</v>
+        <v>505.5</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>173.99</v>
+        <v>501.37</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>172.85</v>
+        <v>494.84</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>167.91</v>
+        <v>443.8</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>500.3</v>
+        <v>661.55</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>482.21</v>
+        <v>653.7</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>467.89</v>
+        <v>657.24</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>450.09</v>
+        <v>619.74</v>
       </c>
       <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>288.7</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>288.01</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>284.03</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>277.61</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>1059.4</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1036.87</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>964.48</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>972.4</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>374.65</v>
+        <v>233.69</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>360.99</v>
+        <v>233.38</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>340.28</v>
+        <v>219.07</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>297.24</v>
+        <v>155.29</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="C22" s="18" t="n">
-        <v>1221.3</v>
+        <v>14.97</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1200.34</v>
+        <v>14.64</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>1145.86</v>
+        <v>14.1</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>1070.85</v>
+        <v>12.22</v>
       </c>
       <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>505.15</v>
+        <v>1761.6</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>500.94</v>
+        <v>1733.24</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>494.4</v>
+        <v>1755.3</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>443.43</v>
+        <v>1722.18</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>658.4</v>
+        <v>552.65</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>652.87</v>
+        <v>551.9</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>657.0700000000001</v>
+        <v>540.8200000000001</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>619.28</v>
+        <v>511.99</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>651.15</v>
+        <v>48385</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>644.47</v>
+        <v>47657.68</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>604.55</v>
+        <v>45131.2</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>588.12</v>
+        <v>40189.04</v>
       </c>
       <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BRIGADE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>853.85</v>
+        <v>164.45</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>700.42</v>
+        <v>163.75</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>643.89</v>
+        <v>158.16</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>554.55</v>
+        <v>136.93</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1076.4</v>
+        <v>1353.6</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1034.5</v>
+        <v>1301.24</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>960.61</v>
+        <v>1254.17</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>971.14</v>
+        <v>980.8200000000001</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>14.9</v>
+        <v>188.03</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>14.6</v>
+        <v>187.11</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>14.07</v>
+        <v>184.46</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>12.18</v>
+        <v>180.94</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>1764.4</v>
+        <v>489.8</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>1730.26</v>
+        <v>482.93</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>1755.05</v>
+        <v>468.75</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>1721.74</v>
+        <v>450.8</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>48775</v>
+        <v>1002.8</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>47581.12</v>
+        <v>729.22</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>44998.41</v>
+        <v>657.97</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>40135.21</v>
+        <v>558.6799999999999</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>1243.9</v>
+        <v>419</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>1231.24</v>
+        <v>412.99</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>1211.47</v>
+        <v>402.98</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>1145.72</v>
+        <v>397.72</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>535.73</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>527.77</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>529.6</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>3276</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>3210.21</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>3050.33</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>2668.37</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>599.8099999999999</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>560.49</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>481.9</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="C34" s="14" t="n">
+        <v>601.15</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>597.73</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>559.89</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>481.05</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>1859</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>1849.77</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1816.8</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>1696.85</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CHOLAFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>416.55</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>412.36</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>402.33</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>397.53</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>552.3</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>532.87</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>526.34</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>529.12</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>82.29000000000001</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>74.42</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>3203.29</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>3041.12</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>2663.05</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>115.82</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>113.52</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>111.03</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>84.34999999999999</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>83.26000000000001</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>82.20999999999999</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>74.28</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>431</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>425.18</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>415.05</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>353.65</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>116.85</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>115.72</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>113.38</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>110.86</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>909</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>896.04</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>890.21</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>827.36</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>213.5</v>
+        <v>426.4</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>208.6</v>
+        <v>413.29</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>210.58</v>
+        <v>414.3</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>191.15</v>
+        <v>414.38</v>
       </c>
       <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIPOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2265,162 +2265,78 @@
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="C40" s="14" t="n">
-        <v>429.5</v>
+        <v>4548.1</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>424.56</v>
+        <v>4412.3</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>414.4</v>
+        <v>4417.02</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>352.14</v>
+        <v>4066.48</v>
       </c>
       <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>914.55</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>894.6799999999999</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>889.4400000000001</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>825.22</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>83.42</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>77.76000000000001</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>432</v>
+        <v>691.4</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>411.91</v>
+        <v>681.42</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>413.81</v>
+        <v>644.1</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>414.15</v>
+        <v>556.87</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>4545</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>4398.01</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>4411.67</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>4063.46</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n">
-        <v>86.84</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>85.58</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>77.69</v>
-      </c>
-      <c r="G44" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="n">
-        <v>705.15</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <v>680.37</v>
-      </c>
-      <c r="E45" s="14" t="n">
-        <v>642.17</v>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>556.3099999999999</v>
-      </c>
-      <c r="G45" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 11-Sep-2026  15:02</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-Sep-2026  16:58</t>
         </is>
       </c>
     </row>
@@ -851,60 +851,60 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="F11" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <v>0.25</v>
-      </c>
       <c r="H11" s="10" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.2667</v>
@@ -1242,7 +1242,7 @@
         <v>2996.94</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2695.66</v>
+        <v>2694.41</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
@@ -1270,7 +1270,7 @@
         <v>2044.21</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1927.6</v>
+        <v>1929.12</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1298,7 +1298,7 @@
         <v>726.46</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>736.66</v>
+        <v>735.77</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1326,7 +1326,7 @@
         <v>2551.92</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2466.09</v>
+        <v>2468.64</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1354,7 +1354,7 @@
         <v>2067.78</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1436.89</v>
+        <v>1441.28</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1382,7 +1382,7 @@
         <v>1607.4</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1428.07</v>
+        <v>1427.32</v>
       </c>
       <c r="G8" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1410,7 +1410,7 @@
         <v>8371.34</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>7132.65</v>
+        <v>7136.07</v>
       </c>
       <c r="G9" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1438,7 +1438,7 @@
         <v>2702.89</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>2243.7</v>
+        <v>2247.88</v>
       </c>
       <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1466,7 +1466,7 @@
         <v>2339.77</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>2212.72</v>
+        <v>2210.61</v>
       </c>
       <c r="G11" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
@@ -1494,7 +1494,7 @@
         <v>843.62</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>730.5700000000001</v>
+        <v>731.16</v>
       </c>
       <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1522,7 +1522,7 @@
         <v>1843.18</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>1630.64</v>
+        <v>1630.48</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1550,7 +1550,7 @@
         <v>1757.39</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1384.28</v>
+        <v>1384.23</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1575,10 +1575,10 @@
         <v>4944.7</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>4880.39</v>
+        <v>4880.38</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>4439.72</v>
+        <v>4435.5</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
@@ -1606,7 +1606,7 @@
         <v>341.46</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>298.17</v>
+        <v>298.46</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1634,7 +1634,7 @@
         <v>1149.44</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1073.67</v>
+        <v>1071.87</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
@@ -1659,10 +1659,10 @@
         <v>501.37</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>494.84</v>
+        <v>494.83</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>443.8</v>
+        <v>443.32</v>
       </c>
       <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
@@ -1690,7 +1690,7 @@
         <v>657.24</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>619.74</v>
+        <v>619.34</v>
       </c>
       <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
@@ -1718,7 +1718,7 @@
         <v>964.48</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>972.4</v>
+        <v>971.47</v>
       </c>
       <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1746,7 +1746,7 @@
         <v>219.07</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>155.29</v>
+        <v>155.58</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1774,7 +1774,7 @@
         <v>14.1</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>12.22</v>
+        <v>12.28</v>
       </c>
       <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
@@ -1799,10 +1799,10 @@
         <v>1733.24</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1755.3</v>
+        <v>1755.31</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1722.18</v>
+        <v>1729.31</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
@@ -1830,7 +1830,7 @@
         <v>540.8200000000001</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>511.99</v>
+        <v>512.29</v>
       </c>
       <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
@@ -1855,10 +1855,10 @@
         <v>47657.68</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>45131.2</v>
+        <v>45131.15</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>40189.04</v>
+        <v>40090.01</v>
       </c>
       <c r="G25" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
@@ -1886,7 +1886,7 @@
         <v>158.16</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>136.93</v>
+        <v>137.51</v>
       </c>
       <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
@@ -1914,7 +1914,7 @@
         <v>1254.17</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>980.8200000000001</v>
+        <v>984.46</v>
       </c>
       <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
@@ -1942,7 +1942,7 @@
         <v>184.46</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>180.94</v>
+        <v>180.91</v>
       </c>
       <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
@@ -1970,7 +1970,7 @@
         <v>468.75</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>450.8</v>
+        <v>450.82</v>
       </c>
       <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
@@ -1980,112 +1980,112 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>419</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>412.99</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>402.98</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>397.7</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>562.9</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>535.73</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>527.77</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>530.34</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>3276</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>3210.21</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>3050.34</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>2671.39</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
+      <c r="C33" s="18" t="n">
         <v>1002.8</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D33" s="18" t="n">
         <v>729.22</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E33" s="18" t="n">
         <v>657.97</v>
       </c>
-      <c r="F30" s="14" t="n">
-        <v>558.6799999999999</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="F33" s="18" t="n">
+        <v>558.96</v>
+      </c>
+      <c r="G33" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>419</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>412.99</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>402.98</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>397.72</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>562.9</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>535.73</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>527.77</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>529.6</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>3276</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>3210.21</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>3050.33</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>2668.37</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
         <v>559.89</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>481.05</v>
+        <v>480.96</v>
       </c>
       <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
@@ -2138,7 +2138,7 @@
         <v>82.29000000000001</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>74.42</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="G35" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
@@ -2166,7 +2166,7 @@
         <v>113.52</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>111.03</v>
+        <v>111.09</v>
       </c>
       <c r="G36" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
@@ -2194,7 +2194,7 @@
         <v>415.05</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>353.65</v>
+        <v>353.7</v>
       </c>
       <c r="G37" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
@@ -2222,7 +2222,7 @@
         <v>890.21</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>827.36</v>
+        <v>827.87</v>
       </c>
       <c r="G38" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
@@ -2250,7 +2250,7 @@
         <v>414.3</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>414.38</v>
+        <v>414.49</v>
       </c>
       <c r="G39" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
@@ -2278,7 +2278,7 @@
         <v>4417.02</v>
       </c>
       <c r="F40" s="14" t="n">
-        <v>4066.48</v>
+        <v>4075.26</v>
       </c>
       <c r="G40" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
@@ -2306,7 +2306,7 @@
         <v>83.42</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>77.76000000000001</v>
+        <v>77.69</v>
       </c>
       <c r="G41" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
@@ -2334,7 +2334,7 @@
         <v>644.1</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>556.87</v>
+        <v>557.17</v>
       </c>
       <c r="G42" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-Sep-2026  16:58</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-Sep-2026  15:37</t>
         </is>
       </c>
     </row>
@@ -665,131 +665,131 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4887</v>
+        <v>0.4167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4833</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -799,239 +799,239 @@
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.311</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.467</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.311</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.25</v>
-      </c>
       <c r="H10" s="6" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.333</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>0.267</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>12</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.167</v>
+        <v>0.083</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2223</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.275</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2167</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.05</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.025</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.275</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1943</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,25 +1044,25 @@
         <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.08869999999999999</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1078,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,1120 +1224,504 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3060</v>
+        <v>1660</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3010.72</v>
+        <v>1652.91</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2996.94</v>
+        <v>1609.46</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2694.41</v>
+        <v>1429.64</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2153.5</v>
+        <v>9198</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2146.61</v>
+        <v>9060.01</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2044.21</v>
+        <v>8403.76</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1929.12</v>
+        <v>7156.58</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>756.1</v>
+        <v>2895.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>734.99</v>
+        <v>2880.98</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>726.46</v>
+        <v>2710.44</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>735.77</v>
+        <v>2254.33</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>872.6</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>864.1900000000001</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>844.76</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>732.5700000000001</v>
+      </c>
+      <c r="G6" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>1932.4</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1928.43</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1846.68</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1633.49</v>
+      </c>
+      <c r="G7" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>1926.9</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>1881.68</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>1764.03</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>1389.63</v>
+      </c>
+      <c r="G8" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1205.48</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1152.24</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1073.35</v>
+      </c>
+      <c r="G9" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>659.15</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>654.22</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>657.3200000000001</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>619.73</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>1078.9</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1040.87</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>968.97</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>972.54</v>
+      </c>
+      <c r="G11" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>1323.5</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1303.36</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1256.89</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>987.83</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>187.82</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>187.17</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>184.59</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>485.6</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>483.19</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>469.41</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>451.16</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>RATNAMANI</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>2811.4</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>2638.31</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>2551.92</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>2468.64</v>
-      </c>
-      <c r="G6" s="15">
+      <c r="C15" s="14" t="n">
+        <v>2691.4</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2643.36</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2557.39</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>2470.86</v>
+      </c>
+      <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C7" s="14" t="n">
-        <v>2676.6</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>2413.21</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>2067.78</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>1441.28</v>
-      </c>
-      <c r="G7" s="15">
+      <c r="C16" s="14" t="n">
+        <v>2413.3</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2413.22</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>2081.33</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1450.96</v>
+      </c>
+      <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>1679.8</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>1652.16</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>1607.4</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>1427.32</v>
-      </c>
-      <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>995.95</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>754.62</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>671.22</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>563.3099999999999</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>9322</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>9045.48</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>8371.34</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>7136.07</v>
-      </c>
-      <c r="G9" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>2922.3</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>2879.45</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>2702.89</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>2247.88</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>2419.2</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>2407.4</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>2339.77</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>2210.61</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>909.3</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>863.3099999999999</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>843.62</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>731.16</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>1968.5</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>1928.01</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>1843.18</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1630.48</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>1969</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>1876.92</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>1757.39</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>1384.23</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>4965.5</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>4944.7</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>4880.38</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>4435.5</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>361.88</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>341.46</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>298.46</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>1237.1</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>1203.84</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>1149.44</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>1071.87</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>505.5</v>
+        <v>542</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>501.37</v>
+        <v>536.33</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>494.83</v>
+        <v>528.33</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>443.32</v>
+        <v>530.45</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>661.55</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>653.7</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>657.24</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>619.34</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>1059.4</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1036.87</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>964.48</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>971.47</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>233.69</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>233.38</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>219.07</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>155.58</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>14.97</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1761.6</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1733.24</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1755.31</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1729.31</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>TEJASNET</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>552.65</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>551.9</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>512.29</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TEJASNET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>48385</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>47657.68</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>45131.15</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>40090.01</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>164.45</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>163.75</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>158.16</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>137.51</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>1353.6</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>1301.24</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>1254.17</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>984.46</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>188.03</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>187.11</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>184.46</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>180.91</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>489.8</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>482.93</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>468.75</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>450.82</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>419</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>412.99</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>402.98</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>397.7</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>562.9</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>535.73</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>527.77</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>530.34</v>
-      </c>
-      <c r="G31" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>3276</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>3210.21</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>3050.34</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>2671.39</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>1002.8</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>729.22</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>657.97</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>558.96</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>KALYANKJIL</t>
         </is>
       </c>
-      <c r="C34" s="14" t="n">
-        <v>601.15</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>597.73</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>559.89</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>480.96</v>
-      </c>
-      <c r="G34" s="15">
+      <c r="C19" s="18" t="n">
+        <v>604.2</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>598.35</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>561.63</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>482.19</v>
+      </c>
+      <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>83.34999999999999</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>82.29000000000001</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>74.43000000000001</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>116.75</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>115.82</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>113.52</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>111.09</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>431</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>425.18</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>415.05</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>353.7</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>909</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>896.04</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>890.21</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>827.87</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
-        <v>426.4</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>413.29</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>414.3</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>414.49</v>
-      </c>
-      <c r="G39" s="15">
+      <c r="C20" s="14" t="n">
+        <v>419.25</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>413.86</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>414.5</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>414.54</v>
+      </c>
+      <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>4548.1</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>4412.3</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>4417.02</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>4075.26</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>86.20999999999999</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>85.64</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>83.42</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>77.69</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>691.4</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>681.42</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>644.1</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>557.17</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,9 +205,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -591,7 +588,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-Sep-2026  15:37</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 16-Sep-2026  15:29</t>
         </is>
       </c>
     </row>
@@ -672,56 +669,56 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4167</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.3</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,7 +731,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>6</v>
@@ -743,7 +740,7 @@
         <v>9</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0.3</v>
@@ -752,35 +749,35 @@
         <v>0.45</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="F7" s="10" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.2667</v>
@@ -789,88 +786,88 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.3</v>
@@ -882,79 +879,79 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.15</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1833</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1387</v>
+        <v>0.1997</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>4</v>
@@ -963,106 +960,106 @@
         <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.083</v>
+        <v>0.267</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1387</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.025</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.275</v>
+        <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1167</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.025</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.275</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1078,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
@@ -1087,13 +1084,13 @@
         <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1229,23 +1226,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1660</v>
+        <v>9158</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1652.91</v>
+        <v>9090.9</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1609.46</v>
+        <v>8467.75</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1429.64</v>
+        <v>7201.26</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1254,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>9198</v>
+        <v>2410</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>9060.01</v>
+        <v>2405.49</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>8403.76</v>
+        <v>2346.6</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>7156.58</v>
+        <v>2214.41</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1282,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2895.5</v>
+        <v>1950.7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>2880.98</v>
+        <v>1933.71</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>2710.44</v>
+        <v>1855.29</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2254.33</v>
+        <v>1640.04</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,414 +1310,386 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>872.6</v>
+        <v>1905.5</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>864.1900000000001</v>
+        <v>1891.13</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>844.76</v>
+        <v>1777.24</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>732.5700000000001</v>
+        <v>1400.46</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>1932.4</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>1928.43</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>1846.68</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>1633.49</v>
-      </c>
-      <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>1926.9</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>1881.68</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>1764.03</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>1389.63</v>
-      </c>
-      <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>2695</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>2648.28</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>2562.79</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>2474.39</v>
+      </c>
+      <c r="G7" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>1054.5</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>1042.17</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>972.33</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>977.37</v>
+      </c>
+      <c r="G8" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1799.3</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1740.82</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1756.77</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1733.73</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>PVRINOX</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>1205.48</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>1152.24</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>1073.35</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="C10" s="18" t="n">
+        <v>1254.6</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>1212.75</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1159.43</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1079.38</v>
+      </c>
+      <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>659.15</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>654.22</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>657.3200000000001</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>619.73</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>1078.9</v>
+        <v>1381.2</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1040.87</v>
+        <v>1310.78</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>968.97</v>
+        <v>1261.76</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>972.54</v>
+        <v>995.14</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>1323.5</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>1303.36</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>1256.89</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>987.83</v>
-      </c>
-      <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>187.82</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>187.17</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>184.59</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>180.98</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="C12" s="14" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>187.33</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>184.76</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>181.32</v>
+      </c>
+      <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>OIL</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
-        <v>485.6</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>483.19</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>469.41</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>451.16</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="C13" s="14" t="n">
+        <v>487.6</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>484.14</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>470.89</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>452.21</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>993.9</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>798.74</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>696.36</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>572.42</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2691.4</v>
+        <v>415</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2643.36</v>
+        <v>413.38</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2557.39</v>
+        <v>404.29</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>2470.86</v>
+        <v>399.02</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2413.3</v>
+        <v>543</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2413.22</v>
+        <v>536.96</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2081.33</v>
+        <v>528.9</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1450.96</v>
+        <v>530.4400000000001</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>995.95</v>
+        <v>682.6</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>754.62</v>
+        <v>681.9400000000001</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>671.22</v>
+        <v>648.5700000000001</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>563.3099999999999</v>
+        <v>560.78</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>542</v>
+        <v>116.8</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>536.33</v>
+        <v>115.89</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>528.33</v>
+        <v>113.81</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>530.45</v>
+        <v>111.24</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>604.2</v>
+        <v>422.25</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>598.35</v>
+        <v>415.68</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>561.63</v>
+        <v>415.24</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>482.19</v>
+        <v>414.81</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>419.25</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>413.86</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>414.5</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>414.54</v>
-      </c>
-      <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -205,6 +205,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 16-Sep-2026  15:29</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 17-Sep-2026  15:36</t>
         </is>
       </c>
     </row>
@@ -669,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -700,56 +703,56 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.067</v>
+        <v>0.267</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.3113</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="F6" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.2833</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -762,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>2</v>
@@ -771,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.2</v>
@@ -780,69 +783,69 @@
         <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.3167</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -855,62 +858,62 @@
         <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -920,7 +923,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>5</v>
@@ -929,50 +932,50 @@
         <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1997</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.133</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.178</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -1003,14 +1006,14 @@
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1</v>
@@ -1019,7 +1022,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0.083</v>
@@ -1028,7 +1031,7 @@
         <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1387</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1041,25 +1044,25 @@
         <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F16" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>0.05</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>0.025</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.275</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1167</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1157,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1226,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>9158</v>
+        <v>1690</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>9090.9</v>
+        <v>1657.54</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>8467.75</v>
+        <v>1616.4</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>7201.26</v>
+        <v>1436.41</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1254,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2410</v>
+        <v>9323</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2405.49</v>
+        <v>9113</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2346.6</v>
+        <v>8501.290000000001</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>2214.41</v>
+        <v>7218.48</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1282,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1950.7</v>
+        <v>2907.8</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1933.71</v>
+        <v>2881.87</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1855.29</v>
+        <v>2730.19</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1640.04</v>
+        <v>2270.53</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1310,386 +1313,666 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1905.5</v>
+        <v>2416</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1891.13</v>
+        <v>2406.49</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1777.24</v>
+        <v>2349.32</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1400.46</v>
+        <v>2213.64</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>2695</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>2648.28</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>2562.79</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>2474.39</v>
-      </c>
-      <c r="G7" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>870.4</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>862.3200000000001</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>845.42</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>735.99</v>
+      </c>
+      <c r="G7" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1054.5</v>
+        <v>1970.3</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1042.17</v>
+        <v>1937.19</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>972.33</v>
+        <v>1859.8</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>977.37</v>
+        <v>1643.3</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1948.1</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1896.55</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1783.94</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1405.83</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1135.1</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1130.81</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1124.2</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1047.43</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>2148.5</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>2142.86</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>2057.68</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1936.3</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2702.6</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2653.45</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2568.27</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>2475.47</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2460.3</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>2437.25</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>2130.3</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>1479.87</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>978.2</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>815.83</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>707.41</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>575.99</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>360.67</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>343.23</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>300.07</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1272.7</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1218.46</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1163.87</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1080.43</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>1064</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1044.25</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>975.92</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>977.3</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>TATACOMM</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>1799.3</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1740.82</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>1756.77</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>1733.73</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="C18" s="14" t="n">
+        <v>1791.6</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1747.66</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1758.35</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1732.91</v>
+      </c>
+      <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>1254.6</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>1212.75</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>1159.43</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>1079.38</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>1381.2</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>1310.78</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>1261.76</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>995.14</v>
-      </c>
-      <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>188.84</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>187.33</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>184.76</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>181.32</v>
-      </c>
-      <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>487.6</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>484.14</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>470.89</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>452.21</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>993.9</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>798.74</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>696.36</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>572.42</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>415</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>413.38</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>404.29</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>399.02</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>543</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>536.96</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>528.9</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>530.4400000000001</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>682.6</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>681.9400000000001</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>648.5700000000001</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>560.78</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>115.89</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>113.81</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>111.24</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>47735</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>47610.38</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>45394.78</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>40334.22</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>413.67</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>404.77</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>399.65</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>545.9</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>539.73</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>530.79</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>531.0700000000001</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>3265.2</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>3217.31</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>3077.13</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>2695.97</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>VGUARD</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>330.15</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>329</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>323.37</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>324.91</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VGUARD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1353.8</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1318.57</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1268.83</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1002.28</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>191.72</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>187.75</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>185.03</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>181.58</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>86.33</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>85.63</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>78.02</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>116.47</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>115.95</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>113.91</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>111.56</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>429.2</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>423.75</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>415.91</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>422.25</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>415.68</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>415.24</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>414.81</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C29" s="18" t="n">
+        <v>418</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>415.9</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>415.35</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>415.14</v>
+      </c>
+      <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 17-Sep-2026  15:36</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-Sep-2026  14:57</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,56 +703,56 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>10</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.267</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4223</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.467</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -768,7 +768,7 @@
         <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>4</v>
@@ -777,44 +777,44 @@
         <v>0.4</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="E8" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3167</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,25 +827,25 @@
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.267</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.311</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,87 +858,87 @@
         <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2443</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.222</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -951,62 +951,62 @@
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.067</v>
+        <v>0.267</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.225</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1663</v>
+        <v>0.2083</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
@@ -1016,7 +1016,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>4</v>
@@ -1025,44 +1025,44 @@
         <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.167</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1663</v>
+        <v>0.1943</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.075</v>
+        <v>0.067</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.05</v>
+        <v>0.133</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.275</v>
+        <v>0.267</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1690</v>
+        <v>27270</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1657.54</v>
+        <v>26215.27</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1616.4</v>
+        <v>26446.86</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1436.41</v>
+        <v>26847.09</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>9323</v>
+        <v>3563.6</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>9113</v>
+        <v>3534.75</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>8501.290000000001</v>
+        <v>3467.29</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>7218.48</v>
+        <v>3105.23</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2907.8</v>
+        <v>5466.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>2881.87</v>
+        <v>5273.09</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>2730.19</v>
+        <v>5365.48</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>2270.53</v>
+        <v>5447.1</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2416</v>
+        <v>1734</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2406.49</v>
+        <v>1662.73</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>2349.32</v>
+        <v>1620.01</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2213.64</v>
+        <v>1441.81</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>870.4</v>
+        <v>9375</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>862.3200000000001</v>
+        <v>9137.959999999999</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>845.42</v>
+        <v>8535.549999999999</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>735.99</v>
+        <v>7244.84</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1970.3</v>
+        <v>2961.9</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1937.19</v>
+        <v>2889.49</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1859.8</v>
+        <v>2739.28</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1643.3</v>
+        <v>2279.8</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1948.1</v>
+        <v>2447.4</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1896.55</v>
+        <v>2410.39</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1783.94</v>
+        <v>2353.17</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1405.83</v>
+        <v>2221.26</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,555 +1425,975 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
+          <t>GRANULES</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>875.5</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>866.51</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>848.8</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>738.84</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>2009.6</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>1944.09</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>1865.68</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>1649.34</v>
+      </c>
+      <c r="G11" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1954</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>1898.65</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>1788.52</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1413</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>1135.1</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1130.81</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1124.2</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>1047.43</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="C13" s="14" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1133.59</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>1125.6</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1049.68</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>3020</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>2994.34</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>2992.01</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>2709.33</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>APLAPOLLO</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>2148.5</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>2142.86</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>2057.68</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>1936.3</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="C15" s="18" t="n">
+        <v>2270.1</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>2154.44</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>2062.45</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1938.13</v>
+      </c>
+      <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>2702.6</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>2653.45</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>2568.27</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>2475.47</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>2460.3</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>2437.25</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>2130.3</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1479.87</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>978.2</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>815.83</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>707.41</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>575.99</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>362.55</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>360.67</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>343.23</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>300.07</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>1272.7</v>
+        <v>596</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1218.46</v>
+        <v>584.12</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1163.87</v>
+        <v>577.6</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1080.43</v>
+        <v>560.53</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>1064</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>1044.25</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>975.92</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>977.3</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>750.95</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>737.36</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>728.98</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>736.9299999999999</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1791.6</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>1747.66</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1758.35</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1732.91</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2859.1</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>2673.64</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>2578.97</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>2484.89</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>47735</v>
+        <v>2660.1</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>47610.38</v>
+        <v>2458.48</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>45394.78</v>
+        <v>2151.07</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>40334.22</v>
+        <v>1492</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>416.5</v>
+        <v>1415.4</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>413.67</v>
+        <v>1327.79</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>404.77</v>
+        <v>1274.58</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>399.65</v>
+        <v>1005.08</v>
       </c>
       <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>545.9</v>
+        <v>660.7</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>539.73</v>
+        <v>619.4</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>530.79</v>
+        <v>642.1900000000001</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>531.0700000000001</v>
+        <v>634.24</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>197.14</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>185.62</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>181.69</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>GAIL</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>173.9</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>173.29</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>172.76</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>287.31</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>284.68</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>278.53</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>369.35</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>302.35</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>1324.7</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1228.58</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1170.18</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>1082.26</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>499.9</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>498.41</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>494.41</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>445.32</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>657.7</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>654.72</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>656.98</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>621.4299999999999</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>MAHLIFE</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>362.73</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>366.14</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>362.3</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>978</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>835.95</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>722.22</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>582.22</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>EXIDEIND</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>435.85</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>428.3</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>430.29</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>397.53</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>4171.3</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>4170.25</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>4100.51</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>3794.45</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>548.15</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>541.12</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>531.72</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>532.99</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>3265.2</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>3217.31</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>3077.13</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>2695.97</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C34" s="14" t="n">
+        <v>3260</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>3216.82</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>3076.93</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>2697.23</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>VGUARD</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>330.15</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>329</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>323.37</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>324.91</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:VGUARD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1353.8</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>1318.57</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>1268.83</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>1002.28</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>191.72</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>187.75</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>185.03</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>181.58</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>1073.3</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>1045.14</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>976.28</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>976.46</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>11896</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>11790.21</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>11506.01</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>9852.639999999999</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>1780.1</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>1747.42</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>1757.46</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>1732.11</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>74.98</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>117.27</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>116.07</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>114.04</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>111.61</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>4535.4</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>4466.94</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>4355.23</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>3710.8</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>439.9</v>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>425.29</v>
+      </c>
+      <c r="E41" s="14" t="n">
+        <v>416.85</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="G41" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>892</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>888.95</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>888</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>829.77</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>32700</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>32032.97</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>32599.97</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>29278.79</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B44" s="17" t="inlineStr">
         <is>
           <t>IDFCFIRSTB</t>
         </is>
       </c>
-      <c r="C26" s="18" t="n">
-        <v>86.33</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>85.63</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>78.02</v>
-      </c>
-      <c r="G26" s="19">
+      <c r="C44" s="18" t="n">
+        <v>85.92</v>
+      </c>
+      <c r="D44" s="18" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="E44" s="18" t="n">
+        <v>83.81999999999999</v>
+      </c>
+      <c r="F44" s="18" t="n">
+        <v>78.11</v>
+      </c>
+      <c r="G44" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>116.47</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>115.95</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>113.91</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>111.56</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>429.2</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>423.75</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>415.91</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>356.71</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>418</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>415.9</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>415.35</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>415.14</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 18-Sep-2026  14:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-Sep-2026  16:58</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>13</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>0.65</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.55</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.65</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6167</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,22 +703,22 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>6</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
         <v>0.5333</v>
@@ -727,60 +727,60 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="F6" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
         <v>0.4</v>
@@ -789,63 +789,63 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.6</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.3997</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>9</v>
-      </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3557</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -882,187 +882,187 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>9</v>
-      </c>
       <c r="F11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.45</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.3</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F12" s="6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>0.25</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.2777</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.167</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2223</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.225</v>
+        <v>0.067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2083</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.175</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.1</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1943</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1557</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>27270</v>
+        <v>26960</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26215.27</v>
+        <v>26271.05</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26446.86</v>
+        <v>26448.73</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26847.09</v>
+        <v>26783.79</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3563.6</v>
+        <v>3542.1</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3534.75</v>
+        <v>3532.83</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3467.29</v>
+        <v>3473.94</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3105.23</v>
+        <v>3116.91</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>5466.5</v>
+        <v>1713.4</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5273.09</v>
+        <v>1670.27</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>5365.48</v>
+        <v>1626.37</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>5447.1</v>
+        <v>1446.03</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ALKEM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1734</v>
+        <v>9410.5</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1662.73</v>
+        <v>9163.91</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1620.01</v>
+        <v>8569.860000000001</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1441.81</v>
+        <v>7264.72</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>9375</v>
+        <v>2940.2</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>9137.959999999999</v>
+        <v>2894.32</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>8535.549999999999</v>
+        <v>2747.16</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>7244.84</v>
+        <v>2286.23</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2961.9</v>
+        <v>2450</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>2889.49</v>
+        <v>2414.16</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2739.28</v>
+        <v>2356.96</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2279.8</v>
+        <v>2216.21</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2447.4</v>
+        <v>875.15</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2410.39</v>
+        <v>867.33</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2353.17</v>
+        <v>849.83</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2221.26</v>
+        <v>738.8099999999999</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>875.5</v>
+        <v>2008.2</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>866.51</v>
+        <v>1950.19</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>848.8</v>
+        <v>1871.27</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>738.84</v>
+        <v>1657.62</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2009.6</v>
+        <v>2017.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1944.09</v>
+        <v>1914.28</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1865.68</v>
+        <v>1803.52</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>1649.34</v>
+        <v>1422.71</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1954</v>
+        <v>2437.8</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1898.65</v>
+        <v>2335.22</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1788.52</v>
+        <v>2379.6</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1413</v>
+        <v>2366.18</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,76 +1509,76 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>4970</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>4918.49</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>4881.54</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>4471.6</v>
+      </c>
+      <c r="G13" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
-        <v>1160</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1133.59</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>1125.6</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>1049.68</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="C14" s="14" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1136.2</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1126.99</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1049.81</v>
+      </c>
+      <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>ADANIENT</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>3020</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>2994.34</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>2992.01</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>2709.33</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
           <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>2270.1</v>
+        <v>2181.1</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>2154.44</v>
+        <v>2157.46</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>2062.45</v>
+        <v>2070.52</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1938.13</v>
+        <v>1941.21</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1597,16 +1597,16 @@
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>596</v>
+        <v>591.8</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>584.12</v>
+        <v>584.85</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>577.6</v>
+        <v>578.16</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>560.53</v>
+        <v>561.1900000000001</v>
       </c>
       <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>750.95</v>
+        <v>1130.6</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>737.36</v>
+        <v>1129.23</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>728.98</v>
+        <v>1122.61</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>736.9299999999999</v>
+        <v>1118.59</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>2859.1</v>
+        <v>751.45</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2673.64</v>
+        <v>737.8099999999999</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>2578.97</v>
+        <v>729.73</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>2484.89</v>
+        <v>738.99</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,722 +1677,666 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>2776.9</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>2687.25</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>2591.62</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>2484.66</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>2660.1</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>2458.48</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>2151.07</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>1492</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C20" s="18" t="n">
+        <v>2762.7</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2487.45</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2175.06</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1504.39</v>
+      </c>
+      <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1415.4</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>1327.79</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>1274.58</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>1005.08</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>ATGL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>660.7</v>
+        <v>660.25</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>619.4</v>
+        <v>655.28</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>642.1900000000001</v>
+        <v>653</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>634.24</v>
+        <v>645.52</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ATGL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>197.14</v>
+        <v>1821</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>188.7</v>
+        <v>1799.13</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>185.62</v>
+        <v>1808.81</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>181.69</v>
+        <v>1723.41</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>GAIL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>173.9</v>
+        <v>1929</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>173.29</v>
+        <v>1897.01</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>172.76</v>
+        <v>1910.5</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>168.7</v>
+        <v>1827.76</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>292.6</v>
+        <v>1084.95</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>287.31</v>
+        <v>859.66</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>284.68</v>
+        <v>736.45</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>278.53</v>
+        <v>586.73</v>
       </c>
       <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>369.35</v>
+        <v>47565</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>362.55</v>
+        <v>47553.46</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>346.15</v>
+        <v>45540.36</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>302.35</v>
+        <v>40454.85</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>1324.7</v>
+        <v>434.5</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1228.58</v>
+        <v>428.89</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>1170.18</v>
+        <v>430.45</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1082.26</v>
+        <v>396.18</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>499.9</v>
+        <v>5419</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>498.41</v>
+        <v>5354.8</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>494.41</v>
+        <v>5335.81</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>445.32</v>
+        <v>5254.6</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>657.7</v>
+        <v>162.91</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>654.72</v>
+        <v>162.72</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>656.98</v>
+        <v>158.85</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>621.4299999999999</v>
+        <v>139.07</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>366.4</v>
+        <v>1486</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>362.73</v>
+        <v>1342.86</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>366.14</v>
+        <v>1282.87</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>362.3</v>
+        <v>1008.86</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>978</v>
+        <v>193.5</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>835.95</v>
+        <v>189.16</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>722.22</v>
+        <v>185.93</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>582.22</v>
+        <v>181.75</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>EXIDEIND</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>435.85</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>428.3</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>430.29</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>397.53</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>287.33</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>284.79</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>278.32</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>4171.3</v>
+        <v>367.25</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>4170.25</v>
+        <v>363</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>4100.51</v>
+        <v>346.98</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>3794.45</v>
+        <v>302.94</v>
       </c>
       <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1349.3</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1240.07</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1177.2</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1083.32</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>660</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>655.4</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>657.08</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>621.9400000000001</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>413.68</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>405.46</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>399.47</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>LICHSGFIN</t>
         </is>
       </c>
-      <c r="C33" s="14" t="n">
-        <v>548.15</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>541.12</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>531.72</v>
-      </c>
-      <c r="F33" s="14" t="n">
+      <c r="C36" s="14" t="n">
+        <v>568</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>533.6799999999999</v>
+      </c>
+      <c r="F36" s="14" t="n">
         <v>532.99</v>
       </c>
-      <c r="G33" s="15">
+      <c r="G36" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>3260</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>3216.82</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>3076.93</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>2697.23</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>1073.3</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>1045.14</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>976.28</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>976.46</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>11896</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>11790.21</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>11506.01</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>9852.639999999999</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OFSS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C37" s="18" t="n">
-        <v>1780.1</v>
+        <v>4480</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>1747.42</v>
+        <v>4468.18</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>1757.46</v>
+        <v>4360.12</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>1732.11</v>
+        <v>3719.82</v>
       </c>
       <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="12" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1060.8</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1048.33</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>982.91</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>973.77</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>83.54000000000001</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>82.69</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>82.18000000000001</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>74.98</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C39" s="14" t="n">
-        <v>117.27</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>116.07</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>114.04</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>111.61</v>
-      </c>
-      <c r="G39" s="15">
+      <c r="C39" s="18" t="n">
+        <v>118</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>116.26</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>111.77</v>
+      </c>
+      <c r="G39" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>4535.4</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>4466.94</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>4355.23</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>3710.8</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>433.4</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>426.06</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>417.5</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>358.71</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>439.9</v>
+        <v>910</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>425.29</v>
+        <v>890.95</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>416.85</v>
+        <v>888.86</v>
       </c>
       <c r="F41" s="14" t="n">
-        <v>357.55</v>
+        <v>829.41</v>
       </c>
       <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>892</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>888.95</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>888</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>829.77</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>POWERINDIA</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>32700</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>32032.97</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>32599.97</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>29278.79</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:POWERINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A42" s="8" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>IDFCFIRSTB</t>
         </is>
       </c>
-      <c r="C44" s="18" t="n">
-        <v>85.92</v>
-      </c>
-      <c r="D44" s="18" t="n">
-        <v>85.65000000000001</v>
-      </c>
-      <c r="E44" s="18" t="n">
-        <v>83.81999999999999</v>
-      </c>
-      <c r="F44" s="18" t="n">
-        <v>78.11</v>
-      </c>
-      <c r="G44" s="19">
+      <c r="C42" s="18" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>85.67</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="G42" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-Sep-2026  16:58</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Sep-2026  15:35</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>13</v>
@@ -681,7 +681,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.65</v>
@@ -690,7 +690,7 @@
         <v>0.65</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6667000000000001</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,25 +703,25 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.467</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -737,19 +737,19 @@
         <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.5</v>
@@ -758,122 +758,122 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="F7" s="10" t="n">
-        <v>0.267</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>0.4</v>
       </c>
-      <c r="H7" s="10" t="n">
-        <v>0.5329999999999999</v>
-      </c>
       <c r="I7" s="11" t="n">
-        <v>0.4</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="F8" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>0.5329999999999999</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.333</v>
-      </c>
       <c r="I8" s="7" t="n">
-        <v>0.3997</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.3</v>
@@ -882,63 +882,63 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2887</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="F12" s="6" t="n">
-        <v>0.1</v>
+        <v>0.333</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.45</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -975,94 +975,94 @@
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.275</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1583</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="F15" s="10" t="n">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.175</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.067</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1663</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>26960</v>
+        <v>27225</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26271.05</v>
+        <v>26361.9</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26448.73</v>
+        <v>26479.17</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26783.79</v>
+        <v>26788.18</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3542.1</v>
+        <v>1700</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3532.83</v>
+        <v>1673.1</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3473.94</v>
+        <v>1629.26</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3116.91</v>
+        <v>1448.56</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1713.4</v>
+        <v>9352</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1670.27</v>
+        <v>9181.83</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1626.37</v>
+        <v>8600.540000000001</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1446.03</v>
+        <v>7285.49</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>9410.5</v>
+        <v>2916.6</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>9163.91</v>
+        <v>2896.44</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8569.860000000001</v>
+        <v>2753.8</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7264.72</v>
+        <v>2292.5</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2940.2</v>
+        <v>2461.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2894.32</v>
+        <v>2418.66</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2747.16</v>
+        <v>2361.06</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2286.23</v>
+        <v>2218.65</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2450</v>
+        <v>1992.4</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>2414.16</v>
+        <v>1954.21</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2356.96</v>
+        <v>1876.02</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2216.21</v>
+        <v>1660.95</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>875.15</v>
+        <v>2006.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>867.33</v>
+        <v>1923.06</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>849.83</v>
+        <v>1811.48</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>738.8099999999999</v>
+        <v>1428.51</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2008.2</v>
+        <v>2480</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1950.19</v>
+        <v>2349</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1871.27</v>
+        <v>2383.54</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1657.62</v>
+        <v>2367.32</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2017.5</v>
+        <v>4935</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1914.28</v>
+        <v>4920.06</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1803.52</v>
+        <v>4883.64</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>1422.71</v>
+        <v>4476.21</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,107 +1481,107 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2437.8</v>
+        <v>1162.3</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2335.22</v>
+        <v>1138.69</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2379.6</v>
+        <v>1128.37</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2366.18</v>
+        <v>1050.93</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>4970</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>4918.49</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>4881.54</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>4471.6</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>2997</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>2992.93</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>2991.57</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>2733</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1161</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1136.2</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>1126.99</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1049.81</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>2161.04</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>2075.4</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>1943.74</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>2181.1</v>
+        <v>590.5</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>2157.46</v>
+        <v>585.39</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>2070.52</v>
+        <v>578.64</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1941.21</v>
+        <v>561.48</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>591.8</v>
+        <v>1141</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>584.85</v>
+        <v>1130.35</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>578.16</v>
+        <v>1123.33</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>561.1900000000001</v>
+        <v>1118.81</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>1130.6</v>
+        <v>743.45</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1129.23</v>
+        <v>738.35</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1122.61</v>
+        <v>730.27</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1118.59</v>
+        <v>739.03</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,23 +1649,23 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>751.45</v>
+        <v>2781.7</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>737.8099999999999</v>
+        <v>2696.25</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>729.73</v>
+        <v>2599.07</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>738.99</v>
+        <v>2487.61</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,79 +1677,79 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2776.9</v>
+        <v>2731.5</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2687.25</v>
+        <v>2510.69</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2591.62</v>
+        <v>2196.88</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>2484.66</v>
+        <v>1516.6</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>2762.7</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>2487.45</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>2175.06</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1504.39</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>669.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>656.63</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>653.65</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>645.76</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>660.25</v>
+        <v>1845.6</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>655.28</v>
+        <v>1803.56</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>653</v>
+        <v>1810.26</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>645.52</v>
+        <v>1724.62</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,23 +1761,23 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1821</v>
+        <v>1953.4</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>1799.13</v>
+        <v>1902.38</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>1808.81</v>
+        <v>1912.19</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>1723.41</v>
+        <v>1829.01</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1789,555 +1789,443 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>1929</v>
+        <v>1116.95</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>1897.01</v>
+        <v>884.17</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>1910.5</v>
+        <v>751.37</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1827.76</v>
+        <v>592.01</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1084.95</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>859.66</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>736.45</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>586.73</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>370.45</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>363.71</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>347.9</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>303.62</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>47565</v>
+        <v>1334.8</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>47553.46</v>
+        <v>1249.1</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>45540.36</v>
+        <v>1183.38</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>40454.85</v>
+        <v>1085.82</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C26" s="18" t="n">
-        <v>434.5</v>
+        <v>503.35</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>428.89</v>
+        <v>497.36</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>430.45</v>
+        <v>494.35</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>396.18</v>
+        <v>446.12</v>
       </c>
       <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:EXIDEIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>661.8</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>656.01</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>657.27</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>622.34</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>48290</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>47623.61</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>45648.19</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>40532.81</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>HEROMOTOCO</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n">
-        <v>5419</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>5354.8</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>5335.81</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>5254.6</v>
-      </c>
-      <c r="G27" s="19">
+      <c r="C29" s="14" t="n">
+        <v>5373</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>5356.53</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>5337.27</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>5255.78</v>
+      </c>
+      <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>162.91</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>162.72</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>158.85</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>139.07</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="C29" s="14" t="n">
-        <v>1486</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>1342.86</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>1282.87</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>1008.86</v>
-      </c>
-      <c r="G29" s="15">
+      <c r="C30" s="18" t="n">
+        <v>1424.5</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1350.63</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1288.42</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1013</v>
+      </c>
+      <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>189.16</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>185.93</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>181.75</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="C31" s="18" t="n">
+        <v>195.61</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>189.77</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>186.31</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>181.89</v>
+      </c>
+      <c r="G31" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>287.33</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>284.79</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>278.32</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>367.25</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>363</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>346.98</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>302.94</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1079</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1051.25</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>986.6799999999999</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>974.8200000000001</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C33" s="18" t="n">
-        <v>1349.3</v>
+        <v>565</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>1240.07</v>
+        <v>546.1</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>1177.2</v>
+        <v>534.91</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>1083.32</v>
+        <v>533.3099999999999</v>
       </c>
       <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>660</v>
+        <v>3262.6</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>655.4</v>
+        <v>3224.24</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>657.08</v>
+        <v>3095.99</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>621.9400000000001</v>
+        <v>2713.27</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>414.8</v>
+        <v>830</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>413.68</v>
+        <v>820.38</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>405.46</v>
+        <v>829.46</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>399.47</v>
+        <v>799.9</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>568</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>544.11</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>533.6799999999999</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>532.99</v>
-      </c>
-      <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>117</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>116.33</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>114.31</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>111.82</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>4480</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>4468.18</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>4360.12</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>3719.82</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>896.1</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>891.4400000000001</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>889.15</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>830.0700000000001</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>1060.8</v>
+        <v>428</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>1048.33</v>
+        <v>416.48</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>982.91</v>
+        <v>415.62</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>973.77</v>
+        <v>414.84</v>
       </c>
       <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>118</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>116.26</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>111.77</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>433.4</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>426.06</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>417.5</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>358.71</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>910</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>890.95</v>
-      </c>
-      <c r="E41" s="14" t="n">
-        <v>888.86</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>829.41</v>
-      </c>
-      <c r="G41" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>83.90000000000001</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Sep-2026  15:35</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 23-Sep-2026  15:28</t>
         </is>
       </c>
     </row>
@@ -665,63 +665,63 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.867</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.667</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.867</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.65</v>
+        <v>0.8003</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.467</v>
+        <v>0.7</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.467</v>
+        <v>0.7</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.8</v>
+        <v>0.65</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.578</v>
+        <v>0.6833</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -789,38 +789,38 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.467</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3557</v>
+        <v>0.4443</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>5</v>
@@ -839,137 +839,137 @@
         <v>0.467</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3557</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>8</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2833</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.167</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,87 +982,87 @@
         <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.125</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.275</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1583</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1387</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1663</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.1</v>
+        <v>0.0333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,1008 +1224,1372 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>27225</v>
+        <v>2993.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26361.9</v>
+        <v>2992.96</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26479.17</v>
+        <v>2991.64</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26788.18</v>
+        <v>2739.36</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1700</v>
+        <v>2195</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1673.1</v>
+        <v>2164.27</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1629.26</v>
+        <v>2080.09</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1448.56</v>
+        <v>1946.53</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9352</v>
+        <v>595.45</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9181.83</v>
+        <v>586.35</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>8600.540000000001</v>
+        <v>579.3</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7285.49</v>
+        <v>562</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2916.6</v>
+        <v>1175.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2896.44</v>
+        <v>1134.63</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>2753.8</v>
+        <v>1125.37</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2292.5</v>
+        <v>1121.81</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2461.4</v>
+        <v>758.55</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2418.66</v>
+        <v>740.27</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2361.06</v>
+        <v>731.38</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2218.65</v>
+        <v>740.3</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1992.4</v>
+        <v>1297.8</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1954.21</v>
+        <v>1281.93</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1876.02</v>
+        <v>1280.76</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1660.95</v>
+        <v>1238.31</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2006.5</v>
+        <v>2800.8</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1923.06</v>
+        <v>2714.05</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1811.48</v>
+        <v>2614.52</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1428.51</v>
+        <v>2496.69</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2480</v>
+        <v>185.44</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2349</v>
+        <v>180.83</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2383.54</v>
+        <v>179.31</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2367.32</v>
+        <v>168.74</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>4935</v>
+        <v>190.82</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>4920.06</v>
+        <v>185.71</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>4883.64</v>
+        <v>187.13</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>4476.21</v>
+        <v>188.41</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>1162.3</v>
+        <v>2796.8</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1138.69</v>
+        <v>2537.94</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>1128.37</v>
+        <v>2220.4</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1050.93</v>
+        <v>1528.6</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>2997</v>
+        <v>26935</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>2992.93</v>
+        <v>26416.48</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>2991.57</v>
+        <v>26497.05</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2733</v>
+        <v>26792.03</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>2195</v>
+        <v>3568.1</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>2161.04</v>
+        <v>3535.03</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>2075.4</v>
+        <v>3479.34</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1943.74</v>
+        <v>3125.82</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>590.5</v>
+        <v>1721.5</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>585.39</v>
+        <v>1677.71</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>578.64</v>
+        <v>1632.88</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>561.48</v>
+        <v>1450.66</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>1141</v>
+        <v>9624</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1130.35</v>
+        <v>9223.940000000001</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1123.33</v>
+        <v>8640.67</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1118.81</v>
+        <v>7305.4</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>743.45</v>
+        <v>2910.2</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>738.35</v>
+        <v>2897.75</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>730.27</v>
+        <v>2759.93</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>739.03</v>
+        <v>2298.84</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>2781.7</v>
+        <v>2475</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2696.25</v>
+        <v>2424.02</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>2599.07</v>
+        <v>2365.53</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>2487.61</v>
+        <v>2221.12</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2731.5</v>
+        <v>1962.6</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2510.69</v>
+        <v>1955.01</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2196.88</v>
+        <v>1879.42</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1516.6</v>
+        <v>1663.62</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2034</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>1933.63</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1820.21</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1435.04</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>2465</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2360.05</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2386.73</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>2365.8</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>4985</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>4926.24</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>4887.62</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>4480.92</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1170.1</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1141.68</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1130.01</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1052.85</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
-        <v>669.5</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>656.63</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>653.65</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>645.76</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C24" s="14" t="n">
+        <v>675</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>658.38</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>654.48</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>644.91</v>
+      </c>
+      <c r="G24" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1162.5</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>1160.63</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1158.26</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1077.73</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LODHA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>OBEROIRLTY</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
-        <v>1845.6</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1803.56</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1810.26</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1724.62</v>
-      </c>
-      <c r="G21" s="15">
+      <c r="C26" s="14" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>1807.98</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1811.81</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1725.23</v>
+      </c>
+      <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>1953.4</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1902.38</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1912.19</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1829.01</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C27" s="14" t="n">
+        <v>1993.2</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1911.03</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1915.36</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1829.68</v>
+      </c>
+      <c r="G27" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
-        <v>1116.95</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>884.17</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>751.37</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>592.01</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="C28" s="14" t="n">
+        <v>1114.65</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>906.12</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>765.62</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>597.7</v>
+      </c>
+      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>370.45</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>363.71</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>347.9</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>303.62</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C29" s="18" t="n">
+        <v>372.7</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>348.87</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>304.3</v>
+      </c>
+      <c r="G29" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>PVRINOX</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>1334.8</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>1249.1</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>1183.38</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>1085.82</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C30" s="18" t="n">
+        <v>1317.5</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>1255.61</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>1188.64</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>1088.71</v>
+      </c>
+      <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>503.35</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>497.36</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>494.35</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>446.12</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>661.8</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>656.01</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>657.27</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>622.34</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>48290</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>47623.61</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>45648.19</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>40532.81</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>5373</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>5356.53</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>5337.27</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>5255.78</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>1424.5</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>1350.63</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>1288.42</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>1013</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>507</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>498.28</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>494.85</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>446.52</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>670.5</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>657.39</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>657.79</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>622.03</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1404.5</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1355.76</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1292.98</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1017.67</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n">
-        <v>195.61</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>189.77</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>186.31</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>181.89</v>
-      </c>
-      <c r="G31" s="19">
+      <c r="C34" s="14" t="n">
+        <v>193.23</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>190.1</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>186.58</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>182.03</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>832.3</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>821.52</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>829.5700000000001</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>799.35</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>4601.9</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>4479.25</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>4372.94</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>3730.1</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>1441</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>1428.92</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>1439.77</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>1383.83</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>47955</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>47655.17</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>45738.65</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>40591.99</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>5394</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>5360.1</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>5339.49</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>5252.57</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>164.4</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>159.18</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>139.71</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>82.26000000000001</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>118.3</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>116.51</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="F42" s="18" t="n">
+        <v>111.91</v>
+      </c>
+      <c r="G42" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>548.61</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>536.38</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>533.33</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>3374</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>3238.5</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>3106.9</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>2720.63</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>CYIENT</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
-        <v>1079</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1051.25</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>986.6799999999999</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>974.8200000000001</v>
-      </c>
-      <c r="G32" s="15">
+      <c r="C45" s="18" t="n">
+        <v>1072.2</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>1053.25</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>990.04</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>976.01</v>
+      </c>
+      <c r="G45" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>565</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>546.1</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>534.91</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>533.3099999999999</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>3262.6</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>3224.24</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>3095.99</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>2713.27</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>830</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>820.38</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>829.46</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>799.9</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>117</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>116.33</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>114.31</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>111.82</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="G46" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>CGPOWER</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
-        <v>896.1</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>891.4400000000001</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>889.15</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>830.0700000000001</v>
-      </c>
-      <c r="G37" s="15">
+      <c r="C47" s="14" t="n">
+        <v>895</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>891.78</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>889.38</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>830.98</v>
+      </c>
+      <c r="G47" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C38" s="14" t="n">
-        <v>428</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>416.48</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>415.62</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>414.84</v>
-      </c>
-      <c r="G38" s="15">
+      <c r="C48" s="14" t="n">
+        <v>424.55</v>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>415.97</v>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>414.89</v>
+      </c>
+      <c r="G48" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="n">
+        <v>4417</v>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>4386.52</v>
+      </c>
+      <c r="E49" s="14" t="n">
+        <v>4402.75</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>4108.62</v>
+      </c>
+      <c r="G49" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="n">
+        <v>1216.4</v>
+      </c>
+      <c r="D50" s="18" t="n">
+        <v>1213.86</v>
+      </c>
+      <c r="E50" s="18" t="n">
+        <v>1205.39</v>
+      </c>
+      <c r="F50" s="18" t="n">
+        <v>1140.62</v>
+      </c>
+      <c r="G50" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>85.84999999999999</v>
+      </c>
+      <c r="E51" s="14" t="n">
+        <v>84.11</v>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>78.23999999999999</v>
+      </c>
+      <c r="G51" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 23-Sep-2026  15:28</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 24-Sep-2026  15:54</t>
         </is>
       </c>
     </row>
@@ -665,63 +665,63 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>13</v>
-      </c>
-      <c r="D4" s="5" t="n">
-        <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.7</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.667</v>
+        <v>0.65</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.867</v>
+        <v>0.65</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.8003</v>
+        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.7</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.7</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.65</v>
+        <v>0.733</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.6833</v>
+        <v>0.5997</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.6</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>5</v>
@@ -774,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.5</v>
@@ -783,7 +783,7 @@
         <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,242 +796,242 @@
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4443</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.467</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3777</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="F10" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.5329999999999999</v>
-      </c>
       <c r="I10" s="7" t="n">
-        <v>0.3557</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.467</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.333</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2833</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="F13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>0.35</v>
-      </c>
       <c r="I13" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.125</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.275</v>
+        <v>0.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.025</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.025</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.275</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,25 +1044,25 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1663</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,1372 +1224,952 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>2993.2</v>
+        <v>26860</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>2992.96</v>
+        <v>26458.72</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>2991.64</v>
+        <v>26511.28</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>2739.36</v>
+        <v>26790.32</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>2195</v>
+        <v>3539.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2164.27</v>
+        <v>3535.45</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2080.09</v>
+        <v>3481.7</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1946.53</v>
+        <v>3128.84</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>595.45</v>
+        <v>1716</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>586.35</v>
+        <v>1681.36</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>579.3</v>
+        <v>1636.14</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>562</v>
+        <v>1451.76</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1175.3</v>
+        <v>9602</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1134.63</v>
+        <v>9259.940000000001</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1125.37</v>
+        <v>8678.370000000001</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1121.81</v>
+        <v>7322.83</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>758.55</v>
+        <v>2430.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>740.27</v>
+        <v>2424.63</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>731.38</v>
+        <v>2368.07</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>740.3</v>
+        <v>2223.35</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1297.8</v>
+        <v>1997.1</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1281.93</v>
+        <v>1959.02</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1280.76</v>
+        <v>1884.03</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1238.31</v>
+        <v>1663.15</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2800.8</v>
+        <v>2026.2</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>2714.05</v>
+        <v>1942.44</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>2614.52</v>
+        <v>1828.29</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>2496.69</v>
+        <v>1440.9</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>185.44</v>
+        <v>2500</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>180.83</v>
+        <v>2373.38</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>179.31</v>
+        <v>2391.17</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>168.74</v>
+        <v>2364.32</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>190.82</v>
+        <v>4928.5</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>185.71</v>
+        <v>4926.46</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>187.13</v>
+        <v>4889.22</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>188.41</v>
+        <v>4482.44</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATASTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2796.8</v>
+        <v>1180.3</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2537.94</v>
+        <v>1145.36</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2220.4</v>
+        <v>1131.98</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>1528.6</v>
+        <v>1053.41</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>26935</v>
+        <v>2184.8</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>26416.48</v>
+        <v>2166.23</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>26497.05</v>
+        <v>2084.2</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>26792.03</v>
+        <v>1948.36</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>3568.1</v>
+        <v>587.15</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>3535.03</v>
+        <v>586.42</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>3479.34</v>
+        <v>579.61</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>3125.82</v>
+        <v>561.5700000000001</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1721.5</v>
+        <v>1157.8</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1677.71</v>
+        <v>1136.84</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1632.88</v>
+        <v>1126.64</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1450.66</v>
+        <v>1121.36</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>9624</v>
+        <v>2824.2</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>9223.940000000001</v>
+        <v>2724.54</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>8640.67</v>
+        <v>2622.74</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>7305.4</v>
+        <v>2500.61</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2910.2</v>
+        <v>184</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>2897.75</v>
+        <v>181.13</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>2759.93</v>
+        <v>179.49</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>2298.84</v>
+        <v>168.81</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>2475</v>
+        <v>2692.2</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>2424.02</v>
+        <v>2552.63</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>2365.53</v>
+        <v>2238.91</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>2221.12</v>
+        <v>1539.9</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>1962.6</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>1955.01</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>1879.42</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>1663.62</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>670.4</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>659.53</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>655.11</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>643.11</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>2034</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1933.63</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1820.21</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1435.04</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1837.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1810.79</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1812.82</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1722.64</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>2465</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>2360.05</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>2386.73</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>2365.8</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1915.22</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1916.91</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1826.92</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>4985</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>4926.24</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>4887.62</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>4480.92</v>
-      </c>
-      <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1203.85</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>934.47</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>782.8</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>603.26</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1170.1</v>
+        <v>374.55</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1141.68</v>
+        <v>365.52</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1130.01</v>
+        <v>349.88</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1052.85</v>
+        <v>305.29</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>675</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>658.38</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>654.48</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>644.91</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>1256.7</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1255.71</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1191.31</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1090.28</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>LODHA</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>1162.5</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>1160.63</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>1158.26</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>1077.73</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LODHA","Chart 📈")</f>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>662.05</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>657.83</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>657.95</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>622.01</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1850</v>
+        <v>1369.7</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>1807.98</v>
+        <v>1357.09</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>1811.81</v>
+        <v>1295.98</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>1725.23</v>
+        <v>1019.57</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>1993.2</v>
+        <v>194.8</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>1911.03</v>
+        <v>190.55</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>1915.36</v>
+        <v>186.91</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>1829.68</v>
+        <v>182.13</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>GAIL</t>
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>1114.65</v>
+        <v>173.85</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>906.12</v>
+        <v>173.15</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>765.62</v>
+        <v>172.77</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>597.7</v>
+        <v>168.47</v>
       </c>
       <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C29" s="18" t="n">
-        <v>372.7</v>
+        <v>117.12</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>364.56</v>
+        <v>116.57</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>348.87</v>
+        <v>114.57</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>304.3</v>
+        <v>111.78</v>
       </c>
       <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>1317.5</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>1255.61</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>1188.64</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>1088.71</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>4481.3</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>4479.44</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>4377.19</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>3738.53</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>507</v>
+        <v>47750</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>498.28</v>
+        <v>47664.2</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>494.85</v>
+        <v>45817.49</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>446.52</v>
+        <v>40611.84</v>
       </c>
       <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>657.39</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>657.79</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>622.03</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1221.8</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1214.61</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1206.04</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1143.84</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>1404.5</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>1355.76</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1292.98</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>1017.67</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>564.25</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>550.1</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>537.48</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>533.49</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>193.23</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>186.58</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>182.03</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>3427.7</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>3256.52</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>3119.48</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>2726.34</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>832.3</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>821.52</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>829.5700000000001</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>799.35</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1057.8</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>1054.64</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>995.4</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>976.3099999999999</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>4601.9</v>
+        <v>422</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>4479.25</v>
+        <v>417.7</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>4372.94</v>
+        <v>416.21</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>3730.1</v>
+        <v>414.87</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>1441</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>1428.92</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>1439.77</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>1383.83</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNITDSPR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>47955</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>47655.17</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>45738.65</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>40591.99</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>5394</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>5360.1</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>5339.49</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>5252.57</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>164.4</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>159.18</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>139.71</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>84.11</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>82.76000000000001</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>82.26000000000001</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n">
-        <v>118.3</v>
-      </c>
-      <c r="D42" s="18" t="n">
-        <v>116.51</v>
-      </c>
-      <c r="E42" s="18" t="n">
-        <v>114.47</v>
-      </c>
-      <c r="F42" s="18" t="n">
-        <v>111.91</v>
-      </c>
-      <c r="G42" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>572.5</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>548.61</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>536.38</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>533.33</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>3374</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>3238.5</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>3106.9</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>2720.63</v>
-      </c>
-      <c r="G44" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>1072.2</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>1053.25</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>990.04</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>976.01</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>IDEA</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>14.52</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>14.15</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>12.48</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDEA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>895</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>891.78</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>889.38</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>830.98</v>
-      </c>
-      <c r="G47" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B48" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C48" s="14" t="n">
-        <v>424.55</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>417.25</v>
-      </c>
-      <c r="E48" s="14" t="n">
-        <v>415.97</v>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>414.89</v>
-      </c>
-      <c r="G48" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>GVT&amp;D</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="n">
-        <v>4417</v>
-      </c>
-      <c r="D49" s="14" t="n">
-        <v>4386.52</v>
-      </c>
-      <c r="E49" s="14" t="n">
-        <v>4402.75</v>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>4108.62</v>
-      </c>
-      <c r="G49" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GVT&amp;D","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n">
-        <v>1216.4</v>
-      </c>
-      <c r="D50" s="18" t="n">
-        <v>1213.86</v>
-      </c>
-      <c r="E50" s="18" t="n">
-        <v>1205.39</v>
-      </c>
-      <c r="F50" s="18" t="n">
-        <v>1140.62</v>
-      </c>
-      <c r="G50" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="D51" s="14" t="n">
-        <v>85.84999999999999</v>
-      </c>
-      <c r="E51" s="14" t="n">
-        <v>84.11</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>78.23999999999999</v>
-      </c>
-      <c r="G51" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IDFCFIRSTB","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 24-Sep-2026  15:54</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 25-Sep-2026  15:54</t>
         </is>
       </c>
     </row>
@@ -734,25 +734,25 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,7 +765,7 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>5</v>
@@ -774,7 +774,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.5</v>
@@ -783,144 +783,144 @@
         <v>0.4</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="6" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>0.267</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>0.4</v>
-      </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.467</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3557</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2887</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F10" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>0.333</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.267</v>
-      </c>
       <c r="I10" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.467</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2443</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3</v>
@@ -929,7 +929,7 @@
         <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.2</v>
@@ -938,7 +938,7 @@
         <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -954,7 +954,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>4</v>
@@ -963,13 +963,13 @@
         <v>0.25</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1833</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>6</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.15</v>
@@ -1000,7 +1000,7 @@
         <v>0.3</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1833</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,25 +1013,25 @@
         <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>11</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.025</v>
+        <v>0.075</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.275</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1083</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>26860</v>
+        <v>26955</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26458.72</v>
+        <v>26505.99</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26511.28</v>
+        <v>26528.68</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26790.32</v>
+        <v>26791.96</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3539.5</v>
+        <v>3547.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3535.45</v>
+        <v>3536.63</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3481.7</v>
+        <v>3484.29</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3128.84</v>
+        <v>3129.68</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1681.36</v>
+        <v>1684.27</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1636.14</v>
+        <v>1639.11</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1451.76</v>
+        <v>1454.84</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>9602</v>
+        <v>9619.5</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>9259.940000000001</v>
+        <v>9294.190000000001</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8678.370000000001</v>
+        <v>8715.27</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7322.83</v>
+        <v>7338.64</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2430.4</v>
+        <v>2917.2</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2424.63</v>
+        <v>2899.58</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2368.07</v>
+        <v>2771.28</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2223.35</v>
+        <v>2307.34</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>1997.1</v>
+        <v>868.65</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>1959.02</v>
+        <v>865.4400000000001</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>1884.03</v>
+        <v>851.5599999999999</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>1663.15</v>
+        <v>743.9400000000001</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>2026.2</v>
+        <v>1970.8</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1942.44</v>
+        <v>1960.14</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1828.29</v>
+        <v>1887.43</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1440.9</v>
+        <v>1666.38</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2500</v>
+        <v>2007</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2373.38</v>
+        <v>1948.59</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2391.17</v>
+        <v>1835.29</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>2364.32</v>
+        <v>1445.46</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>4928.5</v>
+        <v>2474.9</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>4926.46</v>
+        <v>2383.05</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>4889.22</v>
+        <v>2394.45</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>4482.44</v>
+        <v>2365.14</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,79 +1481,79 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>4988.5</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>4932.37</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>4893.11</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>4480.85</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>1180.3</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>1145.36</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>1131.98</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>1053.41</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="C13" s="14" t="n">
+        <v>1203.9</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1150.93</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>1134.8</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1053.56</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>APLAPOLLO</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>2184.8</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>2166.23</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>2084.2</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>1948.36</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="C14" s="18" t="n">
+        <v>2214.7</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>2170.84</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>2089.32</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>1951.98</v>
+      </c>
+      <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>HINDZINC</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>587.15</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>586.42</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>579.61</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>561.5700000000001</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1157.8</v>
+        <v>588.95</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1136.84</v>
+        <v>586.66</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1126.64</v>
+        <v>579.97</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1121.36</v>
+        <v>562.9299999999999</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>2824.2</v>
+        <v>1164.8</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>2724.54</v>
+        <v>1139.5</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>2622.74</v>
+        <v>1128.14</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>2500.61</v>
+        <v>1121.71</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,23 +1621,23 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>184</v>
+        <v>748.25</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>181.13</v>
+        <v>740.92</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>179.49</v>
+        <v>732.3200000000001</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>168.81</v>
+        <v>739.05</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1649,107 +1649,107 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
+          <t>RATNAMANI</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2778.3</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>2729.66</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>2628.85</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>2506.73</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>185</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>179.71</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>168.99</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>2692.2</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>2552.63</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>2238.91</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1539.9</v>
-      </c>
-      <c r="G18" s="19">
+      <c r="C20" s="18" t="n">
+        <v>2832.4</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2579.28</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2262.18</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1552.22</v>
+      </c>
+      <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>670.4</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>659.53</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>655.11</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>643.11</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C21" s="14" t="n">
+        <v>683</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>661.76</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>656.2</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>642.51</v>
+      </c>
+      <c r="G21" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1837.5</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>1810.79</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>1812.82</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>1722.64</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1955</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1915.22</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1916.91</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1826.92</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,414 +1761,610 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
+          <t>LODHA</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1160.82</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1158.51</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1074.92</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LODHA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1858.5</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>1815.34</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1814.61</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1722.36</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1978.4</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>1921.24</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1919.32</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>1827.2</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>1203.85</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>934.47</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>782.8</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>603.26</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C25" s="14" t="n">
+        <v>1196.65</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>959.4400000000001</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>799.03</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>608.96</v>
+      </c>
+      <c r="G25" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n">
-        <v>374.55</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>365.52</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>349.88</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>305.29</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="C26" s="18" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>366.56</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>350.92</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>305.94</v>
+      </c>
+      <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>1256.7</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1255.71</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1191.31</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1090.28</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B27" s="17" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>662.05</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>657.83</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>657.95</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>622.01</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C27" s="18" t="n">
+        <v>668.95</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>658.89</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>658.38</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>623.24</v>
+      </c>
+      <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>48250</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>47719.99</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>45912.88</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>40668.67</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>5360</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>5354.57</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>5338.66</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>5252.89</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>165.71</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>163.05</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>159.56</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>139.66</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>4157.3</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>4156.34</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>4106.81</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>3800.14</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>1218.1</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>1214.95</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>1206.51</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>1143.03</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>792.66</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>790.96</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>870.72</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>1369.7</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1357.09</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1295.98</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1019.57</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C34" s="14" t="n">
+        <v>1365.4</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1357.88</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1298.71</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1023.95</v>
+      </c>
+      <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B35" s="13" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C27" s="14" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>190.55</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>186.91</v>
-      </c>
-      <c r="F27" s="14" t="n">
+      <c r="C35" s="14" t="n">
+        <v>201.67</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>191.61</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>187.48</v>
+      </c>
+      <c r="F35" s="14" t="n">
         <v>182.13</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G35" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>GAIL</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>173.85</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>173.15</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>172.77</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>168.47</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GAIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>117.12</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>116.57</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>114.57</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>111.78</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>4481.3</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>4479.44</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>4377.19</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>3738.53</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>47750</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>47664.2</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>45817.49</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>40611.84</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1221.8</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1214.61</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1206.04</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>1143.84</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>564.25</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>550.1</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>537.48</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>533.49</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>3427.7</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>3256.52</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>3119.48</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>2726.34</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>1057.8</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>1054.64</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>995.4</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>976.3099999999999</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>75.23</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>116.58</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>111.86</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>685.8</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>676.4299999999999</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>653.99</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>564.77</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>4557.1</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>4486.84</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>4384.24</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>3746.15</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>566</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>551.61</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>538.59</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>533.08</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>3324.9</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>3263.03</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>3127.53</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>2733.38</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1094.7</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>1058.46</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>999.29</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>976.65</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B43" s="17" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C36" s="18" t="n">
-        <v>422</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>417.7</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>416.21</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>414.87</v>
-      </c>
-      <c r="G36" s="19">
+      <c r="C43" s="18" t="n">
+        <v>426.1</v>
+      </c>
+      <c r="D43" s="18" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="E43" s="18" t="n">
+        <v>416.6</v>
+      </c>
+      <c r="F43" s="18" t="n">
+        <v>414.95</v>
+      </c>
+      <c r="G43" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 25-Sep-2026  15:54</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Sep-2026  18:35</t>
         </is>
       </c>
     </row>
@@ -1239,10 +1239,10 @@
         <v>26505.99</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26528.68</v>
+        <v>26528.66</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26791.96</v>
+        <v>26749.39</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1270,7 +1270,7 @@
         <v>3484.29</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3129.68</v>
+        <v>3124.45</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1298,7 +1298,7 @@
         <v>1639.11</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1454.84</v>
+        <v>1454.23</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1323,10 +1323,10 @@
         <v>9294.190000000001</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8715.27</v>
+        <v>8715.26</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7338.64</v>
+        <v>7322.34</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1354,7 +1354,7 @@
         <v>2771.28</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2307.34</v>
+        <v>2309.42</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1382,7 +1382,7 @@
         <v>851.5599999999999</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>743.9400000000001</v>
+        <v>742.66</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
@@ -1410,7 +1410,7 @@
         <v>1887.43</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1666.38</v>
+        <v>1663.59</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
@@ -1438,7 +1438,7 @@
         <v>1835.29</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1445.46</v>
+        <v>1440.97</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1466,7 +1466,7 @@
         <v>2394.45</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2365.14</v>
+        <v>2359.85</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1494,7 +1494,7 @@
         <v>4893.11</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>4480.85</v>
+        <v>4485.3</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
@@ -1522,7 +1522,7 @@
         <v>1134.8</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1053.56</v>
+        <v>1051.37</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
@@ -1550,7 +1550,7 @@
         <v>2089.32</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1951.98</v>
+        <v>1952.63</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1578,7 +1578,7 @@
         <v>579.97</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>562.9299999999999</v>
+        <v>562.9</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
@@ -1606,7 +1606,7 @@
         <v>1128.14</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1121.71</v>
+        <v>1121.05</v>
       </c>
       <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
@@ -1634,7 +1634,7 @@
         <v>732.3200000000001</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>739.05</v>
+        <v>735.23</v>
       </c>
       <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
@@ -1659,10 +1659,10 @@
         <v>2729.66</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>2628.85</v>
+        <v>2628.84</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>2506.73</v>
+        <v>2499.49</v>
       </c>
       <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
@@ -1690,7 +1690,7 @@
         <v>179.71</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>168.99</v>
+        <v>168.6</v>
       </c>
       <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
@@ -1718,7 +1718,7 @@
         <v>2262.18</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1552.22</v>
+        <v>1550.03</v>
       </c>
       <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1746,7 +1746,7 @@
         <v>656.2</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>642.51</v>
+        <v>642.6</v>
       </c>
       <c r="G21" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
@@ -1774,7 +1774,7 @@
         <v>1158.51</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>1074.92</v>
+        <v>1075.4</v>
       </c>
       <c r="G22" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LODHA","Chart 📈")</f>
@@ -1802,7 +1802,7 @@
         <v>1814.61</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1722.36</v>
+        <v>1722.45</v>
       </c>
       <c r="G23" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
@@ -1830,7 +1830,7 @@
         <v>1919.32</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>1827.2</v>
+        <v>1826.06</v>
       </c>
       <c r="G24" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
@@ -1858,7 +1858,7 @@
         <v>799.03</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>608.96</v>
+        <v>605.59</v>
       </c>
       <c r="G25" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
@@ -1886,7 +1886,7 @@
         <v>350.92</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>305.94</v>
+        <v>304.87</v>
       </c>
       <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1911,10 +1911,10 @@
         <v>658.89</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>658.38</v>
+        <v>658.39</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>623.24</v>
+        <v>623.62</v>
       </c>
       <c r="G27" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
@@ -1939,10 +1939,10 @@
         <v>47719.99</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>45912.88</v>
+        <v>45912.87</v>
       </c>
       <c r="F28" s="14" t="n">
-        <v>40668.67</v>
+        <v>40654.01</v>
       </c>
       <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
@@ -1967,10 +1967,10 @@
         <v>5354.57</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>5338.66</v>
+        <v>5338.65</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>5252.89</v>
+        <v>5248.63</v>
       </c>
       <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
@@ -1998,7 +1998,7 @@
         <v>159.56</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>139.66</v>
+        <v>139.78</v>
       </c>
       <c r="G30" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
@@ -2023,10 +2023,10 @@
         <v>4156.34</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>4106.81</v>
+        <v>4106.82</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>3800.14</v>
+        <v>3802.68</v>
       </c>
       <c r="G31" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
@@ -2054,7 +2054,7 @@
         <v>1206.51</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>1143.03</v>
+        <v>1140.52</v>
       </c>
       <c r="G32" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
@@ -2082,7 +2082,7 @@
         <v>790.96</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>870.72</v>
+        <v>866.8099999999999</v>
       </c>
       <c r="G33" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
@@ -2110,7 +2110,7 @@
         <v>1298.71</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1023.95</v>
+        <v>1021.08</v>
       </c>
       <c r="G34" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
@@ -2138,7 +2138,7 @@
         <v>187.48</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>182.13</v>
+        <v>181.77</v>
       </c>
       <c r="G35" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
@@ -2166,7 +2166,7 @@
         <v>82.37</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>75.23</v>
+        <v>75.19</v>
       </c>
       <c r="G36" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
@@ -2194,7 +2194,7 @@
         <v>114.65</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>111.86</v>
+        <v>111.71</v>
       </c>
       <c r="G37" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
@@ -2222,7 +2222,7 @@
         <v>653.99</v>
       </c>
       <c r="F38" s="14" t="n">
-        <v>564.77</v>
+        <v>562.98</v>
       </c>
       <c r="G38" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
@@ -2250,7 +2250,7 @@
         <v>4384.24</v>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3746.15</v>
+        <v>3739.91</v>
       </c>
       <c r="G39" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
@@ -2278,7 +2278,7 @@
         <v>538.59</v>
       </c>
       <c r="F40" s="18" t="n">
-        <v>533.08</v>
+        <v>532.75</v>
       </c>
       <c r="G40" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
@@ -2306,7 +2306,7 @@
         <v>3127.53</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>2733.38</v>
+        <v>2732.03</v>
       </c>
       <c r="G41" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
@@ -2334,7 +2334,7 @@
         <v>999.29</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>976.65</v>
+        <v>974.89</v>
       </c>
       <c r="G42" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -2362,7 +2362,7 @@
         <v>416.6</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>414.95</v>
+        <v>414.63</v>
       </c>
       <c r="G43" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Sep-2026  18:35</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 29-Sep-2026  16:57</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>13</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.65</v>
       </c>
       <c r="H4" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I4" s="7" t="n">
         <v>0.65</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.6667000000000001</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,25 +703,25 @@
         <v>15</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.467</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.733</v>
+        <v>0.6</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5997</v>
+        <v>0.489</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -734,25 +734,25 @@
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5333</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -765,180 +765,180 @@
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="F7" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I7" s="11" t="n">
         <v>0.3</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="F8" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>0.333</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.467</v>
-      </c>
       <c r="I8" s="7" t="n">
-        <v>0.3557</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2887</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.025</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.025</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.25</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2447</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -951,93 +951,93 @@
         <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.05</v>
+        <v>0.067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.15</v>
+        <v>0.067</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.3</v>
+        <v>0.133</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="F15" s="10" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1417</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0833</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>26955</v>
+        <v>27270</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26505.99</v>
+        <v>26598.91</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26528.66</v>
+        <v>26565.7</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26749.39</v>
+        <v>26754.48</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3547.8</v>
+        <v>3557.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3536.63</v>
+        <v>3537.63</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3484.29</v>
+        <v>3488.7</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3124.45</v>
+        <v>3132.7</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1712</v>
+        <v>1697.7</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1684.27</v>
+        <v>1686.69</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1639.11</v>
+        <v>1643.61</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1454.23</v>
+        <v>1459.05</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>9619.5</v>
+        <v>9431</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>9294.190000000001</v>
+        <v>9329.26</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8715.26</v>
+        <v>8774.780000000001</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7322.34</v>
+        <v>7365.27</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2917.2</v>
+        <v>1251.9</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2899.58</v>
+        <v>1190.47</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2771.28</v>
+        <v>1193.36</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2309.42</v>
+        <v>1228.83</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>868.65</v>
+        <v>2989.7</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>865.4400000000001</v>
+        <v>2907.85</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>851.5599999999999</v>
+        <v>2784.55</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>742.66</v>
+        <v>2321.97</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1970.8</v>
+        <v>2441.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1960.14</v>
+        <v>2414.23</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1887.43</v>
+        <v>2369.78</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1663.59</v>
+        <v>2223.23</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2007</v>
+        <v>866.75</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1948.59</v>
+        <v>864.35</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1835.29</v>
+        <v>852.15</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1440.97</v>
+        <v>744.97</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2474.9</v>
+        <v>1979</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2383.05</v>
+        <v>1956.84</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>2394.45</v>
+        <v>1847.54</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2359.85</v>
+        <v>1451.94</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>4988.5</v>
+        <v>2545</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>4932.37</v>
+        <v>2403</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>4893.11</v>
+        <v>2401.9</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>4485.3</v>
+        <v>2362.44</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TORNTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1203.9</v>
+        <v>1200.5</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1150.93</v>
+        <v>1161.17</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1134.8</v>
+        <v>1140.4</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1051.37</v>
+        <v>1054.47</v>
       </c>
       <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>2214.7</v>
+        <v>2188.6</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>2170.84</v>
+        <v>2174.79</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>2089.32</v>
+        <v>2097.27</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1952.63</v>
+        <v>1957.39</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
@@ -1565,23 +1565,23 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>588.95</v>
+        <v>2833.3</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>586.66</v>
+        <v>2741.14</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>579.97</v>
+        <v>2641.36</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>562.9</v>
+        <v>2505.27</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HINDZINC","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,23 +1593,23 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>1164.8</v>
+        <v>181.82</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1139.5</v>
+        <v>181.76</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>1128.14</v>
+        <v>179.96</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1121.05</v>
+        <v>168.88</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JINDALSTEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1621,750 +1621,218 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>JSL</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>748.25</v>
+        <v>2842</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>740.92</v>
+        <v>2618.12</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>732.3200000000001</v>
+        <v>2302.91</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>735.23</v>
+        <v>1574.61</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>2778.3</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>2729.66</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>2628.84</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>2499.49</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1924.64</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1920.94</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1828.33</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>185</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>181.5</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>179.71</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>168.6</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1185.75</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>828.55</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>617.02</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2832.4</v>
+        <v>388.4</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2579.28</v>
+        <v>369.77</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>2262.18</v>
+        <v>353.47</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1550.03</v>
+        <v>306.44</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>683</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>661.76</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>656.2</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>642.6</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>553.25</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>488.36</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>485.33</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>515.34</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1165</v>
+        <v>888.2</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>1160.82</v>
+        <v>812.48</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>1158.51</v>
+        <v>799.52</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>1075.4</v>
+        <v>867.52</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LODHA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>1858.5</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>1815.34</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1814.61</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>1722.45</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:OBEROIRLTY","Chart 📈")</f>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>199.83</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>193.21</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>188.48</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>182.14</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>1978.4</v>
+        <v>425</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>1921.24</v>
+        <v>419.46</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>1919.32</v>
+        <v>417.15</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>1826.06</v>
+        <v>414.81</v>
       </c>
       <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>1196.65</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>959.4400000000001</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>799.03</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>605.59</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>376.45</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>366.56</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>350.92</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>304.87</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>668.95</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>658.89</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>658.39</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>623.62</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>48250</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>47719.99</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>45912.87</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>40654.01</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>5360</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>5354.57</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>5338.65</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>5248.63</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>165.71</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>163.05</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>159.56</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>139.78</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>4157.3</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>4156.34</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>4106.82</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>3802.68</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>1218.1</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>1214.95</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1206.51</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>1140.52</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>WHIRLPOOL</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>918.9</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>792.66</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>790.96</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>866.8099999999999</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1365.4</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>1357.88</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>1298.71</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>1021.08</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>201.67</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>191.61</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>187.48</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>181.77</v>
-      </c>
-      <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>84.88</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>82.93000000000001</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>82.37</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>75.19</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n">
-        <v>116.6</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>116.58</v>
-      </c>
-      <c r="E37" s="18" t="n">
-        <v>114.65</v>
-      </c>
-      <c r="F37" s="18" t="n">
-        <v>111.71</v>
-      </c>
-      <c r="G37" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>685.8</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>676.4299999999999</v>
-      </c>
-      <c r="E38" s="14" t="n">
-        <v>653.99</v>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>562.98</v>
-      </c>
-      <c r="G38" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>4557.1</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>4486.84</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>4384.24</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>3739.91</v>
-      </c>
-      <c r="G39" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n">
-        <v>566</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>551.61</v>
-      </c>
-      <c r="E40" s="18" t="n">
-        <v>538.59</v>
-      </c>
-      <c r="F40" s="18" t="n">
-        <v>532.75</v>
-      </c>
-      <c r="G40" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n">
-        <v>3324.9</v>
-      </c>
-      <c r="D41" s="18" t="n">
-        <v>3263.03</v>
-      </c>
-      <c r="E41" s="18" t="n">
-        <v>3127.53</v>
-      </c>
-      <c r="F41" s="18" t="n">
-        <v>2732.03</v>
-      </c>
-      <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1094.7</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <v>1058.46</v>
-      </c>
-      <c r="E42" s="14" t="n">
-        <v>999.29</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>974.89</v>
-      </c>
-      <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>426.1</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>416.6</v>
-      </c>
-      <c r="F43" s="18" t="n">
-        <v>414.63</v>
-      </c>
-      <c r="G43" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 29-Sep-2026  16:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 30-Sep-2026  16:50</t>
         </is>
       </c>
     </row>
@@ -672,124 +672,124 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>14</v>
-      </c>
       <c r="F4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>0.65</v>
       </c>
-      <c r="H4" s="6" t="n">
-        <v>0.7</v>
-      </c>
       <c r="I4" s="7" t="n">
-        <v>0.65</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.467</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.489</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="H6" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
         <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
@@ -799,22 +799,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.067</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,22 +827,22 @@
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>0.1777</v>
@@ -851,122 +851,122 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.025</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>0.1</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0557</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>27270</v>
+        <v>27125</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26598.91</v>
+        <v>26649.02</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26565.7</v>
+        <v>26587.61</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26754.48</v>
+        <v>26728.39</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3557.5</v>
+        <v>3620.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3537.63</v>
+        <v>3545.55</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3488.7</v>
+        <v>3493.88</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3132.7</v>
+        <v>3136.1</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1697.7</v>
+        <v>1233</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1686.69</v>
+        <v>1194.52</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1643.61</v>
+        <v>1194.91</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1459.05</v>
+        <v>1228</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>9431</v>
+        <v>1980</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>9329.26</v>
+        <v>1959.05</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8774.780000000001</v>
+        <v>1852.73</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7365.27</v>
+        <v>1457.26</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1251.9</v>
+        <v>2503.8</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1190.47</v>
+        <v>2412.6</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1193.36</v>
+        <v>2405.9</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1228.83</v>
+        <v>2361.71</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,387 +1369,387 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2989.7</v>
+        <v>1162</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>2907.85</v>
+        <v>1161.25</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2784.55</v>
+        <v>1141.25</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2321.97</v>
+        <v>1054.72</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>GLENMARK</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>2441.5</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>2414.23</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>2369.78</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>2223.23</v>
-      </c>
-      <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>392.85</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>371.96</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>306.38</v>
+      </c>
+      <c r="G9" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>GRANULES</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>866.75</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>864.35</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>852.15</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>744.97</v>
-      </c>
-      <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>506.55</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>498.02</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>495.51</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>448.54</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>1979</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>1956.84</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>1847.54</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>1451.94</v>
-      </c>
-      <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>605</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>499.47</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>490.02</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>515.9299999999999</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2545</v>
+        <v>2190.1</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2403</v>
+        <v>2176.25</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2401.9</v>
+        <v>2100.91</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2362.44</v>
+        <v>1958.91</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>JSL</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1200.5</v>
+        <v>747.4</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1161.17</v>
+        <v>741.6799999999999</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1140.4</v>
+        <v>733.62</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>1054.47</v>
+        <v>735.48</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>2188.6</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>2174.79</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>2097.27</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>1957.39</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>181.49</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>179.61</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>177.79</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>167.07</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>RATNAMANI</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>2833.3</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>2741.14</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>2641.36</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>2505.27</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RATNAMANI","Chart 📈")</f>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>2717</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>2627.54</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>2319.15</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1586.88</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>181.82</v>
+        <v>674</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>181.76</v>
+        <v>662.3099999999999</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>179.96</v>
+        <v>657.04</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>168.88</v>
+        <v>642.5</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C17" s="18" t="n">
-        <v>2842</v>
+        <v>1935</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>2618.12</v>
+        <v>1925.63</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>2302.91</v>
+        <v>1921.49</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1574.61</v>
+        <v>1829.94</v>
       </c>
       <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1929</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>1924.64</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1920.94</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1828.33</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1213.05</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1020.29</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>843.62</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>622.83</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>1185.75</v>
+        <v>163.26</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>1000</v>
+        <v>162.63</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>828.55</v>
+        <v>159.77</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>617.02</v>
+        <v>140.33</v>
       </c>
       <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>388.4</v>
+        <v>1380.1</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>369.77</v>
+        <v>1351.11</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>353.47</v>
+        <v>1302.28</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>306.44</v>
+        <v>1032.37</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>553.25</v>
+        <v>200.52</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>488.36</v>
+        <v>193.9</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>485.33</v>
+        <v>188.95</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>515.34</v>
+        <v>182.63</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1761,78 +1761,190 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1235.1</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1212.78</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1206.41</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1142.73</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
           <t>WHIRLPOOL</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>888.2</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>812.48</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>799.52</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>867.52</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C23" s="14" t="n">
+        <v>890.25</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>819.89</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>803.08</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>866.97</v>
+      </c>
+      <c r="G23" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>199.83</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>193.21</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>188.48</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>182.14</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>1100.7</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1064.07</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1008.38</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>977.84</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>227.02</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>220.82</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>217.86</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>162.8</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>417</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>411.07</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>406.19</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>399.61</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>3300.4</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>3263.95</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>3143.17</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>2745.49</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
+      <c r="C28" s="18" t="n">
         <v>425</v>
       </c>
-      <c r="D24" s="14" t="n">
-        <v>419.46</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>417.15</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>414.81</v>
-      </c>
-      <c r="G24" s="15">
+      <c r="D28" s="18" t="n">
+        <v>419.99</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>417.46</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>415.04</v>
+      </c>
+      <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 30-Sep-2026  16:50</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 01-Oct-2026  17:25</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4833</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,69 +703,69 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4223</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>3</v>
@@ -774,78 +774,78 @@
         <v>6</v>
       </c>
       <c r="F7" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H7" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>0.6</v>
-      </c>
       <c r="I7" s="11" t="n">
-        <v>0.4</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -864,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.133</v>
@@ -873,100 +873,100 @@
         <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1667</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.15</v>
+        <v>0.333</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.15</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.025</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I13" s="11" t="n">
         <v>0.1</v>
@@ -985,7 +985,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>2</v>
@@ -994,13 +994,13 @@
         <v>0.067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
@@ -1028,20 +1028,20 @@
         <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.167</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,20 +1059,20 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0833</v>
+        <v>0.0333</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0333</v>
+        <v>0.0277</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>27125</v>
+        <v>26840</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26649.02</v>
+        <v>26667.21</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26587.61</v>
+        <v>26597.54</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26728.39</v>
+        <v>26777.14</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3620.8</v>
+        <v>3581</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3545.55</v>
+        <v>3548.93</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3493.88</v>
+        <v>3497.3</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3136.1</v>
+        <v>3139.88</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1233</v>
+        <v>1984</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1194.52</v>
+        <v>1961.42</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1194.91</v>
+        <v>1857.88</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1228</v>
+        <v>1464.92</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,639 +1313,387 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1980</v>
+        <v>2535</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1959.05</v>
+        <v>2424.26</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1852.73</v>
+        <v>2410.96</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1457.26</v>
+        <v>2363.75</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>2503.8</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>2412.6</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>2405.9</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>2361.71</v>
-      </c>
-      <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>1162</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>1161.25</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>1141.25</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>1054.72</v>
-      </c>
-      <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>392.85</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>371.96</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>355.01</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>306.38</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="C7" s="18" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>308.99</v>
+      </c>
+      <c r="G7" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>506.55</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>498.02</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>495.51</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>448.54</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>SUNTV</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>605</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>499.47</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>490.02</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>515.9299999999999</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="C8" s="18" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>509.03</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>494.33</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>523.01</v>
+      </c>
+      <c r="G8" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1930</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1926.05</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1921.83</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1831.61</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1197.2</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1037.14</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>857.49</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>629.26</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1808.7</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>1773.21</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1602.42</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>2190.1</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>2176.25</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>2100.91</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>1958.91</v>
-      </c>
-      <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>1104.6</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1067.93</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1012.15</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>979.35</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>JSL</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>747.4</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>741.6799999999999</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>733.62</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>735.48</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>238.36</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>222.49</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>218.67</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>163.6</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>181.49</v>
+        <v>1401.1</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>179.61</v>
+        <v>1355.87</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>177.79</v>
+        <v>1306.16</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>167.07</v>
+        <v>1037.77</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAIL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>2717</v>
+        <v>199.04</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2627.54</v>
+        <v>194.39</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2319.15</v>
+        <v>189.35</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1586.88</v>
+        <v>182.9</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>674</v>
+        <v>1225.1</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>662.3099999999999</v>
+        <v>1213.95</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>657.04</v>
+        <v>1207.14</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>642.5</v>
+        <v>1145.56</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>1935</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1925.63</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1921.49</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>1829.94</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>1213.05</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>1020.29</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>843.62</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>622.83</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>163.26</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>162.63</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>159.77</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>140.33</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>1380.1</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>1351.11</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>1302.28</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1032.37</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>200.52</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>193.9</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>188.95</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>182.63</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1235.1</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1212.78</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1206.41</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1142.73</v>
-      </c>
-      <c r="G22" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>WHIRLPOOL</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>890.25</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>819.89</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>803.08</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>866.97</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>420.4</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>420.03</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>417.57</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>414.98</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>1100.7</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1064.07</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1008.38</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>977.84</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1275.4</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1219.82</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1242.36</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1134.48</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>227.02</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>220.82</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>217.86</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>162.8</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>417</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>411.07</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>406.19</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>399.61</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C19" s="18" t="n">
+        <v>418.35</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>411.77</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>406.67</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>3300.4</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>3263.95</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>3143.17</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>2745.49</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>425</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>419.99</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>417.46</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>415.04</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 01-Oct-2026  17:25</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 02-Oct-2026  16:39</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>26597.54</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26777.14</v>
+        <v>26783.16</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
@@ -1270,7 +1270,7 @@
         <v>3497.3</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3139.88</v>
+        <v>3140.17</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1298,7 +1298,7 @@
         <v>1857.88</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1464.92</v>
+        <v>1464.31</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1326,7 +1326,7 @@
         <v>2410.96</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2363.75</v>
+        <v>2364.44</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
@@ -1354,7 +1354,7 @@
         <v>356.18</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>308.99</v>
+        <v>309.25</v>
       </c>
       <c r="G7" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1382,7 +1382,7 @@
         <v>494.33</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>523.01</v>
+        <v>521.02</v>
       </c>
       <c r="G8" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
@@ -1410,7 +1410,7 @@
         <v>1921.83</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1831.61</v>
+        <v>1831.5</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
@@ -1438,7 +1438,7 @@
         <v>857.49</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>629.26</v>
+        <v>629.73</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
@@ -1466,7 +1466,7 @@
         <v>1773.21</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1602.42</v>
+        <v>1603.42</v>
       </c>
       <c r="G11" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1491,10 +1491,10 @@
         <v>1067.93</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1012.15</v>
+        <v>1012.16</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>979.35</v>
+        <v>981.03</v>
       </c>
       <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1522,7 +1522,7 @@
         <v>218.67</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>163.6</v>
+        <v>163.79</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1550,7 +1550,7 @@
         <v>1306.16</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1037.77</v>
+        <v>1045.45</v>
       </c>
       <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
@@ -1578,7 +1578,7 @@
         <v>189.35</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>182.9</v>
+        <v>183.03</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
@@ -1606,7 +1606,7 @@
         <v>1207.14</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>1145.56</v>
+        <v>1146.73</v>
       </c>
       <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
@@ -1634,7 +1634,7 @@
         <v>417.57</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>414.98</v>
+        <v>414.59</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
@@ -1662,7 +1662,7 @@
         <v>1242.36</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1134.48</v>
+        <v>1136.74</v>
       </c>
       <c r="G18" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
@@ -1690,7 +1690,7 @@
         <v>406.67</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>400.93</v>
+        <v>401.54</v>
       </c>
       <c r="G19" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 02-Oct-2026  16:39</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 06-Oct-2026  17:14</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.25</v>
+        <v>0.45</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.45</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,53 +703,53 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.3333</v>
@@ -758,249 +758,249 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="E7" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.267</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.2167</v>
+        <v>0.3113</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.267</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.1553</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F10" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>0.133</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I10" s="7" t="n">
-        <v>0.1553</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="F11" s="10" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.075</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.125</v>
+        <v>0.2167</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.111</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.175</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="E14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>0.067</v>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" s="6" t="n">
-        <v>0.133</v>
+        <v>0.333</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0667</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1013,25 +1013,25 @@
         <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.0557</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>26840</v>
+        <v>3573.4</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>26667.21</v>
+        <v>3545.84</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>26597.54</v>
+        <v>3499.86</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>26783.16</v>
+        <v>3150.23</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ABBOTINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3581</v>
+        <v>1692.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>3548.93</v>
+        <v>1683.85</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>3497.3</v>
+        <v>1650.02</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>3140.17</v>
+        <v>1470.33</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1984</v>
+        <v>9550</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1961.42</v>
+        <v>9324.469999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1857.88</v>
+        <v>8871.98</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1464.31</v>
+        <v>7470.22</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,387 +1313,807 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>3006.1</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>2914.32</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>2805.26</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>2340.9</v>
+      </c>
+      <c r="G6" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>1972.48</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>1874.26</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>1480.09</v>
+      </c>
+      <c r="G7" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
           <t>MANKIND</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>2535</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>2424.26</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>2410.96</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>2364.44</v>
-      </c>
-      <c r="G6" s="15">
+      <c r="C8" s="14" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>2444.82</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>2421.51</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>2369.25</v>
+      </c>
+      <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1159.5</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>1157.96</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1142.04</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>1058.49</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
-        <v>384.7</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>373.18</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>356.18</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>309.25</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="C10" s="18" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>374.87</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>358.21</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>310.6</v>
+      </c>
+      <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>599.9</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>509.03</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>494.33</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>521.02</v>
-      </c>
-      <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>1930</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1926.05</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>1921.83</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>1831.5</v>
-      </c>
-      <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>1197.2</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1037.14</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>857.49</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>629.73</v>
-      </c>
-      <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>1826</v>
+        <v>1249.4</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1808.7</v>
+        <v>1240.74</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>1773.21</v>
+        <v>1201.4</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1603.42</v>
+        <v>1100.59</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>1104.6</v>
+        <v>503.7</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>1067.93</v>
+        <v>498.23</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1012.16</v>
+        <v>495.87</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>981.03</v>
+        <v>449.77</v>
       </c>
       <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>238.36</v>
+        <v>632.1</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>222.49</v>
+        <v>530.91</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>218.67</v>
+        <v>504.73</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>163.79</v>
+        <v>523.24</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1401.1</v>
+        <v>1849.7</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1355.87</v>
+        <v>1817.68</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1306.16</v>
+        <v>1781.09</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1045.45</v>
+        <v>1614.39</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>199.04</v>
+        <v>1119.4</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>194.39</v>
+        <v>1079.06</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>189.35</v>
+        <v>1021.19</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>183.03</v>
+        <v>984.79</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>1225.1</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>1213.95</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1207.14</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>1146.73</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>262.78</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>229.96</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>222.3</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>166.24</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>420.4</v>
+        <v>389.1</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>420.03</v>
+        <v>377.58</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>417.57</v>
+        <v>379.1</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>414.59</v>
+        <v>386.48</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>SCHNEIDER</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1275.4</v>
+        <v>5521</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1219.82</v>
+        <v>5417.7</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1242.36</v>
+        <v>5404.9</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1136.74</v>
+        <v>5321.06</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>JSL</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>750.95</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>741.89</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>734.58</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>737.48</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2660.9</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2616.28</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2359.62</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1625.93</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>666.1</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>663.01</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>658.1</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>645.0700000000001</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1294.3</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1096.82</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>903.62</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>647.92</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1395.9</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1363.52</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1315.12</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1051.48</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>195.75</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>190.51</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>183.53</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>297.5</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>287.69</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>285.65</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>279.52</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>691.3</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>672.51</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>657.49</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>571.98</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>4460.1</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>4414.9</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>4374.82</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>3786.05</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>418.35</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>411.77</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>406.67</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C28" s="18" t="n">
+        <v>431.9</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>414.05</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>408.01</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>402.71</v>
+      </c>
+      <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>3310</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>3252.35</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>3155.48</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>2770.51</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>867.8</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>835.12</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>812.36</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>866.3200000000001</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>452</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>424.97</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>419.52</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>365.84</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>912</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>884.76</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>886.15</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>832.9400000000001</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1233.48</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1245.77</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1139.64</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>3854</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>3833.97</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>3841.93</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>3607.75</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 06-Oct-2026  17:14</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-Oct-2026  17:51</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4833</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -734,118 +734,118 @@
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="F7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.267</v>
+        <v>0.167</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.467</v>
+        <v>0.25</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3113</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.267</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2447</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2447</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>3</v>
@@ -867,7 +867,7 @@
         <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.2</v>
@@ -876,7 +876,7 @@
         <v>0.133</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -892,19 +892,19 @@
         <v>6</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="I11" s="11" t="n">
         <v>0.2167</v>
@@ -920,22 +920,22 @@
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.133</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.2</v>
@@ -944,104 +944,104 @@
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.175</v>
+        <v>0.067</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.175</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.225</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1583</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.111</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,20 +1059,20 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.167</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0333</v>
+        <v>0.0557</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0277</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3573.4</v>
+        <v>3569.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3545.84</v>
+        <v>3548.12</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3499.86</v>
+        <v>3502.6</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>3150.23</v>
+        <v>3156.64</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1692.8</v>
+        <v>9588</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1683.85</v>
+        <v>9349.57</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1650.02</v>
+        <v>8900.07</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1470.33</v>
+        <v>7513.56</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9550</v>
+        <v>3150.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9324.469999999999</v>
+        <v>2934.74</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>8871.98</v>
+        <v>2821.66</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7470.22</v>
+        <v>2354.28</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3006.1</v>
+        <v>2052.8</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2914.32</v>
+        <v>1980.13</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>2805.26</v>
+        <v>1881.26</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2340.9</v>
+        <v>1485.82</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,107 +1341,107 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2050</v>
+        <v>2500</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>1972.48</v>
+        <v>2450.08</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>1874.26</v>
+        <v>2424.59</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>1480.09</v>
+        <v>2372.51</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>2444.82</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>2421.51</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>2369.25</v>
-      </c>
-      <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>378.45</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>375.21</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>359.01</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>310.85</v>
+      </c>
+      <c r="G8" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>1159.5</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1157.96</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>1142.04</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>1058.49</v>
-      </c>
-      <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1343.8</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1250.56</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1206.98</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1101.69</v>
+      </c>
+      <c r="G9" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>379.55</v>
+        <v>503.75</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>374.87</v>
+        <v>498.54</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>358.21</v>
+        <v>496.15</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>310.6</v>
+        <v>451.18</v>
       </c>
       <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,107 +1453,107 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>1249.4</v>
+        <v>636.5</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1240.74</v>
+        <v>540.96</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>1201.4</v>
+        <v>509.89</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1100.59</v>
+        <v>524.76</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>503.7</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>498.23</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>495.87</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>449.77</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1822.2</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>1818.11</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>1782.7</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1618.36</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>632.1</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>530.91</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>504.73</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>523.24</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1082.48</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>1024.87</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>985.95</v>
+      </c>
+      <c r="G13" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1849.7</v>
+        <v>271.9</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1817.68</v>
+        <v>233.95</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>1781.09</v>
+        <v>224.25</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1614.39</v>
+        <v>167.3</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1565,555 +1565,499 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1119.4</v>
+        <v>5507</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1079.06</v>
+        <v>5426.2</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1021.19</v>
+        <v>5408.91</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>984.79</v>
+        <v>5329.39</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>262.78</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>229.96</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>166.24</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>INDUSTOWER</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>389.1</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>377.58</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>379.1</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>386.48</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>114.59</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>114.07</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>113.91</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>112.07</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>5521</v>
+        <v>1460.2</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>5417.7</v>
+        <v>1372.73</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>5404.9</v>
+        <v>1320.81</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>5321.06</v>
+        <v>1054.7</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>JSL</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>750.95</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>741.89</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>734.58</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>737.48</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSL","Chart 📈")</f>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>197.15</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>195.88</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>190.77</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>183.62</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>2660.9</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>2616.28</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>2359.62</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>1625.93</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>297</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>288.58</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>286.1</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>280.25</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>666.1</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>663.01</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>658.1</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>645.0700000000001</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n">
+        <v>1206.7</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1107.28</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>915.5</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>653.64</v>
+      </c>
+      <c r="G21" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1294.3</v>
+        <v>706.6</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>1096.82</v>
+        <v>675.75</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>903.62</v>
+        <v>659.41</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>647.92</v>
+        <v>573.78</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1395.9</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1363.52</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1315.12</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1051.48</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>4495</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>4422.53</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>4379.54</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>3796.81</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>200.2</v>
+        <v>440</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>195.75</v>
+        <v>416.98</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>190.51</v>
+        <v>409.67</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>183.53</v>
+        <v>402.94</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>297.5</v>
+        <v>3362.6</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>287.69</v>
+        <v>3262.85</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>285.65</v>
+        <v>3163.61</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>279.52</v>
+        <v>2776.67</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>691.3</v>
+        <v>1226.2</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>672.51</v>
+        <v>1215.92</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>657.49</v>
+        <v>1209.03</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>571.98</v>
+        <v>1149.32</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>4460.1</v>
+        <v>569</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>4414.9</v>
+        <v>568.15</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>4374.82</v>
+        <v>564.02</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>3786.05</v>
+        <v>495.26</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>431.9</v>
+        <v>2704.6</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>414.05</v>
+        <v>2624.69</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>408.01</v>
+        <v>2373.15</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>402.71</v>
+        <v>1638.18</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>3310</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>3252.35</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>3155.48</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>2770.51</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1341.4</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>1293.28</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1317.61</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1257.06</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>867.8</v>
+        <v>448.5</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>835.12</v>
+        <v>427.21</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>812.36</v>
+        <v>420.65</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>866.3200000000001</v>
+        <v>366.63</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WHIRLPOOL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>452</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>424.97</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>419.52</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>365.84</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>894.5</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>885.6900000000001</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>886.48</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>833.76</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>912</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>884.76</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>886.15</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>832.9400000000001</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>SCHNEIDER</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n">
-        <v>1274</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>1233.48</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>1245.77</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>1139.64</v>
-      </c>
-      <c r="G33" s="19">
+      <c r="C32" s="14" t="n">
+        <v>1256.2</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>1235.64</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>1246.18</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1140.87</v>
+      </c>
+      <c r="G32" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>3854</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>3833.97</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>3841.93</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>3607.75</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SIEMENS","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 07-Oct-2026  17:51</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 08-Oct-2026  17:54</t>
         </is>
       </c>
     </row>
@@ -665,69 +665,69 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -740,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.3</v>
@@ -749,103 +749,103 @@
         <v>0.25</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.2833</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2447</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,118 +858,118 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.222</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2167</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.067</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.08869999999999999</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,25 +982,25 @@
         <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.15</v>
+        <v>0.025</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.1</v>
+        <v>0.025</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.225</v>
+        <v>0.175</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1583</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0</v>
@@ -1028,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.167</v>
+        <v>0.083</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0557</v>
+        <v>0.0277</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,840 +1224,504 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>AJANTPHARM</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3569.8</v>
+        <v>376</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3548.12</v>
+        <v>375.29</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3502.6</v>
+        <v>359.67</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>3156.64</v>
+        <v>310.87</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>1309.2</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>1256.14</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>1210.99</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>1103.6</v>
+      </c>
+      <c r="G4" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>614.2</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>547.9400000000001</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>513.98</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>524.61</v>
+      </c>
+      <c r="G5" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>DIVISLAB</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n">
-        <v>9588</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>9349.57</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>8900.07</v>
-      </c>
-      <c r="F4" s="14" t="n">
-        <v>7513.56</v>
-      </c>
-      <c r="G4" s="15">
+      <c r="C6" s="18" t="n">
+        <v>9361</v>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>9350.66</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>8918.15</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>7533.23</v>
+      </c>
+      <c r="G6" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>GLAND</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n">
-        <v>3150.6</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>2934.74</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>2821.66</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>2354.28</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="C7" s="18" t="n">
+        <v>3079.1</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>2948.49</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>2831.75</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>2362.83</v>
+      </c>
+      <c r="G7" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n">
-        <v>2052.8</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>1980.13</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>1881.26</v>
-      </c>
-      <c r="F6" s="14" t="n">
-        <v>1485.82</v>
-      </c>
-      <c r="G6" s="15">
+      <c r="C8" s="18" t="n">
+        <v>1997.9</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>1981.82</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1885.83</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1490.15</v>
+      </c>
+      <c r="G8" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>2450.08</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>2424.59</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>2372.51</v>
-      </c>
-      <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>435</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>410.67</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>403.11</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>378.45</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>375.21</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>359.01</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>310.85</v>
-      </c>
-      <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>537</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>534.04</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>533.99</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>531.58</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>1343.8</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>1250.56</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>1206.98</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>1101.69</v>
-      </c>
-      <c r="G9" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>258.31</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>236.27</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>225.58</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>503.75</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>498.54</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>496.15</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>451.18</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>5468</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>5430.18</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>5411.22</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>5330.16</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>636.5</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>540.96</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>509.89</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>524.76</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>1822.2</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>1818.11</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>1782.7</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>1618.36</v>
-      </c>
-      <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>1115</v>
+        <v>82.05</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>1082.48</v>
+        <v>81.89</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>1024.87</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>985.95</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>271.9</v>
+        <v>115.29</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>233.95</v>
+        <v>114.19</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>224.25</v>
+        <v>113.97</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>167.3</v>
+        <v>112.03</v>
       </c>
       <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>5507</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>5426.2</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>5408.91</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>5329.39</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>84.15000000000001</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>81.88</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>81.95999999999999</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>114.59</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>114.07</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>113.91</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>112.07</v>
-      </c>
-      <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>AEGISLOG</t>
         </is>
       </c>
-      <c r="C18" s="14" t="n">
-        <v>1460.2</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>1372.73</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1320.81</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1054.7</v>
-      </c>
-      <c r="G18" s="15">
+      <c r="C15" s="18" t="n">
+        <v>1382.3</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1373.64</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1323.22</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1056.93</v>
+      </c>
+      <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>CASTROLIND</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>197.15</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>195.88</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>190.77</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>183.62</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C16" s="18" t="n">
+        <v>196.08</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>190.98</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>183.63</v>
+      </c>
+      <c r="G16" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>297</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>288.58</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>286.1</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>280.25</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>689.45</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>677.0599999999999</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>660.59</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>574.78</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
-        <v>1206.7</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1107.28</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>915.5</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>653.64</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="C18" s="18" t="n">
+        <v>1167.1</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1112.98</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>925.37</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>658.28</v>
+      </c>
+      <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>706.6</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>675.75</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>659.41</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>573.78</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>4495</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>4422.53</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>4379.54</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>3796.81</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>440</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>416.98</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>409.67</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>402.94</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>3362.6</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>3262.85</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>3163.61</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>2776.67</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1226.2</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1215.92</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1209.03</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1149.32</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>569</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>568.15</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>564.02</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>495.26</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n">
-        <v>2704.6</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>2624.69</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>2373.15</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>1638.18</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="C19" s="14" t="n">
+        <v>2651.3</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>2627.23</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>2384.05</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>1646.92</v>
+      </c>
+      <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>1341.4</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>1293.28</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>1317.61</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>1257.06</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C30" s="14" t="n">
-        <v>448.5</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>427.21</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>420.65</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>366.63</v>
-      </c>
-      <c r="G30" s="15">
+      <c r="C20" s="18" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>427.44</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>421</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>366.79</v>
+      </c>
+      <c r="G20" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>894.5</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>885.6900000000001</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>886.48</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>833.76</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CGPOWER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>SCHNEIDER</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1256.2</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>1235.64</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>1246.18</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>1140.87</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SCHNEIDER","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 08-Oct-2026  17:54</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 09-Oct-2026  17:29</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.3</v>
@@ -687,10 +687,10 @@
         <v>0.3</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,87 +703,87 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>10</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.2833</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F6" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>0.25</v>
-      </c>
       <c r="H6" s="6" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.2333</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,7 +796,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>2</v>
@@ -805,7 +805,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.167</v>
@@ -814,237 +814,237 @@
         <v>0.25</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.133</v>
+        <v>0.333</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.267</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.067</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.1553</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.025</v>
+        <v>0.083</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.175</v>
+        <v>0.167</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.075</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -1053,26 +1053,26 @@
         <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.1</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0277</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>376</v>
+        <v>377.65</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>375.29</v>
+        <v>375.39</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>359.67</v>
+        <v>359.78</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>310.87</v>
+        <v>310.8</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1309.2</v>
+        <v>1327.2</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1256.14</v>
+        <v>1264.01</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1210.99</v>
+        <v>1213.3</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1103.6</v>
+        <v>1103.85</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>614.2</v>
+        <v>635.9</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>547.9400000000001</v>
+        <v>556.1799999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>513.98</v>
+        <v>518.96</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>524.61</v>
+        <v>527.08</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C6" s="18" t="n">
-        <v>9361</v>
+        <v>1693</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>9350.66</v>
+        <v>1681.26</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>8918.15</v>
+        <v>1650.03</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>7533.23</v>
+        <v>1471.66</v>
       </c>
       <c r="G6" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="18" t="n">
-        <v>3079.1</v>
+        <v>3061.8</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>2948.49</v>
+        <v>2960.3</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>2831.75</v>
+        <v>2833.15</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>2362.83</v>
+        <v>2355.14</v>
       </c>
       <c r="G7" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="18" t="n">
-        <v>1997.9</v>
+        <v>2036.6</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>1981.82</v>
+        <v>1984.32</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>1885.83</v>
+        <v>1883.26</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1490.15</v>
+        <v>1483.4</v>
       </c>
       <c r="G8" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
@@ -1392,335 +1392,447 @@
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>435</v>
+        <v>1867.9</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>418.7</v>
+        <v>1822.06</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>410.67</v>
+        <v>1783.66</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>403.11</v>
+        <v>1622.6</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>CYIENT</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1158.8</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1089.59</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1030.59</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>989.22</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>HFCL</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>237.65</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>225.85</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>166.73</v>
+      </c>
+      <c r="G11" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>5770</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>5465.06</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>5425.01</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>5344.72</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>441</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>420.35</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>411.13</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>403.74</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>LICHSGFIN</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>537</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>534.04</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>533.99</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>531.58</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="C14" s="18" t="n">
+        <v>551.65</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>537.47</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>534.9400000000001</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>531.46</v>
+      </c>
+      <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>258.31</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>236.27</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>225.58</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>168.1</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>5468</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>5430.18</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>5411.22</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>5330.16</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>3318.2</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>3269.6</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>3166.7</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>2778.54</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>MAHABANK</t>
         </is>
       </c>
-      <c r="C13" s="14" t="n">
-        <v>82.05</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>81.89</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>81.95999999999999</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>75.81999999999999</v>
-      </c>
-      <c r="G13" s="15">
+      <c r="C16" s="14" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>75.56</v>
+      </c>
+      <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>115.29</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>114.19</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>113.97</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>112.03</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="C17" s="14" t="n">
+        <v>116.98</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>114.17</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>112.22</v>
+      </c>
+      <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>1382.3</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>1373.64</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1323.22</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1056.93</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>196.08</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>195.9</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>190.98</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>183.63</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>689.45</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>677.0599999999999</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>660.59</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>574.78</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1167.1</v>
+        <v>4550</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1112.98</v>
+        <v>4447.81</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>925.37</v>
+        <v>4390.41</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>658.28</v>
+        <v>3793.27</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>1388.9</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1371.65</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1320.15</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>1051.91</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>288.87</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>286.33</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>279.98</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>WELCORP</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>2651.3</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>2627.23</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>2384.05</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>1646.92</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C21" s="18" t="n">
+        <v>2640.4</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>2625.47</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>2372.94</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1631.7</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>KAJARIACER</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1215.4</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1214.77</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1208.5</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1149.51</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>1186.6</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1106.57</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>917.98</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>653.7</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>429.6</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>427.44</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>421</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>366.79</v>
-      </c>
-      <c r="G20" s="19">
+      <c r="C24" s="14" t="n">
+        <v>433.6</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>427.96</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>420.93</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>365.03</v>
+      </c>
+      <c r="G24" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 09-Oct-2026  17:29</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 12-Oct-2026  20:17</t>
         </is>
       </c>
     </row>
@@ -665,29 +665,29 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>0.3667</v>
@@ -696,23 +696,23 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="F5" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.3</v>
@@ -721,7 +721,7 @@
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.35</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -1224,168 +1224,168 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>377.65</v>
+        <v>1693</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>375.39</v>
+        <v>1681.26</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>359.78</v>
+        <v>1650.03</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>310.8</v>
+        <v>1473.11</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1327.2</v>
+        <v>3061.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1264.01</v>
+        <v>2960.3</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1213.3</v>
+        <v>2833.15</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1103.85</v>
+        <v>2353.09</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>635.9</v>
+        <v>2036.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>556.1799999999999</v>
+        <v>1984.32</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>518.96</v>
+        <v>1883.26</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>527.08</v>
+        <v>1484.17</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C6" s="18" t="n">
-        <v>1693</v>
+        <v>377.65</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1681.26</v>
+        <v>375.39</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>1650.03</v>
+        <v>359.78</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1471.66</v>
+        <v>310.85</v>
       </c>
       <c r="G6" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C7" s="18" t="n">
-        <v>3061.8</v>
+        <v>1327.2</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>2960.3</v>
+        <v>1264.01</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>2833.15</v>
+        <v>1213.3</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>2355.14</v>
+        <v>1104.41</v>
       </c>
       <c r="G7" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C8" s="18" t="n">
-        <v>2036.6</v>
+        <v>635.9</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>1984.32</v>
+        <v>556.1799999999999</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>1883.26</v>
+        <v>518.96</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1483.4</v>
+        <v>527.36</v>
       </c>
       <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
         <v>1783.66</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1622.6</v>
+        <v>1622.25</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1438,7 +1438,7 @@
         <v>1030.59</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>989.22</v>
+        <v>988.05</v>
       </c>
       <c r="G10" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1466,7 +1466,7 @@
         <v>225.85</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>166.73</v>
+        <v>166.94</v>
       </c>
       <c r="G11" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1494,7 +1494,7 @@
         <v>5425.01</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>5344.72</v>
+        <v>5343.39</v>
       </c>
       <c r="G12" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1522,7 +1522,7 @@
         <v>411.13</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>403.74</v>
+        <v>403.86</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
@@ -1550,7 +1550,7 @@
         <v>534.9400000000001</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>531.46</v>
+        <v>532.45</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
@@ -1575,10 +1575,10 @@
         <v>3269.6</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>3166.7</v>
+        <v>3166.71</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>2778.54</v>
+        <v>2782.49</v>
       </c>
       <c r="G15" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
@@ -1606,7 +1606,7 @@
         <v>82</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75.56</v>
+        <v>75.64</v>
       </c>
       <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
@@ -1634,7 +1634,7 @@
         <v>114.17</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>112.22</v>
+        <v>112.43</v>
       </c>
       <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
@@ -1662,7 +1662,7 @@
         <v>4390.41</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>3793.27</v>
+        <v>3794.01</v>
       </c>
       <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
@@ -1690,7 +1690,7 @@
         <v>1320.15</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1051.91</v>
+        <v>1052.35</v>
       </c>
       <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
@@ -1718,7 +1718,7 @@
         <v>286.33</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>279.98</v>
+        <v>279.84</v>
       </c>
       <c r="G20" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
@@ -1746,7 +1746,7 @@
         <v>2372.94</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1631.7</v>
+        <v>1631.11</v>
       </c>
       <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
@@ -1774,7 +1774,7 @@
         <v>1208.5</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>1149.51</v>
+        <v>1153.85</v>
       </c>
       <c r="G22" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
@@ -1802,7 +1802,7 @@
         <v>917.98</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>653.7</v>
+        <v>653.34</v>
       </c>
       <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
@@ -1830,7 +1830,7 @@
         <v>420.93</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>365.03</v>
+        <v>364.67</v>
       </c>
       <c r="G24" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 12-Oct-2026  20:17</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 13-Oct-2026  18:08</t>
         </is>
       </c>
     </row>
@@ -665,135 +665,135 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="F4" s="6" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="E5" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I5" s="11" t="n">
         <v>0.5</v>
-      </c>
-      <c r="I5" s="11" t="n">
-        <v>0.3667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.35</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>6</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G7" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.6</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.3667</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>4</v>
@@ -802,72 +802,72 @@
         <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.25</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.133</v>
+        <v>0.333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.222</v>
+        <v>0.3053</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.2</v>
@@ -876,44 +876,44 @@
         <v>0.2</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -923,94 +923,94 @@
         <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1553</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0833</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>1</v>
@@ -1019,81 +1019,81 @@
         <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.025</v>
+        <v>0.067</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.025</v>
+        <v>0.067</v>
       </c>
       <c r="H15" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.1113</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0667</v>
+        <v>0.0917</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.0833</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,615 +1224,979 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>HATHWAY</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1693</v>
+        <v>11.15</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1681.26</v>
+        <v>9.91</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1650.03</v>
+        <v>10.2</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1473.11</v>
+        <v>11.04</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HATHWAY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>3061.8</v>
+        <v>400.45</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>2960.3</v>
+        <v>377.78</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>2833.15</v>
+        <v>361.38</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>2353.09</v>
+        <v>311.74</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>2036.6</v>
+        <v>1404.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1984.32</v>
+        <v>1277.39</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1883.26</v>
+        <v>1220.8</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1484.17</v>
+        <v>1107.4</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>377.65</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>375.39</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>359.78</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>310.85</v>
-      </c>
-      <c r="G6" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>501.15</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>496.46</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>495.08</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>449.93</v>
+      </c>
+      <c r="G6" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n">
-        <v>1327.2</v>
-      </c>
-      <c r="D7" s="18" t="n">
-        <v>1264.01</v>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>1213.3</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>1104.41</v>
-      </c>
-      <c r="G7" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>636.05</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>563.79</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>523.55</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>528.45</v>
+      </c>
+      <c r="G7" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>635.9</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>556.1799999999999</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>518.96</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>527.36</v>
-      </c>
-      <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>706.95</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>654</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>655.5700000000001</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>620.39</v>
+      </c>
+      <c r="G8" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C9" s="14" t="n">
-        <v>1867.9</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1822.06</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>1783.66</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>1622.25</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="C9" s="18" t="n">
+        <v>1929</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1832.24</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1789.36</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1625.3</v>
+      </c>
+      <c r="G9" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>CYIENT</t>
         </is>
       </c>
-      <c r="C10" s="14" t="n">
-        <v>1158.8</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1089.59</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1030.59</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>988.05</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="C10" s="18" t="n">
+        <v>1175.3</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>1097.75</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1036.26</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>989.92</v>
+      </c>
+      <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>HFCL</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
-        <v>260.4</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>237.65</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>225.85</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>166.94</v>
-      </c>
-      <c r="G11" s="15">
+      <c r="C11" s="18" t="n">
+        <v>262</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>239.97</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>227.27</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>167.88</v>
+      </c>
+      <c r="G11" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>2466.3</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>2311.96</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>2330.96</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>2377.77</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>5770</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>5465.06</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>5425.01</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>5343.39</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="C13" s="18" t="n">
+        <v>5988</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>5514.86</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>5447.08</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>5349.8</v>
+      </c>
+      <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1268.4</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1240.31</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1248.19</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1264.3</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>441</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>420.35</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>411.13</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>403.86</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="C15" s="14" t="n">
+        <v>439</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>422.12</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>412.23</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>LICHSGFIN</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
-        <v>551.65</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>537.47</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>534.9400000000001</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>532.45</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="C16" s="14" t="n">
+        <v>564</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>540</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>536.08</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>532.76</v>
+      </c>
+      <c r="G16" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>3318.2</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>3269.6</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>3166.71</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>2782.49</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>83.16</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>82.08</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>82</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>116.98</v>
+        <v>3308</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>114.75</v>
+        <v>3273.25</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>114.17</v>
+        <v>3172.25</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>112.43</v>
+        <v>2787.72</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>4550</v>
+        <v>1684.6</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>4447.81</v>
+        <v>1681.58</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>4390.41</v>
+        <v>1651.39</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>3794.01</v>
+        <v>1475.22</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>1388.9</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>1371.65</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>1320.15</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>1052.35</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1240</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1200.54</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1197.88</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1229.27</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>291.5</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>288.87</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>286.33</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>279.84</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>3091.1</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2972.76</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>2843.26</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>2360.43</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C21" s="18" t="n">
-        <v>2640.4</v>
+        <v>2059.4</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2625.47</v>
+        <v>1991.47</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>2372.94</v>
+        <v>1890.17</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>1631.11</v>
+        <v>1489.89</v>
       </c>
       <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>664.8</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>659.9299999999999</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>657.29</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>646.1900000000001</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>1111.64</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>927.46</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>658.38</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>841.55</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>829.01</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>841.46</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>840.71</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>82.23999999999999</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>75.72</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>116.55</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>114.92</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>114.27</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1326</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>1242.86</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>1255.58</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>1301.34</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
           <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>KAJARIACER</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>1215.4</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1214.77</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1208.5</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1153.85</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C28" s="18" t="n">
+        <v>1226.7</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>1215.9</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>1209.22</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>1154.58</v>
+      </c>
+      <c r="G28" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1186.6</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1106.57</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>917.98</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>653.34</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>571</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>568.49</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>563.99</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>495.39</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>2185</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>2148.97</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>2104.11</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>1972.98</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>2730</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>2635.43</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>2386.94</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>1642.05</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>720.2</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>682.35</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>662.89</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>574.21</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>4540</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>4456.59</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>4396.28</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>3801.44</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1392</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>1373.59</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>1322.97</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1055.73</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>290</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>288.97</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>286.47</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>279.94</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>159.74</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>158.92</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>140.85</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C24" s="14" t="n">
-        <v>433.6</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>427.96</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>420.93</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>364.67</v>
-      </c>
-      <c r="G24" s="15">
+      <c r="C37" s="14" t="n">
+        <v>442.35</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>429.33</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>421.77</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>365.44</v>
+      </c>
+      <c r="G37" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 13-Oct-2026  18:08</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-Oct-2026  15:52</t>
         </is>
       </c>
     </row>
@@ -675,22 +675,22 @@
         <v>8</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.7</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,202 +703,202 @@
         <v>20</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="F5" s="10" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="G5" s="10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>0.4</v>
-      </c>
       <c r="I5" s="11" t="n">
-        <v>0.5</v>
+        <v>0.5667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.583</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.417</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.3667</v>
+        <v>0.4443</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="F7" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>0.3</v>
-      </c>
       <c r="H7" s="10" t="n">
-        <v>0.6</v>
+        <v>0.267</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3667</v>
+        <v>0.4223</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>0.4</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>0.3333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3053</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>0.2</v>
@@ -907,51 +907,51 @@
         <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2223</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>3</v>
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.2</v>
@@ -969,44 +969,44 @@
         <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.133</v>
+        <v>0.225</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.075</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.275</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.1917</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
@@ -1016,53 +1016,53 @@
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0.067</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.267</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1113</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.05</v>
+        <v>0.067</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.025</v>
+        <v>0.067</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0917</v>
+        <v>0.1113</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0.083</v>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0833</v>
+        <v>0.111</v>
       </c>
     </row>
   </sheetData>
@@ -1229,23 +1229,23 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>HATHWAY</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>11.15</v>
+        <v>405.2</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>9.91</v>
+        <v>382.68</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>10.2</v>
+        <v>364.72</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>11.04</v>
+        <v>313.1</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HATHWAY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1257,23 +1257,23 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>400.45</v>
+        <v>1381</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>377.78</v>
+        <v>1297.96</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>361.38</v>
+        <v>1233.89</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>311.74</v>
+        <v>1113.48</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>1404.5</v>
+        <v>510.6</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1277.39</v>
+        <v>497.96</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>1220.8</v>
+        <v>495.8</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>1107.4</v>
+        <v>451.2</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>501.15</v>
+        <v>653.1</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>496.46</v>
+        <v>577.95</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>495.08</v>
+        <v>532.61</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>449.93</v>
+        <v>529.8</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,79 +1341,79 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>636.05</v>
+        <v>718.25</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>563.79</v>
+        <v>662.76</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>523.55</v>
+        <v>659.0700000000001</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>528.45</v>
+        <v>621.03</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>706.95</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>654</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>655.5700000000001</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>620.39</v>
-      </c>
-      <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n">
+        <v>1928</v>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>1843.28</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>1797.08</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1629.21</v>
+      </c>
+      <c r="G8" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C9" s="18" t="n">
-        <v>1929</v>
+        <v>1195.4</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1832.24</v>
+        <v>1112.06</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>1789.36</v>
+        <v>1046.96</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1625.3</v>
+        <v>992.73</v>
       </c>
       <c r="G9" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>1175.3</v>
+        <v>256.65</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1097.75</v>
+        <v>243.73</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>1036.26</v>
+        <v>229.85</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>989.92</v>
+        <v>169.6</v>
       </c>
       <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>262</v>
+        <v>3613.4</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>239.97</v>
+        <v>3324.38</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>227.27</v>
+        <v>3367.16</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>167.88</v>
+        <v>3534.61</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>2466.3</v>
+        <v>2435.3</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>2311.96</v>
+        <v>2328.22</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2330.96</v>
+        <v>2336.07</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>2377.77</v>
+        <v>2377.71</v>
       </c>
       <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>5988</v>
+        <v>5898</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>5514.86</v>
+        <v>5576.45</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>5447.08</v>
+        <v>5477.87</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>5349.8</v>
+        <v>5360.27</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1530,674 +1530,674 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1268.4</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1240.31</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>1248.19</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1264.3</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>568.1</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>509.25</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>521.55</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>439</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>422.12</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>412.23</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>404.21</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>TATATECH</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>745.55</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>726.59</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>744.14</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>704.92</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>564</v>
+        <v>849.45</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>540</v>
+        <v>829.9</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>536.08</v>
+        <v>840.78</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>532.76</v>
+        <v>839.28</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LICHSGFIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>3308</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>3273.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>3172.25</v>
+        <v>82.14</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>2787.72</v>
+        <v>75.67</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>1684.6</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>1681.58</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>1651.39</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1475.22</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>115.36</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>114.5</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>112.43</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>1240</v>
+        <v>713.85</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1200.54</v>
+        <v>687.1</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>1197.88</v>
+        <v>666.34</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>1229.27</v>
+        <v>576.09</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>4554.1</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>4474.23</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>4408.42</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>3809.16</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1327</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1250.01</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1257.3</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1300.89</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1575.2</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1533.99</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>1544.77</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>1498.83</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>GLAND</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n">
-        <v>3091.1</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>2972.76</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>2843.26</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>2360.43</v>
-      </c>
-      <c r="G20" s="19">
+      <c r="C23" s="18" t="n">
+        <v>3052.3</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>2989.54</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>2860.34</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>2373.74</v>
+      </c>
+      <c r="G23" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>LAURUSLABS</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
-        <v>2059.4</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1991.47</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1890.17</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1489.89</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="C24" s="18" t="n">
+        <v>2036.9</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>2002.41</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1902.65</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1501.35</v>
+      </c>
+      <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C22" s="14" t="n">
-        <v>664.8</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>659.9299999999999</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>657.29</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>646.1900000000001</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C25" s="14" t="n">
+        <v>666.9</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>659.86</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>657.41</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>646.41</v>
+      </c>
+      <c r="G25" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>RAYMOND</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
-        <v>1159.8</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>1111.64</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>927.46</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>658.38</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="C26" s="14" t="n">
+        <v>1186.1</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>1122.73</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>946.29</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>668.29</v>
+      </c>
+      <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>841.55</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>829.01</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>841.46</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>840.71</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>83.73999999999999</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>82.23999999999999</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>82.06</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>75.72</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>116.55</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>114.92</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>114.27</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>112.47</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>1326</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>1242.86</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>1255.58</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>1301.34</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1264.6</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1243.84</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1249.04</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>1263.13</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>1226.7</v>
+        <v>438.05</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>1215.9</v>
+        <v>425.44</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>1209.22</v>
+        <v>414.41</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>1154.58</v>
+        <v>404.93</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>571</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>568.49</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>563.99</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>495.39</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KALYANKJIL","Chart 📈")</f>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>AEGISLOG</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1489.1</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>1390.7</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1334.18</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1063.69</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>2185</v>
+        <v>196.96</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>2148.97</v>
+        <v>195.38</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>2104.11</v>
+        <v>191.21</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>1972.98</v>
+        <v>183.7</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>WELCORP</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>2730</v>
+        <v>292.95</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>2635.43</v>
+        <v>289.48</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>2386.94</v>
+        <v>286.88</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1642.05</v>
+        <v>279.83</v>
       </c>
       <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="C32" s="18" t="n">
-        <v>720.2</v>
+        <v>1224.6</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>682.35</v>
+        <v>1217.51</v>
       </c>
       <c r="E32" s="18" t="n">
-        <v>662.89</v>
+        <v>1210.41</v>
       </c>
       <c r="F32" s="18" t="n">
-        <v>574.21</v>
+        <v>1153.71</v>
       </c>
       <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>4540</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>4456.59</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>4396.28</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>3801.44</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1318.4</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1288.07</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1311.81</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1251.43</v>
+      </c>
+      <c r="G33" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>1392</v>
+        <v>464</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>1373.59</v>
+        <v>433.56</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>1322.97</v>
+        <v>424.11</v>
       </c>
       <c r="F34" s="14" t="n">
-        <v>1055.73</v>
+        <v>366.96</v>
       </c>
       <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>290</v>
+        <v>417</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>288.97</v>
+        <v>415.61</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>286.47</v>
+        <v>416.01</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>279.94</v>
+        <v>413.73</v>
       </c>
       <c r="G35" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C36" s="18" t="n">
-        <v>160</v>
+        <v>2160</v>
       </c>
       <c r="D36" s="18" t="n">
-        <v>159.74</v>
+        <v>2150.98</v>
       </c>
       <c r="E36" s="18" t="n">
-        <v>158.92</v>
+        <v>2108.35</v>
       </c>
       <c r="F36" s="18" t="n">
-        <v>140.85</v>
+        <v>1975.22</v>
       </c>
       <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>442.35</v>
+        <v>159.8</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>429.33</v>
+        <v>159.53</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>421.77</v>
+        <v>158.89</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>365.44</v>
+        <v>141.27</v>
       </c>
       <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 14-Oct-2026  15:52</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-Oct-2026  15:41</t>
         </is>
       </c>
     </row>
@@ -665,29 +665,29 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>0.6333</v>
@@ -696,153 +696,153 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.583</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4443</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.8</v>
+        <v>0.45</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4223</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" s="6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I8" s="7" t="n">
-        <v>0.4</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
         <v>0.3333</v>
@@ -851,69 +851,69 @@
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2333</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.3</v>
+        <v>0.467</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -944,156 +944,156 @@
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.222</v>
+        <v>0.2003</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.225</v>
+        <v>0.167</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1917</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1557</v>
+        <v>0.1387</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.15</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.05</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1113</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0.083</v>
-      </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.111</v>
+        <v>0.1333</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,980 +1224,840 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>405.2</v>
+        <v>1934.3</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>382.68</v>
+        <v>1851.95</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>364.72</v>
+        <v>1802.46</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>313.1</v>
+        <v>1637.64</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1381</v>
+        <v>1189.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1297.96</v>
+        <v>1119.46</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1233.89</v>
+        <v>1052.56</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1113.48</v>
+        <v>992.41</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>510.6</v>
+        <v>243.82</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>497.96</v>
+        <v>243.74</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>495.8</v>
+        <v>230.4</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>451.2</v>
+        <v>170.53</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>653.1</v>
+        <v>3686.8</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>577.95</v>
+        <v>3358.9</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>532.61</v>
+        <v>3379.7</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>529.8</v>
+        <v>3534.62</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>2453.2</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>2340.12</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>2340.67</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>2381.45</v>
+      </c>
+      <c r="G7" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>5840</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>5601.55</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>5492.09</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>5397.2</v>
+      </c>
+      <c r="G8" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>549.85</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>513.11</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>522.66</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>538.99</v>
+      </c>
+      <c r="G9" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>1763.7</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>1691.9</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1717.17</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1743.78</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n">
-        <v>718.25</v>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>662.76</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>659.0700000000001</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>621.03</v>
-      </c>
-      <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n">
-        <v>1928</v>
-      </c>
-      <c r="D8" s="18" t="n">
-        <v>1843.28</v>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>1797.08</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>1629.21</v>
-      </c>
-      <c r="G8" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="n">
-        <v>1195.4</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>1112.06</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>1046.96</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>992.73</v>
-      </c>
-      <c r="G9" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>HFCL</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>256.65</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>243.73</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>229.85</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>169.6</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>3613.4</v>
+        <v>406.7</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>3324.38</v>
+        <v>384.96</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>3367.16</v>
+        <v>366.37</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>3534.61</v>
+        <v>314.05</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>2435.3</v>
+        <v>1381.9</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>2328.22</v>
+        <v>1305.95</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>2336.07</v>
+        <v>1239.69</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>2377.71</v>
+        <v>1115.85</v>
       </c>
       <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>5898</v>
+        <v>629.15</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>5576.45</v>
+        <v>582.83</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>5477.87</v>
+        <v>536.39</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>5360.27</v>
+        <v>530.13</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>568.1</v>
+        <v>684.4</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>509.25</v>
+        <v>664.8200000000001</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>521.55</v>
+        <v>660.0599999999999</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>538.23</v>
+        <v>619.38</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>TATATECH</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>745.55</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>726.59</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>744.14</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>704.92</v>
-      </c>
-      <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATATECH","Chart 📈")</f>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>1260.48</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>1261.33</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>1301.5</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>849.45</v>
+        <v>1650</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>829.9</v>
+        <v>1545.04</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>840.78</v>
+        <v>1548.9</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>839.28</v>
+        <v>1499.61</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>MAHABANK</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>82.14</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>75.67</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>1248.05</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1250.56</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>1262.77</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>115.36</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>112.43</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>1389.4</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1352.17</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1367.23</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>1358.97</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>713.85</v>
+        <v>447.95</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>687.1</v>
+        <v>427.58</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>666.34</v>
+        <v>415.72</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>576.09</v>
+        <v>405.32</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>4554.1</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>4474.23</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>4408.42</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>3809.16</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>3066.3</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>2996.85</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>2868.41</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>2381.95</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1327</v>
+        <v>2018.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>1250.01</v>
+        <v>2003.95</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>1257.3</v>
+        <v>1907.2</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1300.89</v>
+        <v>1506.27</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1575.2</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1533.99</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1544.77</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1498.83</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>670.5</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>660.87</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>657.9299999999999</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>647.92</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>3052.3</v>
+        <v>1917.2</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>2989.54</v>
+        <v>1892.21</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>2860.34</v>
+        <v>1905.46</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>2373.74</v>
+        <v>1842.12</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>2036.9</v>
+        <v>1142.1</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>2002.41</v>
+        <v>1124.58</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1902.65</v>
+        <v>953.97</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1501.35</v>
+        <v>673.74</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>AEGISLOG</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>666.9</v>
+        <v>1410.6</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>659.86</v>
+        <v>1392.59</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>657.41</v>
+        <v>1337.18</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>646.41</v>
+        <v>1067.55</v>
       </c>
       <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>1186.1</v>
+        <v>196.23</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>1122.73</v>
+        <v>195.46</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>946.29</v>
+        <v>191.41</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>668.29</v>
+        <v>184.24</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>1264.6</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>1243.84</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>1249.04</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>1263.13</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>295.2</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>290.02</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>280.21</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>438.05</v>
+        <v>726</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>425.44</v>
+        <v>690.8099999999999</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>414.41</v>
+        <v>668.6799999999999</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>404.93</v>
+        <v>578.1</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1489.1</v>
+        <v>160.66</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>1390.7</v>
+        <v>159.64</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>1334.18</v>
+        <v>158.96</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1063.69</v>
+        <v>141.44</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>196.96</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>195.38</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>191.21</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>183.7</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n">
+        <v>335</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>329.67</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>334.03</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="G30" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>292.95</v>
+        <v>434.25</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>289.48</v>
+        <v>433.63</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>286.88</v>
+        <v>424.51</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>279.83</v>
+        <v>367.91</v>
       </c>
       <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>KAJARIACER</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>1224.6</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>1217.51</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>1210.41</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>1153.71</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KAJARIACER","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>NIFTY ENERGY</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>1318.4</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>1288.07</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>1311.81</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>1251.43</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>464</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>433.56</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>424.11</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>366.96</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>COALINDIA</t>
         </is>
       </c>
-      <c r="C35" s="14" t="n">
-        <v>417</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>415.61</v>
-      </c>
-      <c r="E35" s="14" t="n">
-        <v>416.01</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>413.73</v>
-      </c>
-      <c r="G35" s="15">
+      <c r="C32" s="14" t="n">
+        <v>418</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>415.84</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>416.09</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>414.03</v>
+      </c>
+      <c r="G32" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>2160</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>2150.98</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>2108.35</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>1975.22</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>159.8</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>159.53</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>158.89</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>141.27</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 15-Oct-2026  15:41</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 16-Oct-2026  15:21</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6333</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -706,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>5</v>
@@ -715,13 +715,13 @@
         <v>0.6</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -740,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.5</v>
@@ -749,91 +749,91 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.35</v>
+        <v>0.3167</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>10</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>4</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
         <v>0.4</v>
@@ -842,16 +842,16 @@
         <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" s="11" t="n">
         <v>0.3</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>0.3333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -882,45 +882,45 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.467</v>
+        <v>0.333</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.2777</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>3</v>
@@ -929,7 +929,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.333</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.2</v>
@@ -938,100 +938,100 @@
         <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.2443</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.2003</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.2</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.25</v>
+        <v>0.133</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.2</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1387</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1050,7 +1050,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0.15</v>
@@ -1059,41 +1059,41 @@
         <v>0.05</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.2</v>
+        <v>0.225</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.267</v>
+        <v>0.083</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.083</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1934.3</v>
+        <v>1951.9</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1851.95</v>
+        <v>1861.46</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1802.46</v>
+        <v>1808.32</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1637.64</v>
+        <v>1640.44</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1189.8</v>
+        <v>1194.5</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1119.46</v>
+        <v>1126.61</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1052.56</v>
+        <v>1058.13</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>992.41</v>
+        <v>999.01</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>243.82</v>
+        <v>256.01</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>243.74</v>
+        <v>244.9</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>230.4</v>
+        <v>231.41</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>170.53</v>
+        <v>171.39</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3686.8</v>
+        <v>3714.6</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3358.9</v>
+        <v>3392.77</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3379.7</v>
+        <v>3392.83</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3534.62</v>
+        <v>3541.55</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2453.2</v>
+        <v>2500</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2340.12</v>
+        <v>2355.35</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2340.67</v>
+        <v>2346.92</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2381.45</v>
+        <v>2382.77</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5840</v>
+        <v>5741</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5601.55</v>
+        <v>5614.83</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5492.09</v>
+        <v>5501.86</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5397.2</v>
+        <v>5410.34</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>549.85</v>
+        <v>559.65</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>513.11</v>
+        <v>517.55</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>522.66</v>
+        <v>524.11</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>538.99</v>
+        <v>538.5599999999999</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
@@ -1418,58 +1418,58 @@
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>1763.7</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1691.9</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1717.17</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>1743.78</v>
-      </c>
-      <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TATACOMM","Chart 📈")</f>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>418.15</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>388.12</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>315.08</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>406.7</v>
+        <v>1401</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>384.96</v>
+        <v>1315</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>366.37</v>
+        <v>1246.02</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>314.05</v>
+        <v>1118.37</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>1381.9</v>
+        <v>504</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>1305.95</v>
+        <v>498.08</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1239.69</v>
+        <v>496</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>1115.85</v>
+        <v>451.86</v>
       </c>
       <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>629.15</v>
+        <v>638</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>582.83</v>
+        <v>588.08</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>536.39</v>
+        <v>540.38</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>530.13</v>
+        <v>531.79</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>684.4</v>
+        <v>746.9</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>664.8200000000001</v>
+        <v>672.64</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>660.0599999999999</v>
+        <v>663.47</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>619.38</v>
+        <v>623.25</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1360</v>
+        <v>1380</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1260.48</v>
+        <v>1261.8</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1261.33</v>
+        <v>1255.29</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1301.5</v>
+        <v>1292.44</v>
       </c>
       <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
@@ -1593,471 +1593,611 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>2465</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>2195.95</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>2205.21</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>2385.36</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
-        <v>1650</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>1545.04</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>1548.9</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>1499.61</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C17" s="14" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>1568.37</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>1558.35</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>1502.88</v>
+      </c>
+      <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>1288</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1248.05</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1250.56</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>1262.77</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1389.4</v>
+        <v>1233</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1352.17</v>
+        <v>1208.52</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1367.23</v>
+        <v>1201.81</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>1358.97</v>
+        <v>1227.28</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>3043.4</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>3001.29</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>2875.28</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>2386.94</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>2060.1</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>2009.29</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>1913.19</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>1511.58</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>675</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>662.22</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>658.6</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>649.3</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1133.9</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>1125.46</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>961.03</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>678.85</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>447.95</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>427.58</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>415.72</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>405.32</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>3066.3</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>2996.85</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>2868.41</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>2381.95</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>2018.5</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>2003.95</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1907.2</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1506.27</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n">
-        <v>670.5</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>660.87</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>657.9299999999999</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>647.92</v>
-      </c>
-      <c r="G22" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>1917.2</v>
+        <v>1290</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1892.21</v>
+        <v>1252.04</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>1905.46</v>
+        <v>1252.11</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>1842.12</v>
+        <v>1265.28</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1142.1</v>
+        <v>1397</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1124.58</v>
+        <v>1356.44</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>953.97</v>
+        <v>1368.4</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>673.74</v>
+        <v>1360.91</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>AEGISLOG</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>1410.6</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>1392.59</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>1337.18</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>1067.55</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AEGISLOG","Chart 📈")</f>
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>447.4</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>429.47</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>416.96</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>406.67</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>196.23</v>
+        <v>160</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>195.46</v>
+        <v>159.67</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>191.41</v>
+        <v>159</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>184.24</v>
+        <v>141.84</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>295.2</v>
+        <v>4095.1</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>290.02</v>
+        <v>4034.77</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>287.2</v>
+        <v>4058.96</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>280.21</v>
+        <v>3837.17</v>
       </c>
       <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>854.1</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>832.64</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>841.09</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>839.61</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>116.3</v>
+      </c>
+      <c r="D29" s="18" t="n">
+        <v>115.42</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>114.59</v>
+      </c>
+      <c r="F29" s="18" t="n">
+        <v>112.56</v>
+      </c>
+      <c r="G29" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>197.74</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>191.66</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>184.06</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>293</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>290.31</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>287.43</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>280.26</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
           <t>NIFTY FMCG</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>BALRAMCHIN</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n">
-        <v>726</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>690.8099999999999</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>668.6799999999999</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>578.1</v>
-      </c>
-      <c r="G28" s="19">
+      <c r="C32" s="18" t="n">
+        <v>721.15</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>693.7</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>670.74</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>579.37</v>
+      </c>
+      <c r="G32" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>160.66</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>159.64</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>158.96</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>141.44</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>4473.4</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>4471.98</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>4412.5</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>3829.35</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>2152.7</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <v>2150.11</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <v>2111.24</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>1978.85</v>
+      </c>
+      <c r="G34" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>434.6</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>433.72</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>424.91</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>368.6</v>
+      </c>
+      <c r="G35" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n">
+        <v>417.2</v>
+      </c>
+      <c r="D36" s="18" t="n">
+        <v>415.97</v>
+      </c>
+      <c r="E36" s="18" t="n">
+        <v>416.13</v>
+      </c>
+      <c r="F36" s="18" t="n">
+        <v>414.32</v>
+      </c>
+      <c r="G36" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C30" s="18" t="n">
-        <v>335</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>329.67</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>334.03</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>307.89</v>
-      </c>
-      <c r="G30" s="19">
+      <c r="C37" s="14" t="n">
+        <v>338</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>330.46</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>334.19</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>308.03</v>
+      </c>
+      <c r="G37" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>434.25</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>433.63</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>424.51</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>367.91</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>418</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>415.84</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>416.09</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>414.03</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
         <v/>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 16-Oct-2026  15:21</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-Oct-2026  17:29</t>
         </is>
       </c>
     </row>
@@ -675,22 +675,22 @@
         <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.6167</v>
+        <v>0.5832999999999999</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>5</v>
@@ -712,7 +712,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.5</v>
@@ -721,131 +721,131 @@
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.4722999999999999</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3167</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F8" s="6" t="n">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3</v>
+        <v>0.2833</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H9" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="H9" s="10" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I9" s="11" t="n">
-        <v>0.3</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,100 +858,100 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.289</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.133</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.2777</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2443</v>
+        <v>0.1833</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2</v>
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.4</v>
+        <v>0.267</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.133</v>
@@ -969,44 +969,44 @@
         <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.222</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" s="6" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H14" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <v>0.133</v>
-      </c>
       <c r="I14" s="7" t="n">
-        <v>0.222</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
@@ -1016,22 +1016,22 @@
         <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.267</v>
+        <v>0.133</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
@@ -1044,25 +1044,25 @@
         <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="F16" s="6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H16" s="6" t="n">
         <v>0.15</v>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>0.225</v>
-      </c>
       <c r="I16" s="7" t="n">
-        <v>0.1417</v>
+        <v>0.0833</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1951.9</v>
+        <v>1925</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1861.46</v>
+        <v>1867.52</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1808.32</v>
+        <v>1812.9</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1640.44</v>
+        <v>1642.11</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1194.5</v>
+        <v>1172.4</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1126.61</v>
+        <v>1130.97</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1058.13</v>
+        <v>1062.61</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>999.01</v>
+        <v>1002</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>256.01</v>
+        <v>268.81</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>244.9</v>
+        <v>247.18</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>231.41</v>
+        <v>232.87</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>171.39</v>
+        <v>172.29</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3714.6</v>
+        <v>3611.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3392.77</v>
+        <v>3413.59</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3392.83</v>
+        <v>3401.4</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3541.55</v>
+        <v>3542.52</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
@@ -1348,13 +1348,13 @@
         <v>2500</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2355.35</v>
+        <v>2369.12</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2346.92</v>
+        <v>2352.92</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2382.77</v>
+        <v>2381.04</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5741</v>
+        <v>5690</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5614.83</v>
+        <v>5621.99</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5501.86</v>
+        <v>5509.24</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5410.34</v>
+        <v>5413.46</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>559.65</v>
+        <v>552.35</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>517.55</v>
+        <v>520.86</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>524.11</v>
+        <v>525.21</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>538.5599999999999</v>
+        <v>532.84</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>418.15</v>
+        <v>404.2</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>388.12</v>
+        <v>389.66</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>368.4</v>
+        <v>369.8</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>315.08</v>
+        <v>316.63</v>
       </c>
       <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>1401</v>
+        <v>1402.1</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1315</v>
+        <v>1323.3</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>1246.02</v>
+        <v>1252.14</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1118.37</v>
+        <v>1126.26</v>
       </c>
       <c r="G11" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>504</v>
+        <v>510.15</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>498.08</v>
+        <v>499.23</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>496</v>
+        <v>496.56</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>451.86</v>
+        <v>452.17</v>
       </c>
       <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>638</v>
+        <v>639.95</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>588.08</v>
+        <v>593.02</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>540.38</v>
+        <v>544.28</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>531.79</v>
+        <v>532.41</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>746.9</v>
+        <v>771.7</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>672.64</v>
+        <v>682.0700000000001</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>663.47</v>
+        <v>667.72</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>623.25</v>
+        <v>623.1</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
@@ -1560,308 +1560,308 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1380</v>
+        <v>856.85</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1261.8</v>
+        <v>834.95</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1255.29</v>
+        <v>841.71</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1292.44</v>
+        <v>843.3200000000001</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2465</v>
+        <v>121.9</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2195.95</v>
+        <v>116.04</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2205.21</v>
+        <v>114.88</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2385.36</v>
+        <v>112.82</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1790</v>
+        <v>180.7</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1568.37</v>
+        <v>174.34</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>1558.35</v>
+        <v>175.82</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1502.88</v>
+        <v>169.18</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1233</v>
+        <v>1379.9</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1208.52</v>
+        <v>1273.05</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1201.81</v>
+        <v>1260.18</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>1227.28</v>
+        <v>1292.71</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>3043.4</v>
+        <v>2460.9</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>3001.29</v>
+        <v>2221.19</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2875.28</v>
+        <v>2215.24</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>2386.94</v>
+        <v>2389.72</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>2060.1</v>
+        <v>1779.1</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2009.29</v>
+        <v>1588.44</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1913.19</v>
+        <v>1567.01</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1511.58</v>
+        <v>1505.3</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>675</v>
+        <v>1242.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>662.22</v>
+        <v>1211.75</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>658.6</v>
+        <v>1203.41</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>649.3</v>
+        <v>1230.93</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>3019.8</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>3003.05</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>2880.94</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>2393.83</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>2069</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>2014.98</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1919.31</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1521.14</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1133.9</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1125.46</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>961.03</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>678.85</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n">
-        <v>1290</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1252.04</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1252.11</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1265.28</v>
-      </c>
-      <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AXISBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C24" s="18" t="n">
-        <v>1397</v>
+        <v>672.85</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1356.44</v>
+        <v>663.23</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1368.4</v>
+        <v>659.16</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1360.91</v>
+        <v>649.89</v>
       </c>
       <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="C25" s="18" t="n">
-        <v>447.4</v>
+        <v>1130.6</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>429.47</v>
+        <v>1125.95</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>416.96</v>
+        <v>967.67</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>406.67</v>
+        <v>682.33</v>
       </c>
       <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1873,330 +1873,190 @@
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>160</v>
+        <v>4074</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>159.67</v>
+        <v>4038.5</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>159</v>
+        <v>4059.55</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>141.84</v>
+        <v>3845.82</v>
       </c>
       <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>4095.1</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>4034.77</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>4058.96</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>3837.17</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>1381</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>1358.78</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>1368.89</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>1358.83</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>854.1</v>
+        <v>442.3</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>832.64</v>
+        <v>430.69</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>841.09</v>
+        <v>417.96</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>839.61</v>
+        <v>407.17</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n">
-        <v>116.3</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <v>115.42</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <v>114.59</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <v>112.56</v>
-      </c>
-      <c r="G29" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>196.79</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>195.78</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>191.86</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>197.74</v>
+        <v>293.65</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>195.68</v>
+        <v>290.63</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>191.66</v>
+        <v>287.68</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>184.06</v>
+        <v>280.42</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>293</v>
-      </c>
-      <c r="D31" s="14" t="n">
-        <v>290.31</v>
-      </c>
-      <c r="E31" s="14" t="n">
-        <v>287.43</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>280.26</v>
-      </c>
-      <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>701.85</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>694.47</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>671.96</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>579.9299999999999</v>
+      </c>
+      <c r="G31" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>721.15</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>693.7</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>670.74</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>579.37</v>
-      </c>
-      <c r="G32" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>RADICO</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>4473.4</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>4471.98</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>4412.5</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>3829.35</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RADICO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>2152.7</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>2150.11</v>
-      </c>
-      <c r="E34" s="14" t="n">
-        <v>2111.24</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>1978.85</v>
-      </c>
-      <c r="G34" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>434.6</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>433.72</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>424.91</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>368.6</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BHEL","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>COALINDIA</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>417.2</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>415.97</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>416.13</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>414.32</v>
-      </c>
-      <c r="G36" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COALINDIA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C37" s="14" t="n">
-        <v>338</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>330.46</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>334.19</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>308.03</v>
-      </c>
-      <c r="G37" s="15">
+      <c r="C32" s="14" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>332.21</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>334.76</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>309.5</v>
+      </c>
+      <c r="G32" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 19-Oct-2026  17:29</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-Oct-2026  15:43</t>
         </is>
       </c>
     </row>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 20-Oct-2026  15:43</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-Oct-2026  16:02</t>
         </is>
       </c>
     </row>
@@ -672,25 +672,25 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.5832999999999999</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -727,63 +727,63 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.417</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4722999999999999</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.361</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
@@ -796,19 +796,19 @@
         <v>20</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>10</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>0.5</v>
@@ -827,7 +827,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>2</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.2</v>
@@ -845,13 +845,13 @@
         <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2667</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
@@ -882,63 +882,63 @@
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.15</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.15</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.222</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.15</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>0.1833</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -951,7 +951,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>2</v>
@@ -960,7 +960,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.267</v>
+        <v>0.067</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>0.133</v>
@@ -969,131 +969,131 @@
         <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1777</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.025</v>
+        <v>0.067</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.15</v>
+        <v>0.133</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0833</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.083</v>
+        <v>0.025</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1925</v>
+        <v>1951</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1867.52</v>
+        <v>1875.47</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1812.9</v>
+        <v>1818.31</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1642.11</v>
+        <v>1644.69</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1172.4</v>
+        <v>1169.7</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1130.97</v>
+        <v>1134.66</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1062.61</v>
+        <v>1066.81</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1002</v>
+        <v>1003.26</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>268.81</v>
+        <v>264.78</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>247.18</v>
+        <v>248.86</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>232.87</v>
+        <v>234.12</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>172.29</v>
+        <v>173.27</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3611.3</v>
+        <v>3996.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3413.59</v>
+        <v>3469.08</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3401.4</v>
+        <v>3424.73</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3542.52</v>
+        <v>3547.47</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2500</v>
+        <v>2575</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2369.12</v>
+        <v>2388.73</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2352.92</v>
+        <v>2361.63</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2381.04</v>
+        <v>2382.41</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5690</v>
+        <v>5858.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5621.99</v>
+        <v>5644.51</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5509.24</v>
+        <v>5522.93</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5413.46</v>
+        <v>5414.14</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>552.35</v>
+        <v>562.1</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>520.86</v>
+        <v>524.79</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>525.21</v>
+        <v>526.66</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>532.84</v>
+        <v>533.21</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>404.2</v>
+        <v>398.9</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>389.66</v>
+        <v>390.54</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>369.8</v>
+        <v>370.94</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>316.63</v>
+        <v>317.7</v>
       </c>
       <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>1402.1</v>
+        <v>1417.9</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1323.3</v>
+        <v>1332.31</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>1252.14</v>
+        <v>1258.64</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1126.26</v>
+        <v>1128.91</v>
       </c>
       <c r="G11" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
@@ -1485,16 +1485,16 @@
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>510.15</v>
+        <v>510.4</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>499.23</v>
+        <v>500.29</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>496.56</v>
+        <v>497.1</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>452.17</v>
+        <v>452.85</v>
       </c>
       <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>639.95</v>
+        <v>627.15</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>593.02</v>
+        <v>596.27</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>544.28</v>
+        <v>547.53</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>532.41</v>
+        <v>533.59</v>
       </c>
       <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
@@ -1541,16 +1541,16 @@
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>771.7</v>
+        <v>748</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>682.0700000000001</v>
+        <v>688.35</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>667.72</v>
+        <v>670.86</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>623.1</v>
+        <v>625.33</v>
       </c>
       <c r="G14" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
@@ -1560,168 +1560,168 @@
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>856.85</v>
+        <v>1424.2</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>834.95</v>
+        <v>1287.45</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>841.71</v>
+        <v>1266.61</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>843.3200000000001</v>
+        <v>1293.26</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>121.9</v>
+        <v>2529</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>116.04</v>
+        <v>2250.5</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>114.88</v>
+        <v>2227.54</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>112.82</v>
+        <v>2390.42</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>180.7</v>
+        <v>1834.7</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>174.34</v>
+        <v>1611.89</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>175.82</v>
+        <v>1577.51</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>169.18</v>
+        <v>1508.93</v>
       </c>
       <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>1379.9</v>
+        <v>859</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1273.05</v>
+        <v>837.24</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>1260.18</v>
+        <v>842.39</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>1292.71</v>
+        <v>843.4299999999999</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>2460.9</v>
+        <v>122.5</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2221.19</v>
+        <v>116.65</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>2215.24</v>
+        <v>115.18</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>2389.72</v>
+        <v>112.88</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C20" s="18" t="n">
-        <v>1779.1</v>
+        <v>182</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1588.44</v>
+        <v>175.07</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1567.01</v>
+        <v>176.06</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1505.3</v>
+        <v>169.34</v>
       </c>
       <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1242.5</v>
+        <v>1244.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>1211.75</v>
+        <v>1214.87</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>1203.41</v>
+        <v>1205.02</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1230.93</v>
+        <v>1231.63</v>
       </c>
       <c r="G21" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1761,302 +1761,190 @@
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>GLAND</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>3019.8</v>
+        <v>1918.9</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>3003.05</v>
+        <v>1914.07</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>2880.94</v>
+        <v>1896.03</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>2393.83</v>
+        <v>1693.45</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>2069</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>2014.98</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1919.31</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>1521.14</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>664</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>663.3</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>659.35</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>649.85</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>672.85</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>663.23</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>659.16</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>649.89</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>CASTROLIND</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>196.19</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>195.82</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>192.03</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>184.35</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>RAYMOND</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>1130.6</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>1125.95</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>967.67</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>682.33</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>295</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>291.04</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>287.96</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>280.53</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>4074</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>4038.5</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>4059.55</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>3845.82</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>1385</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1361.27</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1369.52</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>1358.4</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>1381</v>
+        <v>437.8</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1358.78</v>
+        <v>431.37</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>1368.89</v>
+        <v>418.74</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>1358.83</v>
+        <v>407.19</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>442.3</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>430.69</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>417.96</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>407.17</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>196.79</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>195.78</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>191.86</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>293.65</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>290.63</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>287.68</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>280.42</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>BALRAMCHIN</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>701.85</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>694.47</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>671.96</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>579.9299999999999</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BALRAMCHIN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C32" s="14" t="n">
-        <v>348.85</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>332.21</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>334.76</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>309.5</v>
-      </c>
-      <c r="G32" s="15">
+      <c r="C28" s="14" t="n">
+        <v>344</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>335.13</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>309.88</v>
+      </c>
+      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 21-Oct-2026  16:02</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Oct-2026  15:57</t>
         </is>
       </c>
     </row>
@@ -675,19 +675,19 @@
         <v>12</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="I4" s="7" t="n">
         <v>0.5</v>
@@ -703,7 +703,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>5</v>
@@ -712,7 +712,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.5</v>
@@ -721,7 +721,7 @@
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
@@ -765,87 +765,87 @@
         <v>12</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.417</v>
+        <v>0.583</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="10" t="n">
         <v>0.333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.361</v>
+        <v>0.3887</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2833</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
@@ -867,7 +867,7 @@
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>0.133</v>
@@ -876,7 +876,7 @@
         <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -913,38 +913,38 @@
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F12" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>0.067</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="H12" s="6" t="n">
         <v>0.133</v>
       </c>
-      <c r="H12" s="6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>0.1333</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
@@ -954,47 +954,47 @@
         <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.067</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.111</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>0.067</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
         <v>0.2</v>
@@ -1047,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>2</v>
@@ -1056,13 +1056,13 @@
         <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0667</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,22 +1075,22 @@
         <v>40</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.075</v>
+        <v>0.05</v>
       </c>
       <c r="I17" s="11" t="n">
         <v>0.025</v>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1951</v>
+        <v>1908.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1875.47</v>
+        <v>1878.64</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1818.31</v>
+        <v>1821.86</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1644.69</v>
+        <v>1648.43</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1169.7</v>
+        <v>1143.7</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1134.66</v>
+        <v>1135.52</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1066.81</v>
+        <v>1069.83</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1003.26</v>
+        <v>1006.41</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>264.78</v>
+        <v>251.55</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>248.86</v>
+        <v>249.11</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>234.12</v>
+        <v>234.81</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>173.27</v>
+        <v>174.01</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3996.3</v>
+        <v>3954.8</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3469.08</v>
+        <v>3515.34</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3424.73</v>
+        <v>3445.52</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3547.47</v>
+        <v>3551.42</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2575</v>
+        <v>2499.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2388.73</v>
+        <v>2399.28</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2361.63</v>
+        <v>2367.04</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2382.41</v>
+        <v>2388.39</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5858.5</v>
+        <v>5740.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5644.51</v>
+        <v>5653.66</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5522.93</v>
+        <v>5531.47</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5414.14</v>
+        <v>5420.4</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>562.1</v>
+        <v>581.3</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>524.79</v>
+        <v>530.17</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>526.66</v>
+        <v>528.8</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>533.21</v>
+        <v>532.4400000000001</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>398.9</v>
+        <v>1419.9</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>390.54</v>
+        <v>1340.65</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>370.94</v>
+        <v>1264.97</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>317.7</v>
+        <v>1131.94</v>
       </c>
       <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>1417.9</v>
+        <v>508.9</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1332.31</v>
+        <v>501.11</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>1258.64</v>
+        <v>497.56</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1128.91</v>
+        <v>453.07</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,23 +1481,23 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C12" s="18" t="n">
-        <v>510.4</v>
+        <v>600.3</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>500.29</v>
+        <v>596.66</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>497.1</v>
+        <v>549.6</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>452.85</v>
+        <v>534.36</v>
       </c>
       <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1509,79 +1509,79 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C13" s="18" t="n">
-        <v>627.15</v>
+        <v>723.25</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>596.27</v>
+        <v>686.26</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>547.53</v>
+        <v>667.3200000000001</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>533.59</v>
+        <v>621.6799999999999</v>
       </c>
       <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="n">
-        <v>748</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>688.35</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>670.86</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>625.33</v>
-      </c>
-      <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1421.7</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1300.23</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1272.69</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1297.6</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1424.2</v>
+        <v>2506.9</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>1287.45</v>
+        <v>2274.92</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>1266.61</v>
+        <v>2238.5</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1293.26</v>
+        <v>2396.97</v>
       </c>
       <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1593,79 +1593,79 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>2529</v>
+        <v>1829.1</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2250.5</v>
+        <v>1632.58</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2227.54</v>
+        <v>1587.38</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>2390.42</v>
+        <v>1513.33</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>1834.7</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>1611.89</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>1577.51</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>1508.93</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>855.7</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>839</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>842.91</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>844.62</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C18" s="18" t="n">
-        <v>859</v>
+        <v>122.5</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>837.24</v>
+        <v>117.21</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>842.39</v>
+        <v>115.46</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>843.4299999999999</v>
+        <v>113.02</v>
       </c>
       <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1677,274 +1677,190 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C19" s="18" t="n">
-        <v>122.5</v>
+        <v>182.85</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>116.65</v>
+        <v>175.81</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>115.18</v>
+        <v>176.33</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>112.88</v>
+        <v>169.57</v>
       </c>
       <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>182</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>175.07</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>176.06</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>169.34</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1909.9</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1892.05</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1903.39</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1845.33</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>DRREDDY</t>
         </is>
       </c>
-      <c r="C21" s="14" t="n">
-        <v>1244.5</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>1214.87</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>1205.02</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>1231.63</v>
-      </c>
-      <c r="G21" s="15">
+      <c r="C21" s="18" t="n">
+        <v>1239</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>1217.17</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>1206.35</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>1230.92</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>1918.9</v>
+        <v>197.38</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>1914.07</v>
+        <v>195.97</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>1896.03</v>
+        <v>192.24</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>1693.45</v>
+        <v>184.47</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C23" s="18" t="n">
-        <v>664</v>
+        <v>1398.5</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>663.3</v>
+        <v>1364.82</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>659.35</v>
+        <v>1370.66</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>649.85</v>
+        <v>1357.26</v>
       </c>
       <c r="G23" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>196.19</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>195.82</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>192.03</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>184.35</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>437</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>431.91</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>419.45</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>407.97</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>295</v>
+        <v>347.8</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>291.04</v>
+        <v>334.71</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>287.96</v>
+        <v>335.62</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>280.53</v>
+        <v>310.29</v>
       </c>
       <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1385</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1361.27</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1369.52</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>1358.4</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>437.8</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>431.37</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>418.74</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>407.19</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>344</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>333.34</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>335.13</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>309.88</v>
-      </c>
-      <c r="G28" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 22-Oct-2026  15:57</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 23-Oct-2026  15:48</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>11</v>
@@ -681,7 +681,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.55</v>
@@ -690,162 +690,162 @@
         <v>0.35</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
         <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4667</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F6" s="6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.3</v>
-      </c>
       <c r="I6" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.583</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.3887</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.167</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.167</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="E9" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,25 +858,25 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="F10" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="H10" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.267</v>
-      </c>
       <c r="I10" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1113</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -889,155 +889,155 @@
         <v>20</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.15</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.111</v>
+        <v>0.08900000000000001</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.083</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>3</v>
-      </c>
       <c r="F14" s="6" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="H14" s="6" t="n">
         <v>0.067</v>
       </c>
-      <c r="H14" s="6" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I14" s="7" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.0447</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.083</v>
+        <v>0.0443</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1075,25 +1075,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.05</v>
+        <v>0.025</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.025</v>
+        <v>0.0083</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1908.8</v>
+        <v>1900.5</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1878.64</v>
+        <v>1880.72</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1821.86</v>
+        <v>1824.95</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1648.43</v>
+        <v>1650.94</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1143.7</v>
+        <v>1233</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1135.52</v>
+        <v>1144.8</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1069.83</v>
+        <v>1076.23</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1006.41</v>
+        <v>1008.66</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>251.55</v>
+        <v>3910.3</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>249.11</v>
+        <v>3552.96</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>234.81</v>
+        <v>3463.74</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>174.01</v>
+        <v>3554.99</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3954.8</v>
+        <v>2480</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3515.34</v>
+        <v>2406.97</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3445.52</v>
+        <v>2371.47</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3551.42</v>
+        <v>2389.3</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2499.5</v>
+        <v>5727.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2399.28</v>
+        <v>5660.69</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2367.04</v>
+        <v>5539.15</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2388.39</v>
+        <v>5423.45</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,498 +1369,330 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5740.5</v>
+        <v>557.15</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5653.66</v>
+        <v>532.74</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5531.47</v>
+        <v>529.91</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5420.4</v>
+        <v>532.6799999999999</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>581.3</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>530.17</v>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>528.8</v>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>532.4400000000001</v>
-      </c>
-      <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>1422.2</v>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>1311.85</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>1278.56</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1298.84</v>
+      </c>
+      <c r="G9" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>2530</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>2299.21</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>2249.93</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>2398.29</v>
+      </c>
+      <c r="G10" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>1635.46</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>1582.81</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1503.79</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>402.15</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>391.42</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>319</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>PVRINOX</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
-        <v>1419.9</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>1340.65</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>1264.97</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>1131.94</v>
-      </c>
-      <c r="G10" s="19">
+      <c r="C13" s="14" t="n">
+        <v>1395.7</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1345.89</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>1270.09</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1134.56</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>501.11</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>497.56</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>453.07</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>600.3</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>596.66</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>549.6</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>534.36</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>723.25</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>686.26</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>667.3200000000001</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>621.6799999999999</v>
-      </c>
-      <c r="G13" s="19">
+      <c r="C14" s="14" t="n">
+        <v>717.05</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>689.1900000000001</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>669.27</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>622.63</v>
+      </c>
+      <c r="G14" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>HCLTECH</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1421.7</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1300.23</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>1272.69</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1297.6</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>1953.3</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>1916.9</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>1898.56</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>1697.73</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>2506.9</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>2274.92</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>2238.5</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>2396.97</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1829.1</v>
+        <v>120.37</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1632.58</v>
+        <v>117.51</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>1587.38</v>
+        <v>115.66</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>1513.33</v>
+        <v>113.1</v>
       </c>
       <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>855.7</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>839</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>842.91</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>844.62</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>117.21</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>115.46</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>113.02</v>
-      </c>
-      <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n">
-        <v>182.85</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>175.81</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>176.33</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>169.57</v>
-      </c>
-      <c r="G19" s="19">
+      <c r="C17" s="14" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>176.43</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>169.66</v>
+      </c>
+      <c r="G17" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1909.9</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>1892.05</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>1903.39</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>1845.33</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="n">
-        <v>1239</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>1217.17</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>1206.35</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>1230.92</v>
-      </c>
-      <c r="G21" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>CASTROLIND</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>197.38</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>195.97</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>192.24</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>184.47</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CASTROLIND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n">
-        <v>1398.5</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>1364.82</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>1370.66</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>1357.26</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="C18" s="18" t="n">
+        <v>1394.2</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1367.62</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1371.58</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>1357.63</v>
+      </c>
+      <c r="G18" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n">
-        <v>437</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>431.91</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>419.45</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>407.97</v>
-      </c>
-      <c r="G24" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
-        <v>347.8</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>334.71</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>335.62</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>310.29</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="C19" s="14" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>335.3</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>310.59</v>
+      </c>
+      <c r="G19" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 23-Oct-2026  15:48</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 26-Oct-2026  17:19</t>
         </is>
       </c>
     </row>
@@ -678,7 +678,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>0.55</v>
@@ -687,10 +687,10 @@
         <v>0.55</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.4833</v>
+        <v>0.5167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -765,56 +765,56 @@
         <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.167</v>
+        <v>0.333</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.167</v>
+        <v>0.067</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.167</v>
+        <v>0.267</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.167</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,180 +827,180 @@
         <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.1113</v>
+        <v>0.167</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.05</v>
+        <v>0.067</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.1</v>
+        <v>0.067</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.15</v>
+        <v>0.267</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.067</v>
+        <v>0.1</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.08900000000000001</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.083</v>
+        <v>0.2</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.083</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0447</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
@@ -1037,7 +1037,7 @@
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0443</v>
+        <v>0.0223</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="10" t="n">
         <v>0</v>
@@ -1090,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0083</v>
+        <v>0.0167</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1900.5</v>
+        <v>1993</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1880.72</v>
+        <v>1891.42</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1824.95</v>
+        <v>1831.54</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1650.94</v>
+        <v>1660.71</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1233</v>
+        <v>1242.9</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1144.8</v>
+        <v>1154.14</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1076.23</v>
+        <v>1082.77</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1008.66</v>
+        <v>1012.05</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>3910.3</v>
+        <v>389</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>3552.96</v>
+        <v>380.21</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>3463.74</v>
+        <v>379.8</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>3554.99</v>
+        <v>387.28</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1313,23 +1313,23 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>2480</v>
+        <v>4035.6</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>2406.97</v>
+        <v>3598.92</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>2371.47</v>
+        <v>3486.17</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>2389.3</v>
+        <v>3560.54</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1341,23 +1341,23 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>5727.5</v>
+        <v>2557.6</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>5660.69</v>
+        <v>2421.31</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>5539.15</v>
+        <v>2378.77</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>5423.45</v>
+        <v>2398.33</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1369,79 +1369,79 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>5678.72</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <v>5551.35</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>5431.25</v>
+      </c>
+      <c r="G8" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
           <t>TANLA</t>
         </is>
       </c>
-      <c r="C8" s="14" t="n">
-        <v>557.15</v>
-      </c>
-      <c r="D8" s="14" t="n">
-        <v>532.74</v>
-      </c>
-      <c r="E8" s="14" t="n">
-        <v>529.91</v>
-      </c>
-      <c r="F8" s="14" t="n">
-        <v>532.6799999999999</v>
-      </c>
-      <c r="G8" s="15">
+      <c r="C9" s="14" t="n">
+        <v>567.8</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>536.08</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>531.4</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>532.59</v>
+      </c>
+      <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>1422.2</v>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>1311.85</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>1278.56</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>1298.84</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="C10" s="18" t="n">
+        <v>1417</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>1321.86</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>1283.99</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1300.79</v>
+      </c>
+      <c r="G10" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="n">
-        <v>2530</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>2299.21</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>2249.93</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>2398.29</v>
-      </c>
-      <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,79 +1453,79 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>2535</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>2321.67</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>2261.11</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>2400.61</v>
+      </c>
+      <c r="G11" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
-        <v>1790</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1635.46</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>1582.81</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>1503.79</v>
-      </c>
-      <c r="G11" s="19">
+      <c r="C12" s="18" t="n">
+        <v>1795</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>1650.65</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>1591.14</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>1506.65</v>
+      </c>
+      <c r="G12" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>402.15</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>391.42</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>372.81</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>319</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="C13" s="14" t="n">
+        <v>400.25</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>392.26</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>373.88</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>319.29</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1395.7</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1345.89</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>1270.09</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>1134.56</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,162 +1537,358 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1404.7</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>1351.49</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1275.37</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>1139.17</v>
+      </c>
+      <c r="G14" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n">
-        <v>717.05</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>689.1900000000001</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>669.27</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>622.63</v>
-      </c>
-      <c r="G14" s="15">
+      <c r="C15" s="14" t="n">
+        <v>716.9</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>691.83</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>671.14</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>624</v>
+      </c>
+      <c r="G15" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>NIFTY PHARMA</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>1310.9</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>1227.16</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1211.33</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>1232.11</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>IPCALAB</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
-        <v>1953.3</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>1916.9</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>1898.56</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>1697.73</v>
-      </c>
-      <c r="G15" s="19">
+      <c r="C17" s="18" t="n">
+        <v>1938.6</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>1918.97</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>1900.13</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>1701.94</v>
+      </c>
+      <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>2058.9</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>2014.14</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>1932.94</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>1541.98</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>1160.4</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1138.84</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>1137.34</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1067.37</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY OIL &amp; GAS</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>291.75</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>290.65</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>288.14</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>280.91</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C16" s="14" t="n">
-        <v>120.37</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>117.51</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>115.66</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>113.1</v>
-      </c>
-      <c r="G16" s="15">
+      <c r="C21" s="18" t="n">
+        <v>120.89</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>117.83</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <v>115.86</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="G21" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="C17" s="14" t="n">
-        <v>178.9</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>176.1</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>176.43</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>169.66</v>
-      </c>
-      <c r="G17" s="15">
+      <c r="C22" s="18" t="n">
+        <v>181.2</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>176.59</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>176.62</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>169.95</v>
+      </c>
+      <c r="G22" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>1225.65</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>1246.89</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1235.34</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>1394.2</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>1367.62</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>1371.58</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1357.63</v>
-      </c>
-      <c r="G18" s="19">
+      <c r="C24" s="18" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1370.99</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1372.81</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1359.23</v>
+      </c>
+      <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>440.75</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>432.63</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>420.7</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>407.22</v>
+      </c>
+      <c r="G25" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C19" s="14" t="n">
-        <v>340.9</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>335.3</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>335.83</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>310.59</v>
-      </c>
-      <c r="G19" s="15">
+      <c r="C26" s="14" t="n">
+        <v>344.4</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>336.17</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>336.17</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>311.45</v>
+      </c>
+      <c r="G26" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 26-Oct-2026  17:19</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 27-Oct-2026  16:22</t>
         </is>
       </c>
     </row>
@@ -672,31 +672,31 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="7" t="n">
         <v>0.55</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>0.5167</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -709,7 +709,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
         <v>0.5</v>
@@ -718,51 +718,51 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>5</v>
@@ -771,298 +771,298 @@
         <v>5</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.35</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.067</v>
+        <v>0.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.167</v>
+        <v>0.467</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.167</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.167</v>
+        <v>0.289</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.067</v>
+        <v>0.333</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.067</v>
+        <v>0.167</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1337</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.15</v>
+        <v>0.267</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.1167</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.133</v>
+        <v>0.1</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.111</v>
+        <v>0.1333</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.083</v>
+        <v>0.08869999999999999</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.0443</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.133</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0223</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I17" s="11" t="n">
         <v>0.05</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>0.0167</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1993</v>
+        <v>1997</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1891.42</v>
+        <v>1901.47</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1831.54</v>
+        <v>1838.03</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1660.71</v>
+        <v>1664.06</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1242.9</v>
+        <v>1182.3</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1154.14</v>
+        <v>1156.83</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1082.77</v>
+        <v>1086.67</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1012.05</v>
+        <v>1013.74</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>389</v>
+        <v>250.11</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>380.21</v>
+        <v>248.12</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>379.8</v>
+        <v>235.97</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>387.28</v>
+        <v>176.12</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDUSTOWER","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4035.6</v>
+        <v>4174.2</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3598.92</v>
+        <v>3637.57</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3486.17</v>
+        <v>3496.55</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3560.54</v>
+        <v>3549.17</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2557.6</v>
+        <v>2618.4</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2421.31</v>
+        <v>2440.08</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2378.77</v>
+        <v>2388.17</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2398.33</v>
+        <v>2400.52</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
@@ -1373,16 +1373,16 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5850</v>
+        <v>5832.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5678.72</v>
+        <v>5693.36</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5551.35</v>
+        <v>5562.37</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5431.25</v>
+        <v>5435.24</v>
       </c>
       <c r="G8" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
@@ -1401,16 +1401,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>567.8</v>
+        <v>579.15</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>536.08</v>
+        <v>540.1799999999999</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>531.4</v>
+        <v>533.27</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>532.59</v>
+        <v>533.05</v>
       </c>
       <c r="G9" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
@@ -1420,475 +1420,755 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C10" s="18" t="n">
-        <v>1417</v>
+        <v>401.3</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1321.86</v>
+        <v>393.12</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>1283.99</v>
+        <v>374.96</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>1300.79</v>
+        <v>320.1</v>
       </c>
       <c r="G10" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C11" s="18" t="n">
-        <v>2535</v>
+        <v>1464</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>2321.67</v>
+        <v>1362.21</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>2261.11</v>
+        <v>1282.77</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>2400.61</v>
+        <v>1142.4</v>
       </c>
       <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>509.5</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>499.78</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>497.33</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>454.45</v>
+      </c>
+      <c r="G12" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>634.55</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>596.76</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>554.84</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>535.13</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>741.6</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>696.5700000000001</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>673.9</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>625.17</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>9505.5</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <v>9229.18</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>8996.6</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>7712.25</v>
+      </c>
+      <c r="G15" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>1235.05</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>1215.2</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>1232.89</v>
+      </c>
+      <c r="G16" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>GLAND</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>2960.3</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>2956.41</v>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>2881.44</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>2417.13</v>
+      </c>
+      <c r="G17" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1980.8</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1924.85</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1903.29</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1704.71</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>2142</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>2026.32</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>1941.14</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>1547.95</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>2502.5</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>2360.48</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>2385.05</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>2360.42</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1172.9</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>1142.08</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>1138.73</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1068.42</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>1331.21</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>1289.32</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>1301.98</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>2496.9</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>2338.36</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>2270.36</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>2401.57</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
-        <v>1795</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>1650.65</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>1591.14</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>1506.65</v>
-      </c>
-      <c r="G12" s="19">
+      <c r="C24" s="18" t="n">
+        <v>1811.4</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1665.96</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1599.77</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1509.68</v>
+      </c>
+      <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>400.25</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>392.26</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>373.88</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>319.29</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1404.7</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>1351.49</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>1275.37</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>1139.17</v>
-      </c>
-      <c r="G14" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>716.9</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>691.83</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>671.14</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>624</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="n">
-        <v>1310.9</v>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>1227.16</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>1211.33</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>1232.11</v>
-      </c>
-      <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>IPCALAB</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>1938.6</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>1918.97</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>1900.13</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>1701.94</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>LAURUSLABS</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="n">
-        <v>2058.9</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>2014.14</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>1932.94</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>1541.98</v>
-      </c>
-      <c r="G18" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>1160.4</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>1138.84</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>1137.34</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>1067.37</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>671</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>663.45</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>659.97</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>651.02</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1905</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>1891.91</v>
+      </c>
+      <c r="E26" s="14" t="n">
+        <v>1901.97</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1848.36</v>
+      </c>
+      <c r="G26" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>45600</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>45241.25</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>45360.49</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>41472.83</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>4087</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>4027.43</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>4050.15</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>3852.73</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>PETRONET</t>
         </is>
       </c>
-      <c r="C20" s="14" t="n">
-        <v>291.75</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>290.65</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>288.14</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>280.91</v>
-      </c>
-      <c r="G20" s="15">
+      <c r="C29" s="14" t="n">
+        <v>296</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>291.16</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>288.45</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>281.06</v>
+      </c>
+      <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>PNB</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n">
-        <v>120.89</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>117.83</v>
-      </c>
-      <c r="E21" s="18" t="n">
-        <v>115.86</v>
-      </c>
-      <c r="F21" s="18" t="n">
-        <v>113.29</v>
-      </c>
-      <c r="G21" s="19">
+      <c r="C30" s="18" t="n">
+        <v>121.27</v>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>118.16</v>
+      </c>
+      <c r="E30" s="18" t="n">
+        <v>116.07</v>
+      </c>
+      <c r="F30" s="18" t="n">
+        <v>113.37</v>
+      </c>
+      <c r="G30" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>NIFTY PSU BANK</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>UNIONBANK</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
-        <v>181.2</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>176.59</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>176.62</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>169.95</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="C31" s="18" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>177.35</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>176.93</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>170.1</v>
+      </c>
+      <c r="G31" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>NIFTY METAL</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>2213.9</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>2128.36</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>2108.75</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>1988.97</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>JSWSTEEL</t>
         </is>
       </c>
-      <c r="C23" s="14" t="n">
-        <v>1260</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>1225.65</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>1246.89</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>1235.34</v>
-      </c>
-      <c r="G23" s="15">
+      <c r="C33" s="14" t="n">
+        <v>1252.7</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>1228.22</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <v>1247.12</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>1235.51</v>
+      </c>
+      <c r="G33" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>ICICIBANK</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>1403</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1370.99</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1372.81</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1359.23</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C34" s="18" t="n">
+        <v>1386.9</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>1372.5</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>1373.37</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>1359.51</v>
+      </c>
+      <c r="G34" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>KOTAKBANK</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n">
-        <v>440.75</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>432.63</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>420.7</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>407.22</v>
-      </c>
-      <c r="G25" s="19">
+      <c r="C35" s="18" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="D35" s="18" t="n">
+        <v>433.57</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <v>421.56</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <v>407.58</v>
+      </c>
+      <c r="G35" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C26" s="14" t="n">
-        <v>344.4</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>336.17</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>336.17</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>311.45</v>
-      </c>
-      <c r="G26" s="15">
+      <c r="C36" s="14" t="n">
+        <v>341.6</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>336.69</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>311.75</v>
+      </c>
+      <c r="G36" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 27-Oct-2026  16:22</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Oct-2026  17:09</t>
         </is>
       </c>
     </row>
@@ -665,32 +665,32 @@
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>0.55</v>
+        <v>0.6333</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1">
@@ -727,32 +727,32 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
         <v>20</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4667</v>
+        <v>0.4833</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
@@ -789,107 +789,107 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY REALTY</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.5329999999999999</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.267</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3</v>
+        <v>0.3777</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY REALTY</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D9" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="F9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>0.267</v>
+        <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.289</v>
+        <v>0.2333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.467</v>
+        <v>0.25</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.133</v>
+        <v>0.167</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.267</v>
+        <v>0.25</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.289</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>2</v>
@@ -898,22 +898,22 @@
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.167</v>
+        <v>0.133</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
@@ -926,7 +926,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>0.2</v>
@@ -935,10 +935,10 @@
         <v>0.2</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.067</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
@@ -975,7 +975,7 @@
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
@@ -985,84 +985,84 @@
         <v>2</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>0.133</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.083</v>
+        <v>0.08869999999999999</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.067</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.133</v>
+        <v>0.083</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0667</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -1075,25 +1075,25 @@
         <v>40</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.05</v>
+        <v>0.075</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="H17" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.05</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1224,308 +1224,308 @@
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>AJANTPHARM</t>
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>1997</v>
+        <v>3459.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>1901.47</v>
+        <v>3396.59</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>1838.03</v>
+        <v>3434.6</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>1664.06</v>
+        <v>3169.9</v>
       </c>
       <c r="G3" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1182.3</v>
+        <v>1644.8</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1156.83</v>
+        <v>1644.17</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1086.67</v>
+        <v>1643.59</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1013.74</v>
+        <v>1488.62</v>
       </c>
       <c r="G4" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>HFCL</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>250.11</v>
+        <v>9558.5</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>248.12</v>
+        <v>9260.549999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>235.97</v>
+        <v>9018.629999999999</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>176.12</v>
+        <v>7726.33</v>
       </c>
       <c r="G5" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HFCL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4174.2</v>
+        <v>1335.4</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>3637.57</v>
+        <v>1244.61</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>3496.55</v>
+        <v>1219.91</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>3549.17</v>
+        <v>1234.33</v>
       </c>
       <c r="G6" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>GLAND</t>
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>2618.4</v>
+        <v>3049</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2440.08</v>
+        <v>2965.23</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2388.17</v>
+        <v>2888.01</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2400.52</v>
+        <v>2422.1</v>
       </c>
       <c r="G7" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>5832.5</v>
+        <v>840.45</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>5693.36</v>
+        <v>825.73</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>5562.37</v>
+        <v>833.8</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>5435.24</v>
+        <v>759.12</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY PHARMA</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>579.15</v>
+        <v>1930.5</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>540.1799999999999</v>
+        <v>1925.39</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>533.27</v>
+        <v>1904.36</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>533.05</v>
+        <v>1705.94</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>2181.9</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>2041.13</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1950.58</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1555.89</v>
+      </c>
+      <c r="G10" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>2372.81</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>2389.17</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>2360.85</v>
+      </c>
+      <c r="G11" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1175.5</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>1145.26</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>1140.17</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>1068.43</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>NAZARA</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
-        <v>401.3</v>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>393.12</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>374.96</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>320.1</v>
-      </c>
-      <c r="G10" s="19">
+      <c r="C13" s="18" t="n">
+        <v>400</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>393.78</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>321.08</v>
+      </c>
+      <c r="G13" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>1464</v>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>1362.21</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>1282.77</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>1142.4</v>
-      </c>
-      <c r="G11" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n">
-        <v>509.5</v>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>499.78</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>497.33</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>454.45</v>
-      </c>
-      <c r="G12" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>634.55</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>596.76</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>554.84</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>535.13</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1537,638 +1537,694 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>1445.3</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>1370.12</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>1289.14</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>1145.85</v>
+      </c>
+      <c r="G14" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>SAREGAMA</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>523.95</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>502.08</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>498.37</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>455.28</v>
+      </c>
+      <c r="G15" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>630.85</v>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>600</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>557.8200000000001</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>536.41</v>
+      </c>
+      <c r="G16" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
           <t>TIPSMUSIC</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
-        <v>741.6</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>696.5700000000001</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>673.9</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>625.17</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="C17" s="18" t="n">
+        <v>793.9</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>705.84</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>678.6</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>626.02</v>
+      </c>
+      <c r="G17" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>9505.5</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>9229.18</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>8996.6</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>7712.25</v>
-      </c>
-      <c r="G15" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>DRREDDY</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>1310</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>1235.05</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>1215.2</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>1232.89</v>
-      </c>
-      <c r="G16" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>GLAND</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>2960.3</v>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>2956.41</v>
-      </c>
-      <c r="E17" s="14" t="n">
-        <v>2881.44</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>2417.13</v>
-      </c>
-      <c r="G17" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>1980.8</v>
+        <v>1961.9</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>1924.85</v>
+        <v>1907.23</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1903.29</v>
+        <v>1842.88</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>1704.71</v>
+        <v>1665.29</v>
       </c>
       <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>2142</v>
+        <v>1156.7</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>2026.32</v>
+        <v>1146.19</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>1941.14</v>
+        <v>1078.82</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1547.95</v>
+        <v>1003.29</v>
       </c>
       <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>2502.5</v>
+        <v>4088.1</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>2360.48</v>
+        <v>3680.48</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>2385.05</v>
+        <v>3519.75</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>2360.42</v>
+        <v>3549.61</v>
       </c>
       <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>NIFTY PHARMA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>1172.9</v>
+        <v>2518</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>1142.08</v>
+        <v>2447.5</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>1138.73</v>
+        <v>2393.26</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1068.42</v>
+        <v>2396.98</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>5848</v>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>5708.09</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>5573.57</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>5435.09</v>
+      </c>
+      <c r="G22" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>598.7</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>545.75</v>
+      </c>
+      <c r="E23" s="14" t="n">
+        <v>535.84</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>533.16</v>
+      </c>
+      <c r="G23" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B24" s="17" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n">
-        <v>1420</v>
-      </c>
-      <c r="D22" s="18" t="n">
-        <v>1331.21</v>
-      </c>
-      <c r="E22" s="18" t="n">
-        <v>1289.32</v>
-      </c>
-      <c r="F22" s="18" t="n">
-        <v>1301.98</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="C24" s="18" t="n">
+        <v>1400.5</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>1337.81</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>1293.68</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>1302.05</v>
+      </c>
+      <c r="G24" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n">
-        <v>2496.9</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>2338.36</v>
-      </c>
-      <c r="E23" s="18" t="n">
-        <v>2270.36</v>
-      </c>
-      <c r="F23" s="18" t="n">
-        <v>2401.57</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="C25" s="18" t="n">
+        <v>2460</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2349.94</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2277.8</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>2399.98</v>
+      </c>
+      <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>TECHM</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>1811.4</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1665.96</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1599.77</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1509.68</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C26" s="18" t="n">
+        <v>1776.6</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>1676.5</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>1606.71</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>1511.09</v>
+      </c>
+      <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>47625</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>45468.28</v>
+      </c>
+      <c r="E27" s="14" t="n">
+        <v>45449.28</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>41495.36</v>
+      </c>
+      <c r="G27" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>5322.5</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>5171.32</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>5221.84</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>5250.31</v>
+      </c>
+      <c r="G28" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>160.33</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>158.02</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>158.34</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>142.79</v>
+      </c>
+      <c r="G29" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>4239.9</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>4047.67</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>4057.58</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>3850.08</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C25" s="14" t="n">
-        <v>671</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>663.45</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>659.97</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>651.02</v>
-      </c>
-      <c r="G25" s="15">
+      <c r="C31" s="18" t="n">
+        <v>666.3</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>663.73</v>
+      </c>
+      <c r="E31" s="18" t="n">
+        <v>660.21</v>
+      </c>
+      <c r="F31" s="18" t="n">
+        <v>650.72</v>
+      </c>
+      <c r="G31" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1905</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1891.91</v>
-      </c>
-      <c r="E26" s="14" t="n">
-        <v>1901.97</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>1848.36</v>
-      </c>
-      <c r="G26" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n">
-        <v>45600</v>
-      </c>
-      <c r="D27" s="18" t="n">
-        <v>45241.25</v>
-      </c>
-      <c r="E27" s="18" t="n">
-        <v>45360.49</v>
-      </c>
-      <c r="F27" s="18" t="n">
-        <v>41472.83</v>
-      </c>
-      <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n">
-        <v>4087</v>
-      </c>
-      <c r="D28" s="18" t="n">
-        <v>4027.43</v>
-      </c>
-      <c r="E28" s="18" t="n">
-        <v>4050.15</v>
-      </c>
-      <c r="F28" s="18" t="n">
-        <v>3852.73</v>
-      </c>
-      <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY OIL &amp; GAS</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>296</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>291.16</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>288.45</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>281.06</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PETRONET","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n">
-        <v>121.27</v>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>118.16</v>
-      </c>
-      <c r="E30" s="18" t="n">
-        <v>116.07</v>
-      </c>
-      <c r="F30" s="18" t="n">
-        <v>113.37</v>
-      </c>
-      <c r="G30" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>177.35</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>176.93</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>2213.9</v>
+        <v>120.31</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>2128.36</v>
+        <v>118.37</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>2108.75</v>
+        <v>116.24</v>
       </c>
       <c r="F32" s="14" t="n">
-        <v>1988.97</v>
+        <v>113.56</v>
       </c>
       <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>1252.7</v>
+        <v>182.98</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1228.22</v>
+        <v>177.89</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>1247.12</v>
+        <v>177.17</v>
       </c>
       <c r="F33" s="14" t="n">
-        <v>1235.51</v>
+        <v>170.4</v>
       </c>
       <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>1386.9</v>
+        <v>2165.3</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1372.5</v>
+        <v>2131.88</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>1373.37</v>
+        <v>2110.96</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>1359.51</v>
+        <v>1991.56</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="C35" s="18" t="n">
-        <v>442.5</v>
+        <v>2564.3</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>433.57</v>
+        <v>2551.96</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>421.56</v>
+        <v>2435.34</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>407.58</v>
+        <v>1738.05</v>
       </c>
       <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="12" t="inlineStr">
         <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>1377.6</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>1372.99</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>1373.53</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>1358.49</v>
+      </c>
+      <c r="G36" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>440</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>434.18</v>
+      </c>
+      <c r="E37" s="14" t="n">
+        <v>422.28</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="G37" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C36" s="14" t="n">
-        <v>341.6</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>336.69</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <v>336.38</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>311.75</v>
-      </c>
-      <c r="G36" s="15">
+      <c r="C38" s="18" t="n">
+        <v>346</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>337.57</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>312.24</v>
+      </c>
+      <c r="G38" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 28-Oct-2026  17:09</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 29-Oct-2026  17:29</t>
         </is>
       </c>
     </row>
@@ -672,19 +672,19 @@
         <v>20</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>12</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="H4" s="6" t="n">
         <v>0.6</v>
@@ -696,125 +696,125 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="F5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.4833</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4333</v>
+        <v>0.4443</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY AUTO</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.5329999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.267</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.3777</v>
+        <v>0.4333</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,56 +827,56 @@
         <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H9" s="10" t="n">
         <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2223</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
@@ -892,7 +892,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3</v>
@@ -901,112 +901,112 @@
         <v>0.2</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="F12" s="6" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H12" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>0.2</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>0.1557</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>0.15</v>
+        <v>0.133</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>0.1333</v>
+        <v>0.1777</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY FINANCIAL SERVICES</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.133</v>
+        <v>0.2</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.111</v>
+        <v>0.1667</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
@@ -1016,84 +1016,84 @@
         <v>2</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
         <v>0.133</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.267</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.175</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.083</v>
+        <v>0.1</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.083</v>
+        <v>0.1167</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.025</v>
+        <v>0.083</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.0667</v>
+        <v>0.083</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3459.8</v>
+        <v>3459.7</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3396.59</v>
+        <v>3402.6</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3434.6</v>
+        <v>3435.59</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>3169.9</v>
+        <v>3178.88</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1644.8</v>
+        <v>1659.9</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1644.17</v>
+        <v>1645.67</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1643.59</v>
+        <v>1644.23</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1488.62</v>
+        <v>1491.37</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9558.5</v>
+        <v>9664</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9260.549999999999</v>
+        <v>9298.969999999999</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>9018.629999999999</v>
+        <v>9043.950000000001</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7726.33</v>
+        <v>7751.74</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1335.4</v>
+        <v>1345</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1244.61</v>
+        <v>1254.17</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1219.91</v>
+        <v>1224.81</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1234.33</v>
+        <v>1232.23</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>3049</v>
+        <v>3074.5</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2965.23</v>
+        <v>2975.64</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2888.01</v>
+        <v>2895.33</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2422.1</v>
+        <v>2428.76</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>840.45</v>
+        <v>2339</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>825.73</v>
+        <v>2276.53</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>833.8</v>
+        <v>2306.72</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>759.12</v>
+        <v>2217.46</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>1930.5</v>
+        <v>837.35</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>1925.39</v>
+        <v>826.84</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>1904.36</v>
+        <v>833.9400000000001</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1705.94</v>
+        <v>760.01</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>2181.9</v>
+        <v>1926.2</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>2041.13</v>
+        <v>1925.47</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1950.58</v>
+        <v>1905.21</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1555.89</v>
+        <v>1708.47</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2490</v>
+        <v>2244</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2372.81</v>
+        <v>2060.45</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>2389.17</v>
+        <v>1962.09</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>2360.85</v>
+        <v>1562.9</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,750 +1481,1002 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>2469.3</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>2382</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>2392.31</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>2365.05</v>
+      </c>
+      <c r="G12" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
           <t>ZYDUSLIFE</t>
         </is>
       </c>
-      <c r="C12" s="14" t="n">
-        <v>1175.5</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>1145.26</v>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>1140.17</v>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>1068.43</v>
-      </c>
-      <c r="G12" s="15">
+      <c r="C13" s="14" t="n">
+        <v>1184.4</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>1148.99</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <v>1141.91</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>1069.72</v>
+      </c>
+      <c r="G13" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="n">
-        <v>400</v>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>393.78</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>375.94</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>321.08</v>
-      </c>
-      <c r="G13" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>1445.3</v>
+        <v>342.5</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1370.12</v>
+        <v>303.02</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1289.14</v>
+        <v>296.87</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1145.85</v>
+        <v>322.85</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BSOFT","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>523.95</v>
+        <v>1962</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>502.08</v>
+        <v>1912.44</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>498.37</v>
+        <v>1847.56</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>455.28</v>
+        <v>1667.21</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>630.85</v>
+        <v>4182.6</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>600</v>
+        <v>3728.3</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>557.8200000000001</v>
+        <v>3545.74</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>536.41</v>
+        <v>3553.57</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>2561.3</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>2458.34</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>2399.85</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>2402.18</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>5724.46</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>5585.59</v>
+      </c>
+      <c r="F18" s="18" t="n">
+        <v>5444.86</v>
+      </c>
+      <c r="G18" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>TANLA</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>618.4</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>552.67</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <v>539.0700000000001</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>535.12</v>
+      </c>
+      <c r="G19" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>ZENSARTECH</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>537.3</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>487.49</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>474.82</v>
+      </c>
+      <c r="F20" s="18" t="n">
+        <v>526.67</v>
+      </c>
+      <c r="G20" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
           <t>NIFTY MEDIA</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n">
-        <v>793.9</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>705.84</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>678.6</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>626.02</v>
-      </c>
-      <c r="G17" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1961.9</v>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>1907.23</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>1842.88</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>1665.29</v>
-      </c>
-      <c r="G18" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>CYIENT</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>1156.7</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>1146.19</v>
-      </c>
-      <c r="E19" s="14" t="n">
-        <v>1078.82</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>1003.29</v>
-      </c>
-      <c r="G19" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:CYIENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>LTTS</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>4088.1</v>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>3680.48</v>
-      </c>
-      <c r="E20" s="14" t="n">
-        <v>3519.75</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>3549.61</v>
-      </c>
-      <c r="G20" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>2518</v>
+        <v>405.4</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>2447.5</v>
+        <v>394.88</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>2393.26</v>
+        <v>377.1</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2396.98</v>
+        <v>321.94</v>
       </c>
       <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>5848</v>
+        <v>1490.3</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>5708.09</v>
+        <v>1381.57</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>5573.57</v>
+        <v>1297.03</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>5435.09</v>
+        <v>1153.35</v>
       </c>
       <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>598.7</v>
+        <v>536</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>545.75</v>
+        <v>505.31</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>535.84</v>
+        <v>499.85</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>533.16</v>
+        <v>456.35</v>
       </c>
       <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>SUNTV</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>619.9</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>601.9</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>560.25</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>538.61</v>
+      </c>
+      <c r="G24" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>791.35</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>713.98</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>683.03</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>627.3099999999999</v>
+      </c>
+      <c r="G25" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n">
+        <v>864.1</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>840.78</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>842.88</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>846.8099999999999</v>
+      </c>
+      <c r="G26" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="D27" s="18" t="n">
+        <v>118.89</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <v>116.54</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <v>113.66</v>
+      </c>
+      <c r="G27" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>178.71</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>177.53</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <v>170.48</v>
+      </c>
+      <c r="G28" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>NIFTY IT</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>HCLTECH</t>
         </is>
       </c>
-      <c r="C24" s="18" t="n">
-        <v>1400.5</v>
-      </c>
-      <c r="D24" s="18" t="n">
-        <v>1337.81</v>
-      </c>
-      <c r="E24" s="18" t="n">
-        <v>1293.68</v>
-      </c>
-      <c r="F24" s="18" t="n">
-        <v>1302.05</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="C29" s="14" t="n">
+        <v>1403.9</v>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>1344.1</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>1298</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>1305.88</v>
+      </c>
+      <c r="G29" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n">
-        <v>2460</v>
-      </c>
-      <c r="D25" s="18" t="n">
-        <v>2349.94</v>
-      </c>
-      <c r="E25" s="18" t="n">
-        <v>2277.8</v>
-      </c>
-      <c r="F25" s="18" t="n">
-        <v>2399.98</v>
-      </c>
-      <c r="G25" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY IT</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>1776.6</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>1676.5</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>1606.71</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>1511.09</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>47625</v>
-      </c>
-      <c r="D27" s="14" t="n">
-        <v>45468.28</v>
-      </c>
-      <c r="E27" s="14" t="n">
-        <v>45449.28</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>41495.36</v>
-      </c>
-      <c r="G27" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>5322.5</v>
-      </c>
-      <c r="D28" s="14" t="n">
-        <v>5171.32</v>
-      </c>
-      <c r="E28" s="14" t="n">
-        <v>5221.84</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>5250.31</v>
-      </c>
-      <c r="G28" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HEROMOTOCO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>160.33</v>
-      </c>
-      <c r="D29" s="14" t="n">
-        <v>158.02</v>
-      </c>
-      <c r="E29" s="14" t="n">
-        <v>158.34</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>142.79</v>
-      </c>
-      <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>2478</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <v>2362.14</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <v>2285.65</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>2400.74</v>
+      </c>
+      <c r="G30" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>1769.6</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <v>1685.37</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <v>1613.09</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>1514.05</v>
+      </c>
+      <c r="G31" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n">
+        <v>694.35</v>
+      </c>
+      <c r="D32" s="18" t="n">
+        <v>666.64</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>661.55</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>651.54</v>
+      </c>
+      <c r="G32" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>1969.9</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>1899.97</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>1904.54</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>1849.81</v>
+      </c>
+      <c r="G33" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>RAYMOND</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n">
+        <v>1101.9</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>1101.26</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <v>994.3099999999999</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <v>710.12</v>
+      </c>
+      <c r="G34" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
           <t>NIFTY AUTO</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>4239.9</v>
-      </c>
-      <c r="D30" s="14" t="n">
-        <v>4047.67</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>4057.58</v>
-      </c>
-      <c r="F30" s="14" t="n">
-        <v>3850.08</v>
-      </c>
-      <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>DLF</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n">
-        <v>666.3</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <v>663.73</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <v>660.21</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <v>650.72</v>
-      </c>
-      <c r="G31" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>120.31</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <v>118.37</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <v>116.24</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>113.56</v>
-      </c>
-      <c r="G32" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>182.98</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <v>177.89</v>
-      </c>
-      <c r="E33" s="14" t="n">
-        <v>177.17</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="G33" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n">
-        <v>2165.3</v>
-      </c>
-      <c r="D34" s="18" t="n">
-        <v>2131.88</v>
-      </c>
-      <c r="E34" s="18" t="n">
-        <v>2110.96</v>
-      </c>
-      <c r="F34" s="18" t="n">
-        <v>1991.56</v>
-      </c>
-      <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>WELCORP</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>2564.3</v>
-      </c>
-      <c r="D35" s="18" t="n">
-        <v>2551.96</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>2435.34</v>
-      </c>
-      <c r="F35" s="18" t="n">
-        <v>1738.05</v>
-      </c>
-      <c r="G35" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WELCORP","Chart 📈")</f>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>47565</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>45667.96</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>45532.19</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>41459.24</v>
+      </c>
+      <c r="G35" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>1377.6</v>
+        <v>160</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>1372.99</v>
+        <v>158.21</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>1373.53</v>
+        <v>158.4</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1358.49</v>
+        <v>143.03</v>
       </c>
       <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY AUTO</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>440</v>
+        <v>4280</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>434.18</v>
+        <v>4069.8</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>422.28</v>
+        <v>4066.3</v>
       </c>
       <c r="F37" s="14" t="n">
-        <v>408.1</v>
+        <v>3849.09</v>
       </c>
       <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n">
+        <v>2195</v>
+      </c>
+      <c r="D38" s="18" t="n">
+        <v>2137.89</v>
+      </c>
+      <c r="E38" s="18" t="n">
+        <v>2114.26</v>
+      </c>
+      <c r="F38" s="18" t="n">
+        <v>1995.9</v>
+      </c>
+      <c r="G38" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n">
+        <v>1255.4</v>
+      </c>
+      <c r="D39" s="18" t="n">
+        <v>1231.93</v>
+      </c>
+      <c r="E39" s="18" t="n">
+        <v>1247.22</v>
+      </c>
+      <c r="F39" s="18" t="n">
+        <v>1240.51</v>
+      </c>
+      <c r="G39" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>MARICO</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>802.9</v>
+      </c>
+      <c r="D40" s="14" t="n">
+        <v>786.2</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>802.35</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>797.16</v>
+      </c>
+      <c r="G40" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY CONSUMER DURABLES</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>BLUESTARCO</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n">
+        <v>1673</v>
+      </c>
+      <c r="D41" s="18" t="n">
+        <v>1560.55</v>
+      </c>
+      <c r="E41" s="18" t="n">
+        <v>1554.33</v>
+      </c>
+      <c r="F41" s="18" t="n">
+        <v>1652.69</v>
+      </c>
+      <c r="G41" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1386.6</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>1374.28</v>
+      </c>
+      <c r="E42" s="14" t="n">
+        <v>1374.05</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1359.37</v>
+      </c>
+      <c r="G42" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
+        <v>459</v>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>436.54</v>
+      </c>
+      <c r="E43" s="14" t="n">
+        <v>423.72</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>408.44</v>
+      </c>
+      <c r="G43" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="n">
+        <v>3231</v>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>3199.53</v>
+      </c>
+      <c r="E44" s="14" t="n">
+        <v>3172.46</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <v>2835.14</v>
+      </c>
+      <c r="G44" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D45" s="18" t="n">
+        <v>1276.97</v>
+      </c>
+      <c r="E45" s="18" t="n">
+        <v>1298.27</v>
+      </c>
+      <c r="F45" s="18" t="n">
+        <v>1259.71</v>
+      </c>
+      <c r="G45" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>NHPC</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="D46" s="18" t="n">
+        <v>73.28</v>
+      </c>
+      <c r="E46" s="18" t="n">
+        <v>74.44</v>
+      </c>
+      <c r="F46" s="18" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="G46" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
           <t>NIFTY BANK</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n">
-        <v>346</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>337.57</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>336.76</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>312.24</v>
-      </c>
-      <c r="G38" s="19">
+      <c r="C47" s="14" t="n">
+        <v>347.75</v>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>338.54</v>
+      </c>
+      <c r="E47" s="14" t="n">
+        <v>337.19</v>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>312.52</v>
+      </c>
+      <c r="G47" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>

--- a/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
+++ b/Report/EMAReport/Sectoral_EMA_Analysis.xlsx
@@ -591,7 +591,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NSE Sectoral EMA Analysis   ·   Generated: 29-Oct-2026  17:29</t>
+          <t>NSE Sectoral EMA Analysis   ·   Generated: 30-Oct-2026  17:07</t>
         </is>
       </c>
     </row>
@@ -696,38 +696,38 @@
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>0.5</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>0.5333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>NIFTY MEDIA</t>
+          <t>NIFTY IT</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
@@ -740,7 +740,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>0.5</v>
@@ -749,51 +749,51 @@
         <v>0.5</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>8</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="G7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.45</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.4443</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>5</v>
@@ -802,19 +802,19 @@
         <v>5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5</v>
+        <v>0.417</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.3</v>
+        <v>0.333</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.4333</v>
+        <v>0.389</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
@@ -827,7 +827,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>3</v>
@@ -836,7 +836,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="10" t="n">
         <v>0.3</v>
@@ -845,7 +845,7 @@
         <v>0.3</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
@@ -858,50 +858,50 @@
         <v>15</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.333</v>
+        <v>0.267</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2</v>
+        <v>0.133</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.267</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.2667</v>
+        <v>0.2223</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>NIFTY METAL</t>
+          <t>NIFTY FMCG</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>0.2</v>
+        <v>0.067</v>
       </c>
       <c r="H11" s="10" t="n">
         <v>0.2</v>
@@ -913,38 +913,38 @@
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NIFTY FMCG</t>
+          <t>NIFTY OIL &amp; GAS</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
         <v>15</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.267</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.133</v>
+        <v>0.067</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.2</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+          <t>NIFTY METAL</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
@@ -954,22 +954,22 @@
         <v>3</v>
       </c>
       <c r="D13" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>2</v>
       </c>
       <c r="F13" s="10" t="n">
         <v>0.2</v>
       </c>
       <c r="G13" s="10" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="H13" s="10" t="n">
         <v>0.2</v>
       </c>
-      <c r="H13" s="10" t="n">
-        <v>0.133</v>
-      </c>
       <c r="I13" s="11" t="n">
-        <v>0.1777</v>
+        <v>0.1557</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1">
@@ -982,7 +982,7 @@
         <v>20</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>3</v>
@@ -991,7 +991,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>0.15</v>
@@ -1000,100 +1000,100 @@
         <v>0.15</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.1667</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>NIFTY OIL &amp; GAS</t>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>4</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>0.133</v>
+        <v>0.15</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0.067</v>
+        <v>0.075</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>0.267</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>0.1557</v>
+        <v>0.1083</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>NIFTY ENERGY</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.175</v>
+        <v>0.083</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.075</v>
+        <v>0.083</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1</v>
+        <v>0.083</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.1167</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>NIFTY BANK</t>
+          <t>NIFTY CONSUMER DURABLES</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="10" t="n">
-        <v>0.083</v>
+        <v>0.133</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>0.083</v>
+        <v>0.067</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>0.083</v>
+        <v>0.0667</v>
       </c>
     </row>
   </sheetData>
@@ -1160,7 +1160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1233,16 +1233,16 @@
         </is>
       </c>
       <c r="C3" s="14" t="n">
-        <v>3459.7</v>
+        <v>3508.8</v>
       </c>
       <c r="D3" s="14" t="n">
-        <v>3402.6</v>
+        <v>3412.72</v>
       </c>
       <c r="E3" s="14" t="n">
-        <v>3435.59</v>
+        <v>3438.46</v>
       </c>
       <c r="F3" s="14" t="n">
-        <v>3178.88</v>
+        <v>3182.72</v>
       </c>
       <c r="G3" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AJANTPHARM","Chart 📈")</f>
@@ -1261,16 +1261,16 @@
         </is>
       </c>
       <c r="C4" s="14" t="n">
-        <v>1659.9</v>
+        <v>1681.4</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>1645.67</v>
+        <v>1649.08</v>
       </c>
       <c r="E4" s="14" t="n">
-        <v>1644.23</v>
+        <v>1645.69</v>
       </c>
       <c r="F4" s="14" t="n">
-        <v>1491.37</v>
+        <v>1492.48</v>
       </c>
       <c r="G4" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:AUROPHARMA","Chart 📈")</f>
@@ -1289,16 +1289,16 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>9664</v>
+        <v>9780</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>9298.969999999999</v>
+        <v>9344.780000000001</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>9043.950000000001</v>
+        <v>9072.82</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>7751.74</v>
+        <v>7783.85</v>
       </c>
       <c r="G5" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DIVISLAB","Chart 📈")</f>
@@ -1317,16 +1317,16 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1345</v>
+        <v>1352</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>1254.17</v>
+        <v>1263.48</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>1224.81</v>
+        <v>1229.8</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>1232.23</v>
+        <v>1229.37</v>
       </c>
       <c r="G6" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DRREDDY","Chart 📈")</f>
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>3074.5</v>
+        <v>3095.9</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>2975.64</v>
+        <v>2987.09</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>2895.33</v>
+        <v>2903.19</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>2428.76</v>
+        <v>2435.51</v>
       </c>
       <c r="G7" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLAND","Chart 📈")</f>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2339</v>
+        <v>839.75</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>2276.53</v>
+        <v>828.0700000000001</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>2306.72</v>
+        <v>834.17</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>2217.46</v>
+        <v>761.0599999999999</v>
       </c>
       <c r="G8" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GLENMARK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1397,23 +1397,23 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>IPCALAB</t>
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>837.35</v>
+        <v>1927.8</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>826.84</v>
+        <v>1925.69</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>833.9400000000001</v>
+        <v>1906.1</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>760.01</v>
+        <v>1710.57</v>
       </c>
       <c r="G9" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:GRANULES","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1425,23 +1425,23 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>IPCALAB</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>1926.2</v>
+        <v>2405.5</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1925.47</v>
+        <v>2093.32</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>1905.21</v>
+        <v>1979.48</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>1708.47</v>
+        <v>1572.01</v>
       </c>
       <c r="G10" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:IPCALAB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1453,23 +1453,23 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>2244</v>
+        <v>2492.8</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>2060.45</v>
+        <v>2392.55</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>1962.09</v>
+        <v>2396.25</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>1562.9</v>
+        <v>2366.56</v>
       </c>
       <c r="G11" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LAURUSLABS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -1481,611 +1481,611 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>2469.3</v>
+        <v>1245.5</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>2382</v>
+        <v>1158.18</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>2392.31</v>
+        <v>1145.97</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>2365.05</v>
+        <v>1070.07</v>
       </c>
       <c r="G12" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MANKIND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY PHARMA</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>ZYDUSLIFE</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1184.4</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1148.99</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>1141.91</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>1069.72</v>
-      </c>
-      <c r="G13" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZYDUSLIFE","Chart 📈")</f>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>NAZARA</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>398.8</v>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>395.26</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>377.95</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>322.99</v>
+      </c>
+      <c r="G13" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C14" s="18" t="n">
-        <v>342.5</v>
+        <v>1495.1</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>303.02</v>
+        <v>1392.38</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>296.87</v>
+        <v>1304.8</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>322.85</v>
+        <v>1157.42</v>
       </c>
       <c r="G14" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BSOFT","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="C15" s="18" t="n">
-        <v>1962</v>
+        <v>548.65</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>1912.44</v>
+        <v>509.44</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>1847.56</v>
+        <v>501.76</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>1667.21</v>
+        <v>457.39</v>
       </c>
       <c r="G15" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+          <t>NIFTY MEDIA</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="C16" s="18" t="n">
-        <v>4182.6</v>
+        <v>607.55</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>3728.3</v>
+        <v>602.4400000000001</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>3545.74</v>
+        <v>562.11</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>3553.57</v>
+        <v>538.53</v>
       </c>
       <c r="G16" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="20" t="inlineStr">
         <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>TIPSMUSIC</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>782.05</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>720.47</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>686.91</v>
+      </c>
+      <c r="F17" s="18" t="n">
+        <v>629.4299999999999</v>
+      </c>
+      <c r="G17" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1428.1</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>1352.1</v>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>1303.11</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>1306.49</v>
+      </c>
+      <c r="G18" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>2502.6</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>2375.52</v>
+      </c>
+      <c r="E19" s="14" t="n">
+        <v>2294.15</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>2399.96</v>
+      </c>
+      <c r="G19" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1790.8</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>1695.41</v>
+      </c>
+      <c r="E20" s="14" t="n">
+        <v>1620.06</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1515.32</v>
+      </c>
+      <c r="G20" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>198.31</v>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>180.63</v>
+      </c>
+      <c r="E21" s="14" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>190.55</v>
+      </c>
+      <c r="G21" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:WIPRO","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>BSOFT</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n">
+        <v>323</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <v>304.92</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <v>297.89</v>
+      </c>
+      <c r="F22" s="18" t="n">
+        <v>322.94</v>
+      </c>
+      <c r="G22" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BSOFT","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>1925.07</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <v>1855.3</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <v>1671.83</v>
+      </c>
+      <c r="G23" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:COFORGE","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>LTTS</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n">
+        <v>4280.2</v>
+      </c>
+      <c r="D24" s="18" t="n">
+        <v>3780.86</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <v>3574.54</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <v>3561.11</v>
+      </c>
+      <c r="G24" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:LTTS","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>MPHASIS</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n">
-        <v>2561.3</v>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>2458.34</v>
-      </c>
-      <c r="E17" s="18" t="n">
-        <v>2399.85</v>
-      </c>
-      <c r="F17" s="18" t="n">
-        <v>2402.18</v>
-      </c>
-      <c r="G17" s="19">
+      <c r="C25" s="18" t="n">
+        <v>2525.6</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>2464.75</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <v>2404.78</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <v>2404.96</v>
+      </c>
+      <c r="G25" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MPHASIS","Chart 📈")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>PERSISTENT</t>
         </is>
       </c>
-      <c r="C18" s="18" t="n">
-        <v>5880</v>
-      </c>
-      <c r="D18" s="18" t="n">
-        <v>5724.46</v>
-      </c>
-      <c r="E18" s="18" t="n">
-        <v>5585.59</v>
-      </c>
-      <c r="F18" s="18" t="n">
-        <v>5444.86</v>
-      </c>
-      <c r="G18" s="19">
+      <c r="C26" s="18" t="n">
+        <v>6048</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>5755.28</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>5603.73</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <v>5456.73</v>
+      </c>
+      <c r="G26" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PERSISTENT","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>618.4</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>552.67</v>
-      </c>
-      <c r="E19" s="18" t="n">
-        <v>539.0700000000001</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>535.12</v>
-      </c>
-      <c r="G19" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>ZENSARTECH</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n">
-        <v>537.3</v>
-      </c>
-      <c r="D20" s="18" t="n">
-        <v>487.49</v>
-      </c>
-      <c r="E20" s="18" t="n">
-        <v>474.82</v>
-      </c>
-      <c r="F20" s="18" t="n">
-        <v>526.67</v>
-      </c>
-      <c r="G20" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>NAZARA</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>405.4</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>394.88</v>
-      </c>
-      <c r="E21" s="14" t="n">
-        <v>377.1</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>321.94</v>
-      </c>
-      <c r="G21" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NAZARA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>PVRINOX</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1490.3</v>
-      </c>
-      <c r="D22" s="14" t="n">
-        <v>1381.57</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>1297.03</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>1153.35</v>
-      </c>
-      <c r="G22" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PVRINOX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>SAREGAMA</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>536</v>
-      </c>
-      <c r="D23" s="14" t="n">
-        <v>505.31</v>
-      </c>
-      <c r="E23" s="14" t="n">
-        <v>499.85</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <v>456.35</v>
-      </c>
-      <c r="G23" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SAREGAMA","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>SUNTV</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>619.9</v>
-      </c>
-      <c r="D24" s="14" t="n">
-        <v>601.9</v>
-      </c>
-      <c r="E24" s="14" t="n">
-        <v>560.25</v>
-      </c>
-      <c r="F24" s="14" t="n">
-        <v>538.61</v>
-      </c>
-      <c r="G24" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:SUNTV","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY MEDIA</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>791.35</v>
-      </c>
-      <c r="D25" s="14" t="n">
-        <v>713.98</v>
-      </c>
-      <c r="E25" s="14" t="n">
-        <v>683.03</v>
-      </c>
-      <c r="F25" s="14" t="n">
-        <v>627.3099999999999</v>
-      </c>
-      <c r="G25" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TIPSMUSIC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY PSU BANK</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>864.1</v>
-      </c>
-      <c r="D26" s="18" t="n">
-        <v>840.78</v>
-      </c>
-      <c r="E26" s="18" t="n">
-        <v>842.88</v>
-      </c>
-      <c r="F26" s="18" t="n">
-        <v>846.8099999999999</v>
-      </c>
-      <c r="G26" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>123.9</v>
+        <v>627.15</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>118.89</v>
+        <v>559.77</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>116.54</v>
+        <v>542.53</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>113.66</v>
+        <v>536.16</v>
       </c>
       <c r="G27" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TANLA","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>NIFTY PSU BANK</t>
+          <t>NIFTY MIDSMALL IT &amp; TELECOM</t>
         </is>
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ZENSARTECH</t>
         </is>
       </c>
       <c r="C28" s="18" t="n">
-        <v>186.5</v>
+        <v>535.5</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>178.71</v>
+        <v>492.06</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>177.53</v>
+        <v>477.2</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>170.48</v>
+        <v>526.95</v>
       </c>
       <c r="G28" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ZENSARTECH","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>1403.9</v>
+        <v>865.5</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>1344.1</v>
+        <v>843.14</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>1298</v>
+        <v>843.76</v>
       </c>
       <c r="F29" s="14" t="n">
-        <v>1305.88</v>
+        <v>847.03</v>
       </c>
       <c r="G29" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:HCLTECH","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:INDIANB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>2478</v>
+        <v>81.36</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>2362.14</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>2285.65</v>
+        <v>81.14</v>
       </c>
       <c r="F30" s="14" t="n">
-        <v>2400.74</v>
+        <v>76.28</v>
       </c>
       <c r="G30" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TCS","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MAHABANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>NIFTY IT</t>
+          <t>NIFTY PSU BANK</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>1769.6</v>
+        <v>122.85</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>1685.37</v>
+        <v>119.27</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>1613.09</v>
+        <v>116.79</v>
       </c>
       <c r="F31" s="14" t="n">
-        <v>1514.05</v>
+        <v>113.67</v>
       </c>
       <c r="G31" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TECHM","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PNB","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY PSU BANK</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>186</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="E32" s="14" t="n">
+        <v>177.87</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>170.32</v>
+      </c>
+      <c r="G32" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:UNIONBANK","Chart 📈")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>NIFTY REALTY</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>DLF</t>
         </is>
       </c>
-      <c r="C32" s="18" t="n">
-        <v>694.35</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>666.64</v>
-      </c>
-      <c r="E32" s="18" t="n">
-        <v>661.55</v>
-      </c>
-      <c r="F32" s="18" t="n">
-        <v>651.54</v>
-      </c>
-      <c r="G32" s="19">
+      <c r="C33" s="18" t="n">
+        <v>691.55</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>669.01</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>662.73</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <v>651.76</v>
+      </c>
+      <c r="G33" s="19">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:DLF","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY REALTY</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n">
-        <v>1969.9</v>
-      </c>
-      <c r="D33" s="18" t="n">
-        <v>1899.97</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>1904.54</v>
-      </c>
-      <c r="F33" s="18" t="n">
-        <v>1849.81</v>
-      </c>
-      <c r="G33" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2097,23 +2097,23 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>RAYMOND</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="C34" s="18" t="n">
-        <v>1101.9</v>
+        <v>1957.2</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>1101.26</v>
+        <v>1905.42</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>994.3099999999999</v>
+        <v>1906.6</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>710.12</v>
+        <v>1850.5</v>
       </c>
       <c r="G34" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:RAYMOND","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:PHOENIXLTD","Chart 📈")</f>
         <v/>
       </c>
     </row>
@@ -2129,16 +2129,16 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>47565</v>
+        <v>47200</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>45667.96</v>
+        <v>45813.87</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>45532.19</v>
+        <v>45597.58</v>
       </c>
       <c r="F35" s="14" t="n">
-        <v>41459.24</v>
+        <v>41502.22</v>
       </c>
       <c r="G35" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BOSCHLTD","Chart 📈")</f>
@@ -2153,330 +2153,190 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>160</v>
+        <v>4195.2</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>158.21</v>
+        <v>4081.74</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>158.4</v>
+        <v>4071.36</v>
       </c>
       <c r="F36" s="14" t="n">
-        <v>143.03</v>
+        <v>3851.93</v>
       </c>
       <c r="G36" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MOTHERSON","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY AUTO</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>TVSMOTOR</t>
-        </is>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>4280</v>
-      </c>
-      <c r="D37" s="14" t="n">
-        <v>4069.8</v>
-      </c>
-      <c r="E37" s="14" t="n">
-        <v>4066.3</v>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>3849.09</v>
-      </c>
-      <c r="G37" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:TVSMOTOR","Chart 📈")</f>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n">
+        <v>2165.1</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>2140.48</v>
+      </c>
+      <c r="E37" s="18" t="n">
+        <v>2116.25</v>
+      </c>
+      <c r="F37" s="18" t="n">
+        <v>1995.9</v>
+      </c>
+      <c r="G37" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n">
-        <v>2195</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>2137.89</v>
-      </c>
-      <c r="E38" s="18" t="n">
-        <v>2114.26</v>
-      </c>
-      <c r="F38" s="18" t="n">
-        <v>1995.9</v>
-      </c>
-      <c r="G38" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:APLAPOLLO","Chart 📈")</f>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>1398</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>1376.54</v>
+      </c>
+      <c r="E38" s="14" t="n">
+        <v>1374.98</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <v>1359.09</v>
+      </c>
+      <c r="G38" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY METAL</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n">
-        <v>1255.4</v>
-      </c>
-      <c r="D39" s="18" t="n">
-        <v>1231.93</v>
-      </c>
-      <c r="E39" s="18" t="n">
-        <v>1247.22</v>
-      </c>
-      <c r="F39" s="18" t="n">
-        <v>1240.51</v>
-      </c>
-      <c r="G39" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:JSWSTEEL","Chart 📈")</f>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>NIFTY FINANCIAL SERVICES</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>438.93</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>425.21</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>408.74</v>
+      </c>
+      <c r="G39" s="15">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY FMCG</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>MARICO</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>802.9</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <v>786.2</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>802.35</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>797.16</v>
-      </c>
-      <c r="G40" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MARICO","Chart 📈")</f>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>ADANIGREEN</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n">
+        <v>1298.7</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>1279.04</v>
+      </c>
+      <c r="E40" s="18" t="n">
+        <v>1298.29</v>
+      </c>
+      <c r="F40" s="18" t="n">
+        <v>1262.4</v>
+      </c>
+      <c r="G40" s="19">
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY CONSUMER DURABLES</t>
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="C41" s="18" t="n">
-        <v>1673</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>1560.55</v>
+        <v>73.7</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>1554.33</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>1652.69</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G41" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:BLUESTARCO","Chart 📈")</f>
+        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
+          <t>NIFTY BANK</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="C42" s="14" t="n">
-        <v>1386.6</v>
+        <v>339.7</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>1374.28</v>
+        <v>338.65</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>1374.05</v>
+        <v>337.29</v>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1359.37</v>
+        <v>312.78</v>
       </c>
       <c r="G42" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ICICIBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="n">
-        <v>459</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <v>436.54</v>
-      </c>
-      <c r="E43" s="14" t="n">
-        <v>423.72</v>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>408.44</v>
-      </c>
-      <c r="G43" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:KOTAKBANK","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="16" t="inlineStr">
-        <is>
-          <t>NIFTY FINANCIAL SERVICES</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C44" s="14" t="n">
-        <v>3231</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>3199.53</v>
-      </c>
-      <c r="E44" s="14" t="n">
-        <v>3172.46</v>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>2835.14</v>
-      </c>
-      <c r="G44" s="15">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:MCX","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B45" s="17" t="inlineStr">
-        <is>
-          <t>ADANIGREEN</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>1307</v>
-      </c>
-      <c r="D45" s="18" t="n">
-        <v>1276.97</v>
-      </c>
-      <c r="E45" s="18" t="n">
-        <v>1298.27</v>
-      </c>
-      <c r="F45" s="18" t="n">
-        <v>1259.71</v>
-      </c>
-      <c r="G45" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:ADANIGREEN","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>NIFTY ENERGY</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>NHPC</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>73.28</v>
-      </c>
-      <c r="E46" s="18" t="n">
-        <v>74.44</v>
-      </c>
-      <c r="F46" s="18" t="n">
-        <v>77.09999999999999</v>
-      </c>
-      <c r="G46" s="19">
-        <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:NHPC","Chart 📈")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>NIFTY BANK</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="n">
-        <v>347.75</v>
-      </c>
-      <c r="D47" s="14" t="n">
-        <v>338.54</v>
-      </c>
-      <c r="E47" s="14" t="n">
-        <v>337.19</v>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>312.52</v>
-      </c>
-      <c r="G47" s="15">
         <f>HYPERLINK("https://www.tradingview.com/chart/?symbol=NSE:FEDERALBNK","Chart 📈")</f>
         <v/>
       </c>
